--- a/public/datos/plan_cuadrillas_risaralda.xlsx
+++ b/public/datos/plan_cuadrillas_risaralda.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plan'!$A$1:$AD$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plan'!$A$1:$AD$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD61"/>
+  <dimension ref="A1:AD63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,7 +636,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>LAS PALMAS</t>
+          <t>JESUS DE LA BUENA ESPERANZA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>166001002754</t>
+          <t>166001000450</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>AV DEL RIO NO 43 - 26</t>
+          <t>CR 3 NO 34 - 46</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>6.25</v>
+        <v>4.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.41</v>
+        <v>5.64</v>
       </c>
       <c r="R2" t="n">
-        <v>15.3</v>
+        <v>10.3</v>
       </c>
       <c r="S2" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -708,12 +708,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Carrera 5</t>
+          <t>Carrera 2 Bis</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>4.818122534</v>
+        <v>4.819868522229693</v>
       </c>
       <c r="AD2" t="n">
-        <v>-75.71553498</v>
+        <v>-75.70621902228969</v>
       </c>
     </row>
     <row r="3">
@@ -744,15 +744,15 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Pereira</t>
@@ -760,17 +760,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>JESUS DE LA BUENA ESPERANZA</t>
+          <t>PROVIDENCIA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA JESUS DE LA BUENA ESPERANZA</t>
+          <t>COMPLEJO EDUCATIVO LA JULITA</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>166001000450</t>
+          <t>166001004978</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>CR 3 NO 34 - 46</t>
+          <t>KR 20 23 15</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -799,20 +799,20 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.41</v>
+        <v>5.49</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.63</v>
+        <v>4.56</v>
       </c>
       <c r="R3" t="n">
-        <v>15.3</v>
+        <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 14 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 3 m de esa vía.</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Carrera 3</t>
+          <t>Carrera 20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>4.819642871</v>
+        <v>4.803937</v>
       </c>
       <c r="AD3" t="n">
-        <v>-75.70678902</v>
+        <v>-75.699062</v>
       </c>
     </row>
     <row r="4">
@@ -868,11 +868,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -884,17 +884,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA LUIS CARLOS GONZALEZ MEJIA</t>
+          <t>LAS PALMAS</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA LUIS CARLOS GONZALEZ MEJIA</t>
+          <t>INSTITUCION EDUCATIVA JESUS DE LA BUENA ESPERANZA</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>166001003505</t>
+          <t>166001002754</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>KR 17 82 103</t>
+          <t>AV DEL RIO NO 43 - 26</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Belen De Umbria</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>14.02</v>
+        <v>6.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.05</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>116.1</v>
+        <v>15.5</v>
       </c>
       <c r="S4" t="n">
-        <v>78.5</v>
+        <v>6</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -956,7 +956,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 9 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Carrera 5</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -965,10 +970,10 @@
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>4.806935893</v>
+        <v>4.818122534</v>
       </c>
       <c r="AD4" t="n">
-        <v>-75.74500842</v>
+        <v>-75.71553498</v>
       </c>
     </row>
     <row r="5">
@@ -987,14 +992,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1003,17 +1008,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>EL PLACER</t>
+          <t>INSTITUCION EDUCATIVA SAN FERNANDO</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA COMBIA</t>
+          <t>INSTITUCION EDUCATIVA SAN FERNANDO</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>266001001698</t>
+          <t>166001000344</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1023,12 +1028,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>CRUCERO DE COMBIA</t>
+          <t>IND CLL 70 NO 23-20 SAN FERNANDO CUBA</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1038,29 +1043,29 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Belen De Umbria</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>17.05</v>
+        <v>13.53</v>
       </c>
       <c r="Q5" t="n">
-        <v>85</v>
+        <v>1.83</v>
       </c>
       <c r="R5" t="n">
-        <v>116.1</v>
+        <v>31.7</v>
       </c>
       <c r="S5" t="n">
-        <v>78.5</v>
+        <v>14.1</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1075,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 147 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 5 m de esa vía.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1084,10 +1089,10 @@
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>4.819139218</v>
+        <v>4.805705</v>
       </c>
       <c r="AD5" t="n">
-        <v>-75.76076208000001</v>
+        <v>-75.73962299999999</v>
       </c>
     </row>
     <row r="6">
@@ -1106,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SE MARIA AUXILIADORA</t>
+          <t>INST EDUCATIVA JESUS MARIA ORMAZA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>IE LICEO DE OCCIDENTE</t>
+          <t>INSTITUCION EDUCATIVA JESUS MARIA ORMAZA</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>166383000195</t>
+          <t>166001000646</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>La Celia</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1147,39 +1152,39 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CL 5 2 69</t>
+          <t>CL 70 22 00 BR CUBA</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Belen De Umbria</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>95.02</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>51.88</v>
+        <v>16.37</v>
       </c>
       <c r="R6" t="n">
-        <v>146.9</v>
+        <v>31.7</v>
       </c>
       <c r="S6" t="n">
-        <v>89</v>
+        <v>14.1</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1194,12 +1199,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 18 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 35 m de esa vía.</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Calle 5</t>
+          <t>Calle 75</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1208,10 +1213,10 @@
         </is>
       </c>
       <c r="AC6" t="n">
-        <v>5.00296197</v>
+        <v>4.803217136</v>
       </c>
       <c r="AD6" t="n">
-        <v>-76.00271345</v>
+        <v>-75.74425404</v>
       </c>
     </row>
     <row r="7">
@@ -1230,11 +1235,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -1246,64 +1251,64 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SE INSTITUTO SANTUARIO - SEDE PRINCIPAL</t>
+          <t>SE MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>INSTITUCIÓN EDUCATIVA INSTITUTO SANTUARIO</t>
+          <t>IE LICEO DE OCCIDENTE</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>166687000256</t>
+          <t>166383000195</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>La Celia</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>CL 5 2 69</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>Santuario</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>CL 6 7 17</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Santuario</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Santuario</t>
-        </is>
-      </c>
       <c r="P7" t="n">
-        <v>0.1</v>
+        <v>96.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.08</v>
+        <v>51.88</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2</v>
+        <v>148.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1318,12 +1323,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 18 m de esa vía.</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Carrera 7</t>
+          <t>Calle 5</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="AC7" t="n">
-        <v>5.072806629</v>
+        <v>5.00296197</v>
       </c>
       <c r="AD7" t="n">
-        <v>-75.96351957</v>
+        <v>-76.00271345</v>
       </c>
     </row>
     <row r="8">
@@ -1354,11 +1359,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -1370,17 +1375,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SE LA BAMBA</t>
+          <t>SE INSTITUTO SANTUARIO - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IE MARIA AUXILIADORA</t>
+          <t>INSTITUCIÓN EDUCATIVA INSTITUTO SANTUARIO</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>266687000030</t>
+          <t>166687000256</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1390,12 +1395,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>VDA LA BAMBA</t>
+          <t>CL 6 7 17</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1409,16 +1414,16 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>34.86</v>
+        <v>0.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>26.5</v>
+        <v>0.08</v>
       </c>
       <c r="R8" t="n">
-        <v>61.4</v>
+        <v>0.2</v>
       </c>
       <c r="S8" t="n">
-        <v>17.5</v>
+        <v>0.1</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1442,7 +1447,12 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 121 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Carrera 7</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1451,10 +1461,10 @@
         </is>
       </c>
       <c r="AC8" t="n">
-        <v>5.063056</v>
+        <v>5.072806629</v>
       </c>
       <c r="AD8" t="n">
-        <v>-75.99972200000001</v>
+        <v>-75.96351957</v>
       </c>
     </row>
     <row r="9">
@@ -1469,15 +1479,15 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -1489,17 +1499,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SE NUESTRA SEÑORA DEL ROSARIO - SEDE PRINCIPAL</t>
+          <t>SE LA BAMBA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CE NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>IE MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>266687000331</t>
+          <t>266687000030</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1514,7 +1524,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>CGTO PERALONSO</t>
+          <t>VDA LA BAMBA</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1524,20 +1534,20 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apia</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>49.62</v>
+        <v>34.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>58.58</v>
+        <v>26.5</v>
       </c>
       <c r="R9" t="n">
-        <v>108.2</v>
+        <v>61.4</v>
       </c>
       <c r="S9" t="n">
-        <v>42.3</v>
+        <v>17.5</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1561,19 +1571,19 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 12 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 121 m de esa vía.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC9" t="n">
-        <v>4.99014911697</v>
+        <v>5.063056</v>
       </c>
       <c r="AD9" t="n">
-        <v>-75.9242208477</v>
+        <v>-75.99972200000001</v>
       </c>
     </row>
     <row r="10">
@@ -1592,11 +1602,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -1608,22 +1618,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SE CAJA DE ORO</t>
+          <t>SE NUESTRA SEÑORA DEL ROSARIO - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IE INTERCULTURAL DOKABU</t>
+          <t>CE NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>266572001237</t>
+          <t>266687000331</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1633,54 +1643,54 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>VDA CAJA DE ORO</t>
+          <t>CGTO PERALONSO</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>Santuario</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>Apia</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Pueblo Rico</t>
-        </is>
-      </c>
       <c r="P10" t="n">
-        <v>167.98</v>
+        <v>49.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>120.41</v>
+        <v>58.58</v>
       </c>
       <c r="R10" t="n">
-        <v>288.4</v>
+        <v>108.2</v>
       </c>
       <c r="S10" t="n">
-        <v>90.5</v>
+        <v>42.3</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>camino destapado</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 240 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1689,10 +1699,10 @@
         </is>
       </c>
       <c r="AC10" t="n">
-        <v>5.331280525</v>
+        <v>4.99014911697</v>
       </c>
       <c r="AD10" t="n">
-        <v>-75.9852455</v>
+        <v>-75.9242208477</v>
       </c>
     </row>
     <row r="11">
@@ -1711,11 +1721,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -1727,55 +1737,55 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SE SAN PEDRO CLAVER</t>
+          <t>SE ANTONIA SANTOS</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>IE AGROAMBIENTAL PIO XII</t>
+          <t>IE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>266572000141</t>
+          <t>166045000198</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Apía</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>CGTO SANTA CECILIA</t>
+          <t>KR 7 7 49</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Apia</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Apia</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>48.16</v>
+        <v>0.21</v>
       </c>
       <c r="Q11" t="n">
-        <v>48.79</v>
+        <v>0.17</v>
       </c>
       <c r="R11" t="n">
-        <v>98.40000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="S11" t="n">
-        <v>63.9</v>
+        <v>0.1</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1799,12 +1809,12 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 20 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Calle 3</t>
+          <t>Carrera 7</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1813,10 +1823,10 @@
         </is>
       </c>
       <c r="AC11" t="n">
-        <v>5.340317929</v>
+        <v>5.104722222</v>
       </c>
       <c r="AD11" t="n">
-        <v>-76.14533188999999</v>
+        <v>-75.9425</v>
       </c>
     </row>
     <row r="12">
@@ -1835,14 +1845,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1851,69 +1861,69 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SE SAN PABLO - SEDE PRINCIPAL</t>
+          <t>SE LA FLORESTA - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>IE SAN PABLO</t>
+          <t>IE LA FLORESTA</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>166572000015</t>
+          <t>266045000061</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Apía</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>KR 5 4 51</t>
+          <t>VDA LA FLORESTA</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Apia</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Apia</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>48.79</v>
+        <v>21.47</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.42</v>
+        <v>23.33</v>
       </c>
       <c r="R12" t="n">
-        <v>98.40000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="S12" t="n">
-        <v>63.9</v>
+        <v>17.8</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1923,12 +1933,12 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 75 m de esa vía.</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Calle 3 A</t>
+          <t>Mateguadua-Apia</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -1937,10 +1947,10 @@
         </is>
       </c>
       <c r="AC12" t="n">
-        <v>5.21916175028</v>
+        <v>5.11777777778</v>
       </c>
       <c r="AD12" t="n">
-        <v>-76.0331189595</v>
+        <v>-75.90472222219999</v>
       </c>
     </row>
     <row r="13">
@@ -1959,11 +1969,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -1975,22 +1985,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SE BICHUBARA</t>
+          <t>ESCUELA PATIO BONITO</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>IE DACHI DADA KERA</t>
+          <t>IE PATIO BONITO</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>466572001121</t>
+          <t>266383800005</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>La Celia</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2000,39 +2010,39 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>VDA BICHUBARA</t>
+          <t>VDA PATIO BONITO</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Apia</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>50.02</v>
+        <v>48.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.82</v>
+        <v>0.43</v>
       </c>
       <c r="R13" t="n">
-        <v>109.2</v>
+        <v>98.8</v>
       </c>
       <c r="S13" t="n">
-        <v>74.09999999999999</v>
+        <v>41.2</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -2047,19 +2057,19 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «primary»). La sede queda a 3687 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC13" t="n">
-        <v>5.312197</v>
+        <v>4.997163</v>
       </c>
       <c r="AD13" t="n">
-        <v>-76.166676</v>
+        <v>-75.980045</v>
       </c>
     </row>
     <row r="14">
@@ -2078,11 +2088,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F14" t="n">
         <v>2</v>
@@ -2094,22 +2104,22 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SE SIKUEDO</t>
+          <t>SE PATIO BONITO - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>IE DACHI DADA KERA</t>
+          <t>IE PATIO BONITO</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>266572000940</t>
+          <t>266383000050</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>La Celia</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2119,39 +2129,39 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>VDA SIKUEDO</t>
+          <t>VDA PATIO BONITO</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Apia</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>4.82</v>
+        <v>0.43</v>
       </c>
       <c r="Q14" t="n">
-        <v>54.39</v>
+        <v>50.17</v>
       </c>
       <c r="R14" t="n">
-        <v>109.2</v>
+        <v>98.8</v>
       </c>
       <c r="S14" t="n">
-        <v>74.09999999999999</v>
+        <v>41.2</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2166,7 +2176,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «primary»). La sede queda a 281 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 92 m de esa vía.</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2175,10 +2185,10 @@
         </is>
       </c>
       <c r="AC14" t="n">
-        <v>5.355261</v>
+        <v>4.996254019</v>
       </c>
       <c r="AD14" t="n">
-        <v>-76.177787</v>
+        <v>-75.98177889999999</v>
       </c>
     </row>
     <row r="15">
@@ -2197,11 +2207,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -2213,22 +2223,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>SE OSKORDO</t>
+          <t>SE TAMBORES - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>IE INTERCULTURAL DOKABU</t>
+          <t>IE TAMBORES</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>266572001326</t>
+          <t>266075000022</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Balboa</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2238,30 +2248,30 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>VDA OSKORDO</t>
+          <t>VDA TAMBORES</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apia</t>
+          <t>Cartago</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>104.73</v>
+        <v>83.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>119.27</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>224</v>
+        <v>154</v>
       </c>
       <c r="S15" t="n">
-        <v>79.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2275,17 +2285,17 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>La vía de entrada es otra según OpenStreetMap (clase «track_grade3»). La sede queda a 5445 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 1 m de esa vía.</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2294,10 +2304,10 @@
         </is>
       </c>
       <c r="AC15" t="n">
-        <v>5.275278</v>
+        <v>4.885083</v>
       </c>
       <c r="AD15" t="n">
-        <v>-76.162778</v>
+        <v>-75.97331699999999</v>
       </c>
     </row>
     <row r="16">
@@ -2312,42 +2322,42 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ESCUELA PATIO BONITO</t>
+          <t>EL PLACER</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>IE PATIO BONITO</t>
+          <t>INSTITUCION EDUCATIVA COMBIA</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>266383800005</t>
+          <t>266001001698</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>La Celia</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2357,44 +2367,44 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>VDA PATIO BONITO</t>
+          <t>CRUCERO DE COMBIA</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Apia</t>
+          <t>Cartago</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>48.23</v>
+        <v>41.84</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.43</v>
+        <v>16.71</v>
       </c>
       <c r="R16" t="n">
-        <v>98.8</v>
+        <v>74.2</v>
       </c>
       <c r="S16" t="n">
-        <v>41.2</v>
+        <v>42.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2404,7 +2414,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 2 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 147 m de esa vía.</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2413,10 +2423,10 @@
         </is>
       </c>
       <c r="AC16" t="n">
-        <v>4.997163</v>
+        <v>4.819139218</v>
       </c>
       <c r="AD16" t="n">
-        <v>-75.980045</v>
+        <v>-75.76076208000001</v>
       </c>
     </row>
     <row r="17">
@@ -2431,89 +2441,89 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SE PATIO BONITO - SEDE PRINCIPAL</t>
+          <t>INSTITUCION EDUCATIVA LUIS CARLOS GONZALEZ MEJIA</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>IE PATIO BONITO</t>
+          <t>INSTITUCION EDUCATIVA LUIS CARLOS GONZALEZ MEJIA</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>266383000050</t>
+          <t>166001003505</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>La Celia</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>VDA PATIO BONITO</t>
+          <t>KR 17 82 103</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Apia</t>
+          <t>Cartago</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.43</v>
+        <v>16.71</v>
       </c>
       <c r="Q17" t="n">
-        <v>50.17</v>
+        <v>15.61</v>
       </c>
       <c r="R17" t="n">
-        <v>98.8</v>
+        <v>74.2</v>
       </c>
       <c r="S17" t="n">
-        <v>41.2</v>
+        <v>42.7</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2523,7 +2533,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 92 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 9 m de esa vía.</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2532,16 +2542,16 @@
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>4.996254019</v>
+        <v>4.806935893</v>
       </c>
       <c r="AD17" t="n">
-        <v>-75.98177889999999</v>
+        <v>-75.74500842</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2550,57 +2560,57 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SE TAMBORES - SEDE PRINCIPAL</t>
+          <t>BASICO OTUN</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>IE TAMBORES</t>
+          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>266075000022</t>
+          <t>166170000329</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Balboa</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>VDA TAMBORES</t>
+          <t>BARRIO SAN JUDAS EL BALSO</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2609,40 +2619,45 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>83.7</v>
+        <v>5.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>93.56999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="R18" t="n">
-        <v>177.3</v>
+        <v>18</v>
       </c>
       <c r="S18" t="n">
-        <v>95.3</v>
+        <v>6.8</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 1 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 7 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Carrera 19</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2651,16 +2666,16 @@
         </is>
       </c>
       <c r="AC18" t="n">
-        <v>4.885083</v>
+        <v>4.816666667</v>
       </c>
       <c r="AD18" t="n">
-        <v>-75.97331699999999</v>
+        <v>-75.68333333</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2669,7 +2684,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,34 +2692,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA SAN FERNANDO</t>
+          <t>LUIS CARLOS GONZALES MEJIA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA SAN FERNANDO</t>
+          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>166001000344</t>
+          <t>166170001490</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2714,7 +2729,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>IND CLL 70 NO 23-20 SAN FERNANDO CUBA</t>
+          <t>BARRIO VILLA ALEXANDRA</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2724,34 +2739,34 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>13.53</v>
+        <v>4.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.83</v>
+        <v>7.6</v>
       </c>
       <c r="R19" t="n">
-        <v>44.5</v>
+        <v>18</v>
       </c>
       <c r="S19" t="n">
-        <v>18.9</v>
+        <v>6.8</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Bajo</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2761,7 +2776,12 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 5 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 5 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Calle 9</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2770,16 +2790,16 @@
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>4.805705</v>
+        <v>4.823055556</v>
       </c>
       <c r="AD19" t="n">
-        <v>-75.73962299999999</v>
+        <v>-75.6925</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2788,42 +2808,42 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>INST EDUCATIVA JESUS MARIA ORMAZA</t>
+          <t>POPULAR DIOCESANO</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA JESUS MARIA ORMAZA</t>
+          <t>INSTITUCION EDUCATIVA POPULAR DIOCESANO</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>166001000646</t>
+          <t>166170000256</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2833,7 +2853,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>CL 70 22 00 BR CUBA</t>
+          <t>LA BADEA</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2843,29 +2863,29 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.83</v>
+        <v>11.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>29.11</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>44.5</v>
+        <v>22.4</v>
       </c>
       <c r="S20" t="n">
-        <v>18.9</v>
+        <v>9</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Bajo</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -2880,12 +2900,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 35 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>Calle 75</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -2894,16 +2909,16 @@
         </is>
       </c>
       <c r="AC20" t="n">
-        <v>4.803217136</v>
+        <v>4.824166667</v>
       </c>
       <c r="AD20" t="n">
-        <v>-75.74425404</v>
+        <v>-75.69972222</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2912,7 +2927,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2920,81 +2935,81 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dosquebradas</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>LA BADEA</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>166170001741</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Dos Quebradas</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>BARRIO LA BADEA(ENSEGUIDA A LA IGLESIA)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
         <v>1</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Pereira</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>PROVIDENCIA</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>COMPLEJO EDUCATIVO LA JULITA</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>166001004978</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Pereira</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>KR 20 23 15</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Dos Quebradas</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Pereira</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>15.19</v>
-      </c>
       <c r="Q21" t="n">
-        <v>4.56</v>
+        <v>9.9</v>
       </c>
       <c r="R21" t="n">
-        <v>19.8</v>
+        <v>22.4</v>
       </c>
       <c r="S21" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3004,24 +3019,19 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 3 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>Carrera 20</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 20 m de esa vía.</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AC21" t="n">
-        <v>4.803937</v>
+        <v>4.82381384716</v>
       </c>
       <c r="AD21" t="n">
-        <v>-75.699062</v>
+        <v>-75.699591841</v>
       </c>
     </row>
     <row r="22">
@@ -3040,48 +3050,48 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>BASICO OTUN</t>
+          <t>SE LAS TAZAS</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
+          <t>IE AGRICOLA MARSELLA</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>166170000329</t>
+          <t>266440000100</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>BARRIO SAN JUDAS EL BALSO</t>
+          <t>VDA LAS TAZAS</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3091,24 +3101,24 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>5.75</v>
+        <v>51.42</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.5</v>
+        <v>11.61</v>
       </c>
       <c r="R22" t="n">
-        <v>17.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>6.7</v>
+        <v>35.5</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3118,22 +3128,17 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 7 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>Carrera 19</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 35 m de esa vía.</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3142,10 +3147,10 @@
         </is>
       </c>
       <c r="AC22" t="n">
-        <v>4.816666667</v>
+        <v>4.9022</v>
       </c>
       <c r="AD22" t="n">
-        <v>-75.68333333</v>
+        <v>-75.773707</v>
       </c>
     </row>
     <row r="23">
@@ -3164,48 +3169,48 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>INSTITUTO EDUCATIVO EMPRESARIAL</t>
+          <t>SE LA BORDADITA</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
+          <t>IE AGRICOLA MARSELLA</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>166170001911</t>
+          <t>266440000525</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>LA BADEA -ANTIGUA  PLAZA DE FERIAS</t>
+          <t>RESG INDIGENA ALTO MIRA</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3215,49 +3220,44 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>4.5</v>
+        <v>11.61</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.44</v>
+        <v>34.84</v>
       </c>
       <c r="R23" t="n">
-        <v>17.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>6.7</v>
+        <v>35.5</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 21 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Calle 9</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 40 m de esa vía.</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="AC23" t="n">
-        <v>4.823055556</v>
+        <v>4.928985175</v>
       </c>
       <c r="AD23" t="n">
-        <v>-75.69194444</v>
+        <v>-75.77832192</v>
       </c>
     </row>
     <row r="24">
@@ -3288,85 +3288,85 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>MANUELA BELTRAN</t>
+          <t>SE ALTO CAUCA - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA CRISTO REY</t>
+          <t>IE INSTITUTO AGRICOLA ALTO CAUCA</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>166170000272</t>
+          <t>266440000070</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>KR 19 64 08</t>
+          <t>CGTO ALTO CAUCA</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Santa Rosa De Cabal</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>14.36</v>
+        <v>34.87</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.86</v>
+        <v>7.8</v>
       </c>
       <c r="R24" t="n">
-        <v>30.6</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>15.7</v>
+        <v>22.9</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>camino destapado</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3376,24 +3376,19 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 17 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Calle 64</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 110 m de esa vía.</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AC24" t="n">
-        <v>4.843075404</v>
+        <v>4.991425841</v>
       </c>
       <c r="AD24" t="n">
-        <v>-75.66069447</v>
+        <v>-75.75301358</v>
       </c>
     </row>
     <row r="25">
@@ -3412,100 +3407,100 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
         <v>2</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA CRISTO REY</t>
+          <t>ANTONIO JOSE DE SUCRE</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA CRISTO REY</t>
+          <t>IE INSTITUTO AGRICOLA ALTO CAUCA</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>166170000159</t>
+          <t>266440800017</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>CLLE 67 # 18-01 BARRIO LA CAPILLA</t>
+          <t>CORREGIMIENTO DE ALTO CAUCA</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Santa Rosa De Cabal</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.86</v>
+        <v>7.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>15.33</v>
+        <v>34.19</v>
       </c>
       <c r="R25" t="n">
-        <v>30.6</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>15.7</v>
+        <v>22.9</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 11 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 7 m de esa vía.</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Calle 67</t>
+          <t>Buena Vista</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3514,10 +3509,10 @@
         </is>
       </c>
       <c r="AC25" t="n">
-        <v>4.844819</v>
+        <v>4.992762</v>
       </c>
       <c r="AD25" t="n">
-        <v>-75.660687</v>
+        <v>-75.74432</v>
       </c>
     </row>
     <row r="26">
@@ -3536,11 +3531,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -3552,22 +3547,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>SE PEDRO URIBE MEJIA - SEDE PRINCIPAL</t>
+          <t>SE EL RAYO</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>IE INSTITUTO AGRICOLA PEDRO URIBE MEJIA</t>
+          <t>IE INSTITUTO ESTRADA</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>266682000465</t>
+          <t>266440000274</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Santa Rosa de Cabal</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3577,30 +3572,30 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>VDA EL JAZMIN</t>
+          <t>VDA EL RAYO</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Santa Rosa De Cabal</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Santa Rosa De Cabal</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>22.68</v>
+        <v>15.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>33.82</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="R26" t="n">
-        <v>86.09999999999999</v>
+        <v>50.1</v>
       </c>
       <c r="S26" t="n">
-        <v>37.4</v>
+        <v>19.3</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -3624,24 +3619,19 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 135 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>A Campoalegre</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 22 m de esa vía.</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AC26" t="n">
-        <v>4.914981371</v>
+        <v>4.909338798</v>
       </c>
       <c r="AD26" t="n">
-        <v>-75.61788369</v>
+        <v>-75.72299636</v>
       </c>
     </row>
     <row r="27">
@@ -3660,11 +3650,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
         <v>2</v>
@@ -3676,22 +3666,22 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SE CHARCO HONDO</t>
+          <t>SE SAN ANDRES</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>IE INSTITUTO AGRICOLA PEDRO URIBE MEJIA</t>
+          <t>IE INSTITUTO ESTRADA</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>266682000996</t>
+          <t>266440000045</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Santa Rosa de Cabal</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3701,30 +3691,30 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>VDA CHARCO HONDO</t>
+          <t>VDA SAN ANDRES</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Santa Rosa De Cabal</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Santa Rosa De Cabal</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>33.82</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>29.58</v>
+        <v>25.13</v>
       </c>
       <c r="R27" t="n">
-        <v>86.09999999999999</v>
+        <v>50.1</v>
       </c>
       <c r="S27" t="n">
-        <v>37.4</v>
+        <v>19.3</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -3748,19 +3738,24 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 55 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 318 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Vía la Bodega</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AC27" t="n">
-        <v>4.966084</v>
+        <v>4.896608682</v>
       </c>
       <c r="AD27" t="n">
-        <v>-75.63563000000001</v>
+        <v>-75.71433512</v>
       </c>
     </row>
     <row r="28">
@@ -3779,11 +3774,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
@@ -3795,17 +3790,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>SE COL DE JESUS</t>
+          <t>SE EL ESPAÑOL</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>IE INSTITUTO TECNOLOGICO SANTA ROSA DE CABAL</t>
+          <t>IE INSTITUTO AGRICOLA LA FLORIDA</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>166682001025</t>
+          <t>266682001771</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3815,35 +3810,35 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>KR 15 12 71</t>
+          <t>CGTO EL ESPAÑOL</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
+          <t>Marsella</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
           <t>Santa Rosa De Cabal</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Dos Quebradas</t>
-        </is>
-      </c>
       <c r="P28" t="n">
-        <v>1.84</v>
+        <v>42.71</v>
       </c>
       <c r="Q28" t="n">
-        <v>16.02</v>
+        <v>51.83</v>
       </c>
       <c r="R28" t="n">
-        <v>21.2</v>
+        <v>105</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>43.1</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -3857,7 +3852,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3867,12 +3862,12 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 14 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 20 m de esa vía.</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Carrera 15</t>
+          <t>Al Español</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -3881,10 +3876,10 @@
         </is>
       </c>
       <c r="AC28" t="n">
-        <v>4.865108</v>
+        <v>4.932181</v>
       </c>
       <c r="AD28" t="n">
-        <v>-75.62179101</v>
+        <v>-75.698198</v>
       </c>
     </row>
     <row r="29">
@@ -3903,75 +3898,75 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F29" t="n">
         <v>2</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ANTONIO JOSE DE SUCRE</t>
+          <t>SE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA PABLO SEXTO</t>
+          <t>IE INSTITUTO AGROPECUARIO VERACRUZ</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>166170000043</t>
+          <t>266682001372</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Santa Rosa de Cabal</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>CL 16 14 A 19</t>
+          <t>VDA SANTO DOMINGO</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
+          <t>Marsella</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
           <t>Santa Rosa De Cabal</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Dos Quebradas</t>
-        </is>
-      </c>
       <c r="P29" t="n">
-        <v>16.02</v>
+        <v>51.83</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.34</v>
+        <v>10.45</v>
       </c>
       <c r="R29" t="n">
-        <v>21.2</v>
+        <v>105</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>43.1</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -3981,22 +3976,17 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 23 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>Calle 61</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 30 m de esa vía.</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4005,10 +3995,10 @@
         </is>
       </c>
       <c r="AC29" t="n">
-        <v>4.843896232</v>
+        <v>4.884255</v>
       </c>
       <c r="AD29" t="n">
-        <v>-75.66503904</v>
+        <v>-75.634398</v>
       </c>
     </row>
     <row r="30">
@@ -4023,79 +4013,79 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ELADIA MEJIA GONZALEZ</t>
+          <t>SE PEDRO URIBE MEJIA - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA PABLO SEXTO</t>
+          <t>IE INSTITUTO AGRICOLA PEDRO URIBE MEJIA</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>166170000175</t>
+          <t>266682000465</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Santa Rosa de Cabal</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>KR 21 41 80</t>
+          <t>VDA EL JAZMIN</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Santa Rosa De Cabal</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Santa Rosa De Cabal</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3.07</v>
+        <v>22.68</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.26</v>
+        <v>33.82</v>
       </c>
       <c r="R30" t="n">
-        <v>6.1</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="S30" t="n">
-        <v>2.1</v>
+        <v>37.4</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4105,22 +4095,22 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 12 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 135 m de esa vía.</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Carrera 21</t>
+          <t>A Campoalegre</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4129,10 +4119,10 @@
         </is>
       </c>
       <c r="AC30" t="n">
-        <v>4.833675657</v>
+        <v>4.914981371</v>
       </c>
       <c r="AD30" t="n">
-        <v>-75.66815895000001</v>
+        <v>-75.61788369</v>
       </c>
     </row>
     <row r="31">
@@ -4147,79 +4137,79 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F31" t="n">
         <v>2</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA PABLO VI</t>
+          <t>SE CHARCO HONDO</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA PABLO SEXTO</t>
+          <t>IE INSTITUTO AGRICOLA PEDRO URIBE MEJIA</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>166170000078</t>
+          <t>266682000996</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Santa Rosa de Cabal</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>CALLE 44 NO. 23 - 24</t>
+          <t>VDA CHARCO HONDO</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Santa Rosa De Cabal</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Santa Rosa De Cabal</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.26</v>
+        <v>33.82</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.8</v>
+        <v>29.58</v>
       </c>
       <c r="R31" t="n">
-        <v>6.1</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="S31" t="n">
-        <v>2.1</v>
+        <v>37.4</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4229,22 +4219,17 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 4 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>Carrera 23</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 55 m de esa vía.</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4253,10 +4238,10 @@
         </is>
       </c>
       <c r="AC31" t="n">
-        <v>4.834166667</v>
+        <v>4.966084</v>
       </c>
       <c r="AD31" t="n">
-        <v>-75.66527778</v>
+        <v>-75.63563000000001</v>
       </c>
     </row>
     <row r="32">
@@ -4271,79 +4256,79 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SAN RAFAEL</t>
+          <t>SE COL DE JESUS</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA FABIO VASQUEZ BOTERO</t>
+          <t>IE INSTITUTO TECNOLOGICO SANTA ROSA DE CABAL</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>166170001937</t>
+          <t>166682001025</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t>Santa Rosa de Cabal</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>KR 15 12 71</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Santa Rosa De Cabal</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
           <t>Dos Quebradas</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>KR 31 CL 13 SAN RAFAEL</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Dos Quebradas</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Dos Quebradas</t>
-        </is>
-      </c>
       <c r="P32" t="n">
-        <v>9.470000000000001</v>
+        <v>1.84</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.81</v>
+        <v>16.02</v>
       </c>
       <c r="R32" t="n">
-        <v>22.9</v>
+        <v>21.2</v>
       </c>
       <c r="S32" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4353,7 +4338,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4363,7 +4348,12 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 14 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Carrera 15</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4372,10 +4362,10 @@
         </is>
       </c>
       <c r="AC32" t="n">
-        <v>4.817222222</v>
+        <v>4.865108</v>
       </c>
       <c r="AD32" t="n">
-        <v>-75.6725</v>
+        <v>-75.62179101</v>
       </c>
     </row>
     <row r="33">
@@ -4390,15 +4380,15 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F33" t="n">
         <v>2</v>
@@ -4410,17 +4400,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>CENTRO EDUCATIVO NARANJALES</t>
+          <t>ANTONIO JOSE DE SUCRE</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA FABIO VASQUEZ BOTERO</t>
+          <t>INSTITUCION EDUCATIVA PABLO SEXTO</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>266170000897</t>
+          <t>166170000043</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4430,35 +4420,35 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>NARANJALES</t>
+          <t>CL 16 14 A 19</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
+          <t>Santa Rosa De Cabal</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
           <t>Dos Quebradas</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Dos Quebradas</t>
-        </is>
-      </c>
       <c r="P33" t="n">
-        <v>3.81</v>
+        <v>16.02</v>
       </c>
       <c r="Q33" t="n">
-        <v>9.65</v>
+        <v>3.34</v>
       </c>
       <c r="R33" t="n">
-        <v>22.9</v>
+        <v>21.2</v>
       </c>
       <c r="S33" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -4482,7 +4472,12 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 56 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 23 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Calle 61</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4491,10 +4486,10 @@
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>4.818297979</v>
+        <v>4.843896232</v>
       </c>
       <c r="AD33" t="n">
-        <v>-75.66450766</v>
+        <v>-75.66503904</v>
       </c>
     </row>
     <row r="34">
@@ -4513,11 +4508,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
@@ -4529,17 +4524,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FABIO VASQUEZ BOTERO</t>
+          <t>INSTITUCION EDUCATIVA PABLO VI</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA FABIO VASQUEZ BOTERO</t>
+          <t>INSTITUCION EDUCATIVA PABLO SEXTO</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>166170001023</t>
+          <t>166170000078</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4554,7 +4549,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>LA PRADERA</t>
+          <t>CALLE 44 NO. 23 - 24</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4564,29 +4559,29 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>7.14</v>
+        <v>2.64</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.33</v>
+        <v>1.24</v>
       </c>
       <c r="R34" t="n">
-        <v>23.4</v>
+        <v>5</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>1.7</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -4601,7 +4596,12 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 16 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 4 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Carrera 23</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="AC34" t="n">
-        <v>4.830277778</v>
+        <v>4.834166667</v>
       </c>
       <c r="AD34" t="n">
-        <v>-75.6825</v>
+        <v>-75.66527778</v>
       </c>
     </row>
     <row r="35">
@@ -4632,11 +4632,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F35" t="n">
         <v>2</v>
@@ -4648,17 +4648,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>LA BADEA</t>
+          <t>RUFINO JOSE CUERVO</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
+          <t>INSTITUCION EDUCATIVA PABLO SEXTO</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>166170001741</t>
+          <t>166170000744</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>BARRIO LA BADEA(ENSEGUIDA A LA IGLESIA)</t>
+          <t>KR 18 43 08</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4683,24 +4683,24 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>6.33</v>
+        <v>1.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.9</v>
+        <v>1.17</v>
       </c>
       <c r="R35" t="n">
-        <v>23.4</v>
+        <v>5</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>1.7</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -4720,19 +4720,24 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 20 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 18 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Carrera 18</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC35" t="n">
-        <v>4.82381384716</v>
+        <v>4.835834367</v>
       </c>
       <c r="AD35" t="n">
-        <v>-75.699591841</v>
+        <v>-75.66730004</v>
       </c>
     </row>
     <row r="36">
@@ -4751,53 +4756,53 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SE LAS MANGAS</t>
+          <t>MANUELA BELTRAN</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>IE INSTITUTO AGROPECUARIO VERACRUZ</t>
+          <t>INSTITUCION EDUCATIVA CRISTO REY</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>266682001101</t>
+          <t>166170000272</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Santa Rosa de Cabal</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>VDA LAS MANGAS</t>
+          <t>KR 19 64 08</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -4806,27 +4811,27 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>20.9</v>
+        <v>2.78</v>
       </c>
       <c r="Q36" t="n">
-        <v>23.55</v>
+        <v>0.86</v>
       </c>
       <c r="R36" t="n">
-        <v>50.1</v>
+        <v>7.4</v>
       </c>
       <c r="S36" t="n">
-        <v>19.4</v>
+        <v>3</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X36" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
@@ -4839,7 +4844,12 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 81 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 17 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Calle 64</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -4848,10 +4858,10 @@
         </is>
       </c>
       <c r="AC36" t="n">
-        <v>4.783364</v>
+        <v>4.843075404</v>
       </c>
       <c r="AD36" t="n">
-        <v>-75.641834</v>
+        <v>-75.66069447</v>
       </c>
     </row>
     <row r="37">
@@ -4870,11 +4880,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F37" t="n">
         <v>2</v>
@@ -4886,17 +4896,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CENTRO EDUCATIVO LAS VIOLETAS</t>
+          <t>INSTITUCION EDUCATIVA CRISTO REY</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA FABIO VASQUEZ BOTERO</t>
+          <t>INSTITUCION EDUCATIVA CRISTO REY</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>166170001562</t>
+          <t>166170000159</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4906,17 +4916,17 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>CL 26A KR 27A -28</t>
+          <t>CLLE 67 # 18-01 BARRIO LA CAPILLA</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4925,16 +4935,16 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>23.55</v>
+        <v>0.86</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.66</v>
+        <v>3.73</v>
       </c>
       <c r="R37" t="n">
-        <v>50.1</v>
+        <v>7.4</v>
       </c>
       <c r="S37" t="n">
-        <v>19.4</v>
+        <v>3</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -4958,7 +4968,12 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 36 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 11 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Calle 67</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -4967,10 +4982,10 @@
         </is>
       </c>
       <c r="AC37" t="n">
-        <v>4.825547182</v>
+        <v>4.844819</v>
       </c>
       <c r="AD37" t="n">
-        <v>-75.66634138000001</v>
+        <v>-75.660687</v>
       </c>
     </row>
     <row r="38">
@@ -4989,11 +5004,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
@@ -5005,7 +5020,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>RUFINO JOSE CUERVO</t>
+          <t>ELADIA MEJIA GONZALEZ</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5015,7 +5030,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>166170000744</t>
+          <t>166170000175</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5030,7 +5045,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>KR 18 43 08</t>
+          <t>KR 21 41 80</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5040,20 +5055,20 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.78</v>
+        <v>3.07</v>
       </c>
       <c r="Q38" t="n">
-        <v>10.76</v>
+        <v>4.1</v>
       </c>
       <c r="R38" t="n">
-        <v>77.3</v>
+        <v>12.8</v>
       </c>
       <c r="S38" t="n">
-        <v>36.7</v>
+        <v>4.3</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -5067,7 +5082,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -5077,12 +5092,12 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 18 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Carrera 18</t>
+          <t>Carrera 21</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5091,10 +5106,10 @@
         </is>
       </c>
       <c r="AC38" t="n">
-        <v>4.835834367</v>
+        <v>4.833675657</v>
       </c>
       <c r="AD38" t="n">
-        <v>-75.66730004</v>
+        <v>-75.66815895000001</v>
       </c>
     </row>
     <row r="39">
@@ -5113,11 +5128,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F39" t="n">
         <v>2</v>
@@ -5129,17 +5144,17 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>POPULAR DIOCESANO</t>
+          <t>CENTRO EDUCATIVO LAS VIOLETAS</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA POPULAR DIOCESANO</t>
+          <t>INSTITUCION EDUCATIVA FABIO VASQUEZ BOTERO</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>166170000256</t>
+          <t>166170001562</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5149,12 +5164,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>LA BADEA</t>
+          <t>CL 26A KR 27A -28</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5164,29 +5179,29 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>10.76</v>
+        <v>4.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>63.77</v>
+        <v>5.66</v>
       </c>
       <c r="R39" t="n">
-        <v>77.3</v>
+        <v>12.8</v>
       </c>
       <c r="S39" t="n">
-        <v>36.7</v>
+        <v>4.3</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -5201,7 +5216,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 6 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 36 m de esa vía.</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5210,10 +5225,10 @@
         </is>
       </c>
       <c r="AC39" t="n">
-        <v>4.824166667</v>
+        <v>4.825547182</v>
       </c>
       <c r="AD39" t="n">
-        <v>-75.69972222</v>
+        <v>-75.66634138000001</v>
       </c>
     </row>
     <row r="40">
@@ -5232,75 +5247,75 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SE ALTO CAUCA - SEDE PRINCIPAL</t>
+          <t>FABIO VASQUEZ BOTERO</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>IE INSTITUTO AGRICOLA ALTO CAUCA</t>
+          <t>INSTITUCION EDUCATIVA FABIO VASQUEZ BOTERO</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>266440000070</t>
+          <t>166170001023</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>CGTO ALTO CAUCA</t>
+          <t>LA PRADERA</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>34.87</v>
+        <v>7.14</v>
       </c>
       <c r="Q40" t="n">
-        <v>7.8</v>
+        <v>3.88</v>
       </c>
       <c r="R40" t="n">
-        <v>76.90000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="S40" t="n">
-        <v>22.9</v>
+        <v>7.2</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5310,29 +5325,29 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>camino destapado</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 110 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 16 m de esa vía.</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>4.991425841</v>
+        <v>4.830277778</v>
       </c>
       <c r="AD40" t="n">
-        <v>-75.75301358</v>
+        <v>-75.6825</v>
       </c>
     </row>
     <row r="41">
@@ -5351,100 +5366,100 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F41" t="n">
         <v>2</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>ANTONIO JOSE DE SUCRE</t>
+          <t>INSTITUTO EDUCATIVO EMPRESARIAL</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>IE INSTITUTO AGRICOLA ALTO CAUCA</t>
+          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>266440800017</t>
+          <t>166170001911</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>CORREGIMIENTO DE ALTO CAUCA</t>
+          <t>LA BADEA -ANTIGUA  PLAZA DE FERIAS</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>7.8</v>
+        <v>3.88</v>
       </c>
       <c r="Q41" t="n">
-        <v>34.19</v>
+        <v>7.44</v>
       </c>
       <c r="R41" t="n">
-        <v>76.90000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="S41" t="n">
-        <v>22.9</v>
+        <v>7.2</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 7 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 21 m de esa vía.</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>Buena Vista</t>
+          <t>Calle 9</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -5453,10 +5468,10 @@
         </is>
       </c>
       <c r="AC41" t="n">
-        <v>4.992762</v>
+        <v>4.823055556</v>
       </c>
       <c r="AD41" t="n">
-        <v>-75.74432</v>
+        <v>-75.69194444</v>
       </c>
     </row>
     <row r="42">
@@ -5471,15 +5486,15 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
@@ -5491,22 +5506,22 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SE EL RAYO</t>
+          <t>SE LAS MANGAS</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>IE INSTITUTO ESTRADA</t>
+          <t>IE INSTITUTO AGROPECUARIO VERACRUZ</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>266440000274</t>
+          <t>266682001101</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Santa Rosa de Cabal</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -5516,30 +5531,30 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>VDA EL RAYO</t>
+          <t>VDA LAS MANGAS</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>15.5</v>
+        <v>20.9</v>
       </c>
       <c r="Q42" t="n">
-        <v>9.460000000000001</v>
+        <v>21.38</v>
       </c>
       <c r="R42" t="n">
-        <v>50.1</v>
+        <v>51.9</v>
       </c>
       <c r="S42" t="n">
-        <v>19.3</v>
+        <v>20.4</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -5563,19 +5578,19 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 22 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 81 m de esa vía.</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC42" t="n">
-        <v>4.909338798</v>
+        <v>4.783364</v>
       </c>
       <c r="AD42" t="n">
-        <v>-75.72299636</v>
+        <v>-75.641834</v>
       </c>
     </row>
     <row r="43">
@@ -5590,42 +5605,42 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F43" t="n">
         <v>2</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>SE SAN ANDRES</t>
+          <t>CENTRO EDUCATIVO NARANJALES</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>IE INSTITUTO ESTRADA</t>
+          <t>INSTITUCION EDUCATIVA FABIO VASQUEZ BOTERO</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>266440000045</t>
+          <t>266170000897</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -5635,71 +5650,66 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>VDA SAN ANDRES</t>
+          <t>NARANJALES</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>9.460000000000001</v>
+        <v>21.38</v>
       </c>
       <c r="Q43" t="n">
-        <v>25.13</v>
+        <v>9.65</v>
       </c>
       <c r="R43" t="n">
-        <v>50.1</v>
+        <v>51.9</v>
       </c>
       <c r="S43" t="n">
-        <v>19.3</v>
+        <v>20.4</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
+          <t>Afectación menor</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 318 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Vía la Bodega</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 56 m de esa vía.</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC43" t="n">
-        <v>4.896608682</v>
+        <v>4.818297979</v>
       </c>
       <c r="AD43" t="n">
-        <v>-75.71433512</v>
+        <v>-75.66450766</v>
       </c>
     </row>
     <row r="44">
@@ -5714,99 +5724,99 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SE LAS TAZAS</t>
+          <t>SAN RAFAEL</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>IE AGRICOLA MARSELLA</t>
+          <t>INSTITUCION EDUCATIVA FABIO VASQUEZ BOTERO</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>266440000100</t>
+          <t>166170001937</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>VDA LAS TAZAS</t>
+          <t>KR 31 CL 13 SAN RAFAEL</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>29.63</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="Q44" t="n">
-        <v>11.61</v>
+        <v>3.41</v>
       </c>
       <c r="R44" t="n">
-        <v>76.09999999999999</v>
+        <v>22.3</v>
       </c>
       <c r="S44" t="n">
-        <v>29.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 35 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -5815,10 +5825,10 @@
         </is>
       </c>
       <c r="AC44" t="n">
-        <v>4.9022</v>
+        <v>4.817222222</v>
       </c>
       <c r="AD44" t="n">
-        <v>-75.773707</v>
+        <v>-75.6725</v>
       </c>
     </row>
     <row r="45">
@@ -5833,75 +5843,75 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F45" t="n">
         <v>2</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SE LA BORDADITA</t>
+          <t>LUIS CARLOS GALAN SARMIENTO</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>IE AGRICOLA MARSELLA</t>
+          <t>INSTITUCION EDUCATIVA POPULAR DIOCESANO</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>266440000525</t>
+          <t>166170001481</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>RESG INDIGENA ALTO MIRA</t>
+          <t>BARRIO LAS VEGAS</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>11.61</v>
+        <v>3.41</v>
       </c>
       <c r="Q45" t="n">
-        <v>34.84</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="R45" t="n">
-        <v>76.09999999999999</v>
+        <v>22.3</v>
       </c>
       <c r="S45" t="n">
-        <v>29.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -5910,22 +5920,27 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 40 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 13 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Carrera 24A</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -5934,16 +5949,16 @@
         </is>
       </c>
       <c r="AC45" t="n">
-        <v>4.928985175</v>
+        <v>4.816944444</v>
       </c>
       <c r="AD45" t="n">
-        <v>-75.77832192</v>
+        <v>-75.67805556</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5952,7 +5967,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5960,7 +5975,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
@@ -5972,22 +5987,22 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SE EL ESPAÑOL</t>
+          <t>SE AGUA SALADA</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>IE INSTITUTO AGRICOLA LA FLORIDA</t>
+          <t>IE SAUSAGUA</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>266682001771</t>
+          <t>266594000544</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Santa Rosa de Cabal</t>
+          <t>Quinchía</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5997,39 +6012,39 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>CGTO EL ESPAÑOL</t>
+          <t>VDA AGUA SALADA</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Quinchia</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>42.71</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="Q46" t="n">
-        <v>51.83</v>
+        <v>29.34</v>
       </c>
       <c r="R46" t="n">
-        <v>116.3</v>
+        <v>118.1</v>
       </c>
       <c r="S46" t="n">
-        <v>50.9</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -6044,12 +6059,12 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 20 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 19 m de esa vía.</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Al Español</t>
+          <t>Via Irra a Quinchia</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -6058,16 +6073,16 @@
         </is>
       </c>
       <c r="AC46" t="n">
-        <v>4.932181</v>
+        <v>5.29672</v>
       </c>
       <c r="AD46" t="n">
-        <v>-75.698198</v>
+        <v>-75.66537599999999</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6076,18 +6091,18 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -6096,22 +6111,22 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SE SANTO DOMINGO</t>
+          <t>SE ENCENILLAL</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>IE INSTITUTO AGROPECUARIO VERACRUZ</t>
+          <t>IE NUCLEO ESCOLAR RURAL</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>266682001372</t>
+          <t>266594000234</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Santa Rosa de Cabal</t>
+          <t>Quinchía</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -6121,30 +6136,30 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>VDA SANTO DOMINGO</t>
+          <t>VDA ENCENILLAL</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Quinchia</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Quinchia</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>51.83</v>
+        <v>10.14</v>
       </c>
       <c r="Q47" t="n">
-        <v>21.8</v>
+        <v>10.98</v>
       </c>
       <c r="R47" t="n">
-        <v>116.3</v>
+        <v>21.1</v>
       </c>
       <c r="S47" t="n">
-        <v>50.9</v>
+        <v>6.5</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -6168,7 +6183,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 30 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 199 m de esa vía.</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6177,16 +6192,16 @@
         </is>
       </c>
       <c r="AC47" t="n">
-        <v>4.884255</v>
+        <v>5.328055556</v>
       </c>
       <c r="AD47" t="n">
-        <v>-75.634398</v>
+        <v>-75.74833332999999</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6195,79 +6210,79 @@
         </is>
       </c>
       <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
         <v>3</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>martes</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>14</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>LUIS CARLOS GALAN SARMIENTO</t>
+          <t>SE NUESTRA SEÑORA DE LA CEIBA</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA POPULAR DIOCESANO</t>
+          <t>IE NUCLEO ESCOLAR RURAL</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>166170001481</t>
+          <t>266594000340</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Quinchía</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>BARRIO LAS VEGAS</t>
+          <t>VDA LA CEIBA</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Quinchia</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Quinchia</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>10.53</v>
+        <v>12.46</v>
       </c>
       <c r="Q48" t="n">
-        <v>5.99</v>
+        <v>13.76</v>
       </c>
       <c r="R48" t="n">
-        <v>24.1</v>
+        <v>26.2</v>
       </c>
       <c r="S48" t="n">
-        <v>9.199999999999999</v>
+        <v>13.1</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -6277,22 +6292,17 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 13 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>Carrera 24A</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 36 m de esa vía.</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -6301,16 +6311,16 @@
         </is>
       </c>
       <c r="AC48" t="n">
-        <v>4.816944444</v>
+        <v>5.370566</v>
       </c>
       <c r="AD48" t="n">
-        <v>-75.67805556</v>
+        <v>-75.74896699999999</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6319,75 +6329,75 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>LUIS CARLOS GONZALES MEJIA</t>
+          <t>SE EL TRIUNFO</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
+          <t>IE AGROPECUARIO NARANJAL</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>166170001490</t>
+          <t>266594000382</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Quinchía</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>BARRIO VILLA ALEXANDRA</t>
+          <t>VDA GUERRERO</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Quinchia</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Quinchia</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>5.99</v>
+        <v>34.41</v>
       </c>
       <c r="Q49" t="n">
-        <v>7.6</v>
+        <v>35.17</v>
       </c>
       <c r="R49" t="n">
-        <v>24.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S49" t="n">
-        <v>9.199999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -6396,27 +6406,22 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 5 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>Calle 9</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -6425,10 +6430,10 @@
         </is>
       </c>
       <c r="AC49" t="n">
-        <v>4.823055556</v>
+        <v>5.283929</v>
       </c>
       <c r="AD49" t="n">
-        <v>-75.6925</v>
+        <v>-75.69113299999999</v>
       </c>
     </row>
     <row r="50">
@@ -6447,11 +6452,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
@@ -6463,64 +6468,64 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SE LA FLORESTA - SEDE PRINCIPAL</t>
+          <t>SE INSTITUTO GUATICA - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>IE LA FLORESTA</t>
+          <t>IE INSTITUTO GUATICA</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>266045000061</t>
+          <t>166318000030</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Apía</t>
+          <t>Guática</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>VDA LA FLORESTA</t>
+          <t>IND BR GAMONRRA</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Quinchia</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Apia</t>
+          <t>Mistrato</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>104.36</v>
+        <v>30.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>23.33</v>
+        <v>13.31</v>
       </c>
       <c r="R50" t="n">
-        <v>127.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="S50" t="n">
-        <v>78.8</v>
+        <v>43.3</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
@@ -6535,24 +6540,24 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 75 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 13 m de esa vía.</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>Mateguadua-Apia</t>
+          <t>Calle 12</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC50" t="n">
-        <v>5.11777777778</v>
+        <v>5.318849336</v>
       </c>
       <c r="AD50" t="n">
-        <v>-75.90472222219999</v>
+        <v>-75.80047681000001</v>
       </c>
     </row>
     <row r="51">
@@ -6571,15 +6576,15 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E51" t="n">
+        <v>5</v>
+      </c>
+      <c r="F51" t="n">
         <v>2</v>
       </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>Risaralda</t>
@@ -6587,64 +6592,64 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SE ANTONIA SANTOS</t>
+          <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>IE SAGRADA FAMILIA</t>
+          <t>IE SANTA ANA</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>166045000198</t>
+          <t>266318800006</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Apía</t>
+          <t>Guática</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>KR 7 7 49</t>
+          <t>CORREGIMIENTO SANTA ANA</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Apia</t>
+          <t>Quinchia</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Apia</t>
+          <t>Mistrato</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0.21</v>
+        <v>13.31</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.17</v>
+        <v>36.83</v>
       </c>
       <c r="R51" t="n">
-        <v>0.4</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="S51" t="n">
-        <v>0.1</v>
+        <v>43.3</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
@@ -6659,12 +6664,12 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 4 m de esa vía.</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>Carrera 7</t>
+          <t>Carrera 4</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -6673,10 +6678,10 @@
         </is>
       </c>
       <c r="AC51" t="n">
-        <v>5.104722222</v>
+        <v>5.30751835</v>
       </c>
       <c r="AD51" t="n">
-        <v>-75.9425</v>
+        <v>-75.82041798</v>
       </c>
     </row>
     <row r="52">
@@ -6695,11 +6700,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
@@ -6711,22 +6716,22 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SE EL ABEJERO</t>
+          <t>SE ALTO PUEBLO RICO</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>IE SANTA EMILIA</t>
+          <t>IE INSTITUTO MISTRATO</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>266088000315</t>
+          <t>266456000100</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Belén de Umbría</t>
+          <t>Mistrató</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -6736,44 +6741,44 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>VDA EL ABEJERO</t>
+          <t>VDA ALTO PUEBLO RICO</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Apia</t>
+          <t>Mistrato</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Belen De Umbria</t>
+          <t>Mistrato</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>67.72</v>
+        <v>6.84</v>
       </c>
       <c r="Q52" t="n">
-        <v>48.09</v>
+        <v>9.26</v>
       </c>
       <c r="R52" t="n">
-        <v>115.8</v>
+        <v>16.1</v>
       </c>
       <c r="S52" t="n">
-        <v>35.5</v>
+        <v>7.6</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -6783,7 +6788,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>La vía de entrada es otra según OpenStreetMap (clase «track_grade3»). La sede queda a 293 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 11 m de esa vía.</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -6792,10 +6797,10 @@
         </is>
       </c>
       <c r="AC52" t="n">
-        <v>5.151535</v>
+        <v>5.279785869</v>
       </c>
       <c r="AD52" t="n">
-        <v>-75.904819</v>
+        <v>-75.89025909</v>
       </c>
     </row>
     <row r="53">
@@ -6810,15 +6815,15 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
@@ -6830,17 +6835,17 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SE COLEGIO TECNICO AGROPECUARIO TAPARCAL - SEDE PRINCIPAL</t>
+          <t>SE EL TIGRE</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>IE COLEGIO TECNICO AGROPECUARIO TAPARCAL</t>
+          <t>IE SANTA EMILIA</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>266088000528</t>
+          <t>266088000366</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -6855,54 +6860,54 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>CGTO TAPARCAL</t>
+          <t>VDA EL TIGRE</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
+          <t>Mistrato</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
           <t>Belen De Umbria</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>Belen De Umbria</t>
-        </is>
-      </c>
       <c r="P53" t="n">
-        <v>14.18</v>
+        <v>53.11</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.26</v>
+        <v>32.26</v>
       </c>
       <c r="R53" t="n">
-        <v>31.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="S53" t="n">
-        <v>10.5</v>
+        <v>35.1</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Colapso total</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino destapado</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 44 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
@@ -6911,10 +6916,10 @@
         </is>
       </c>
       <c r="AC53" t="n">
-        <v>5.165871128</v>
+        <v>5.174781</v>
       </c>
       <c r="AD53" t="n">
-        <v>-75.86350014999999</v>
+        <v>-75.89761</v>
       </c>
     </row>
     <row r="54">
@@ -6929,19 +6934,19 @@
         </is>
       </c>
       <c r="C54" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>8</v>
+      </c>
+      <c r="F54" t="n">
         <v>1</v>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>jueves</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>4</v>
-      </c>
-      <c r="F54" t="n">
-        <v>2</v>
-      </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>Risaralda</t>
@@ -6949,7 +6954,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SE TAPARCAL</t>
+          <t>SE COLEGIO TECNICO AGROPECUARIO TAPARCAL - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6959,7 +6964,7 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>266088000111</t>
+          <t>266088000528</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -6988,10 +6993,10 @@
         </is>
       </c>
       <c r="P54" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="Q54" t="n">
         <v>0.26</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>16.89</v>
       </c>
       <c r="R54" t="n">
         <v>31.3</v>
@@ -7001,12 +7006,12 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Colapso total</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
@@ -7021,7 +7026,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 44 m de esa vía.</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
@@ -7030,10 +7035,10 @@
         </is>
       </c>
       <c r="AC54" t="n">
-        <v>5.165833</v>
+        <v>5.165871128</v>
       </c>
       <c r="AD54" t="n">
-        <v>-75.864133</v>
+        <v>-75.86350014999999</v>
       </c>
     </row>
     <row r="55">
@@ -7048,18 +7053,18 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -7068,17 +7073,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SE EL TIGRE</t>
+          <t>SE TAPARCAL</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>IE SANTA EMILIA</t>
+          <t>IE COLEGIO TECNICO AGROPECUARIO TAPARCAL</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>266088000366</t>
+          <t>266088000111</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -7093,7 +7098,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>VDA EL TIGRE</t>
+          <t>CGTO TAPARCAL</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7107,20 +7112,20 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>26.66</v>
+        <v>0.26</v>
       </c>
       <c r="Q55" t="n">
-        <v>32.26</v>
+        <v>16.89</v>
       </c>
       <c r="R55" t="n">
-        <v>58.9</v>
+        <v>31.3</v>
       </c>
       <c r="S55" t="n">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -7130,17 +7135,17 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>camino destapado</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 8 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -7149,10 +7154,10 @@
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>5.174781</v>
+        <v>5.165833</v>
       </c>
       <c r="AD55" t="n">
-        <v>-75.89761</v>
+        <v>-75.864133</v>
       </c>
     </row>
     <row r="56">
@@ -7167,15 +7172,15 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
@@ -7187,22 +7192,22 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SE AGUA SALADA</t>
+          <t>SE EL ABEJERO</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>IE SAUSAGUA</t>
+          <t>IE SANTA EMILIA</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>266594000544</t>
+          <t>266088000315</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Quinchía</t>
+          <t>Belén de Umbría</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -7212,7 +7217,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>VDA AGUA SALADA</t>
+          <t>VDA EL ABEJERO</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -7222,20 +7227,20 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Quinchia</t>
+          <t>Apia</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>65.5</v>
+        <v>40.29</v>
       </c>
       <c r="Q56" t="n">
-        <v>29.34</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="R56" t="n">
-        <v>94.8</v>
+        <v>116.8</v>
       </c>
       <c r="S56" t="n">
-        <v>75.59999999999999</v>
+        <v>35.5</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -7249,7 +7254,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>otra</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -7259,12 +7264,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 19 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>Via Irra a Quinchia</t>
+          <t>La vía de entrada es otra según OpenStreetMap (clase «track_grade3»). La sede queda a 293 m de esa vía.</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -7273,10 +7273,10 @@
         </is>
       </c>
       <c r="AC56" t="n">
-        <v>5.29672</v>
+        <v>5.151535</v>
       </c>
       <c r="AD56" t="n">
-        <v>-75.66537599999999</v>
+        <v>-75.904819</v>
       </c>
     </row>
     <row r="57">
@@ -7295,11 +7295,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -7311,22 +7311,22 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>SE ENCENILLAL</t>
+          <t>SE CAJA DE ORO</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>IE NUCLEO ESCOLAR RURAL</t>
+          <t>IE INTERCULTURAL DOKABU</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>266594000234</t>
+          <t>266572001237</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Quinchía</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -7336,44 +7336,44 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>VDA ENCENILLAL</t>
+          <t>VDA CAJA DE ORO</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Quinchia</t>
+          <t>Apia</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Quinchia</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>10.14</v>
+        <v>167.98</v>
       </c>
       <c r="Q57" t="n">
-        <v>10.98</v>
+        <v>120.41</v>
       </c>
       <c r="R57" t="n">
-        <v>21.1</v>
+        <v>288.4</v>
       </c>
       <c r="S57" t="n">
-        <v>6.5</v>
+        <v>90.5</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>camino destapado</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -7383,19 +7383,19 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 199 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 240 m de esa vía.</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AC57" t="n">
-        <v>5.328055556</v>
+        <v>5.331280525</v>
       </c>
       <c r="AD57" t="n">
-        <v>-75.74833332999999</v>
+        <v>-75.9852455</v>
       </c>
     </row>
     <row r="58">
@@ -7414,11 +7414,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
@@ -7430,22 +7430,22 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SE INSTITUTO GUATICA - SEDE PRINCIPAL</t>
+          <t>SE SAN PABLO - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>IE INSTITUTO GUATICA</t>
+          <t>IE SAN PABLO</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>166318000030</t>
+          <t>166572000015</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Guática</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -7455,44 +7455,44 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>IND BR GAMONRRA</t>
+          <t>KR 5 4 51</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Quinchia</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Mistrato</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>30.5</v>
+        <v>1.82</v>
       </c>
       <c r="Q58" t="n">
-        <v>48.79</v>
+        <v>1.42</v>
       </c>
       <c r="R58" t="n">
-        <v>79.3</v>
+        <v>3.2</v>
       </c>
       <c r="S58" t="n">
-        <v>43.1</v>
+        <v>0.8</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -7502,24 +7502,24 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 13 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Calle 12</t>
+          <t>Calle 3 A</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AC58" t="n">
-        <v>5.318849336</v>
+        <v>5.21916175028</v>
       </c>
       <c r="AD58" t="n">
-        <v>-75.80047681000001</v>
+        <v>-76.0331189595</v>
       </c>
     </row>
     <row r="59">
@@ -7538,11 +7538,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F59" t="n">
         <v>1</v>
@@ -7554,22 +7554,22 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>SE ALTO PUEBLO RICO</t>
+          <t>SE SAN PEDRO CLAVER</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>IE INSTITUTO MISTRATO</t>
+          <t>IE AGROAMBIENTAL PIO XII</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>266456000100</t>
+          <t>266572000141</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Mistrató</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -7579,30 +7579,30 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>VDA ALTO PUEBLO RICO</t>
+          <t>CGTO SANTA CECILIA</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Mistrato</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Mistrato</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>6.84</v>
+        <v>48.16</v>
       </c>
       <c r="Q59" t="n">
-        <v>9.26</v>
+        <v>12.95</v>
       </c>
       <c r="R59" t="n">
-        <v>16.1</v>
+        <v>107.9</v>
       </c>
       <c r="S59" t="n">
-        <v>7.6</v>
+        <v>67</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -7626,7 +7626,12 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 11 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 20 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>Calle 3</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
@@ -7635,10 +7640,10 @@
         </is>
       </c>
       <c r="AC59" t="n">
-        <v>5.279785869</v>
+        <v>5.340317929</v>
       </c>
       <c r="AD59" t="n">
-        <v>-75.89025909</v>
+        <v>-76.14533188999999</v>
       </c>
     </row>
     <row r="60">
@@ -7657,14 +7662,14 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7673,22 +7678,22 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>SE NUESTRA SEÑORA DE LA CEIBA</t>
+          <t>ESCUELA NUEVA AGÜITA</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>IE NUCLEO ESCOLAR RURAL</t>
+          <t>IE INTERCULTURAL DOKABU</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>266594000340</t>
+          <t>266572800032</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Quinchía</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -7698,39 +7703,39 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>VDA LA CEIBA</t>
+          <t>VDA AGUITA</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Mistrato</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Quinchia</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>62.93</v>
+        <v>12.95</v>
       </c>
       <c r="Q60" t="n">
-        <v>13.76</v>
+        <v>46.77</v>
       </c>
       <c r="R60" t="n">
-        <v>76.7</v>
+        <v>107.9</v>
       </c>
       <c r="S60" t="n">
-        <v>44.3</v>
+        <v>67</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -7745,7 +7750,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 36 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 58 m de esa vía.</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
@@ -7754,10 +7759,10 @@
         </is>
       </c>
       <c r="AC60" t="n">
-        <v>5.370566</v>
+        <v>5.366205</v>
       </c>
       <c r="AD60" t="n">
-        <v>-75.74896699999999</v>
+        <v>-76.10596200000001</v>
       </c>
     </row>
     <row r="61">
@@ -7772,15 +7777,15 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F61" t="n">
         <v>1</v>
@@ -7792,22 +7797,22 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SE EL TRIUNFO</t>
+          <t>SE BICHUBARA</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>IE AGROPECUARIO NARANJAL</t>
+          <t>IE DACHI DADA KERA</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>266594000382</t>
+          <t>466572001121</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Quinchía</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -7817,30 +7822,30 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>VDA GUERRERO</t>
+          <t>VDA BICHUBARA</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Quinchia</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>34.41</v>
+        <v>50.02</v>
       </c>
       <c r="Q61" t="n">
-        <v>101.84</v>
+        <v>4.82</v>
       </c>
       <c r="R61" t="n">
-        <v>136.2</v>
+        <v>109.2</v>
       </c>
       <c r="S61" t="n">
-        <v>96.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -7854,33 +7859,271 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 8 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «primary»). La sede queda a 3687 m de esa vía.</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="AC61" t="n">
+        <v>5.312197</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>-76.166676</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>13</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>SE SIKUEDO</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>IE DACHI DADA KERA</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>266572000940</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Pueblo Rico</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>VDA SIKUEDO</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Pueblo Rico</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Pueblo Rico</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>54.39</v>
+      </c>
+      <c r="R62" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="S62" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>via principal pavimentada</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>fácil</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «primary»). La sede queda a 281 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC61" t="n">
-        <v>5.283929</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>-75.69113299999999</v>
+      <c r="AC62" t="n">
+        <v>5.355261</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>-76.177787</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>14</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>SE OSKORDO</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>IE INTERCULTURAL DOKABU</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>266572001326</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Pueblo Rico</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>VDA OSKORDO</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Pueblo Rico</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Apia</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>104.73</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>119.27</v>
+      </c>
+      <c r="R63" t="n">
+        <v>224</v>
+      </c>
+      <c r="S63" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Sin afectación</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sin afectación</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>otra</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>fácil</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>La vía de entrada es otra según OpenStreetMap (clase «track_grade3»). La sede queda a 5445 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AC63" t="n">
+        <v>5.275278</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>-76.162778</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD61"/>
+  <autoFilter ref="A1:AD63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7906,7 +8149,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>63 SE Risaralda. Las 60 sedes ruteables de las 63 del listado V5. Las otras tres no tienen coordenada en ninguna fuente y se le pidieron al MEN el 22-sep-2026. Tres cuadrillas con base en Pereira: con dos no cabe. Sin volver a la base los domingos.</t>
+          <t>63 SE Risaralda. Las 62 sedes ruteables de las 63 del listado V5. Falta KURMADO (Marsella), que no tiene coordenada en ninguna fuente. Dos de las tres que faltaban se ubicaron con fotos georreferenciadas el 24-sep-2026. Tres cuadrillas con base en Pereira: con dos no cabe. Sin volver a la base los domingos.</t>
         </is>
       </c>
     </row>
@@ -7918,7 +8161,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -8026,22 +8269,22 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>13</v>
+      </c>
+      <c r="C10" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>349</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" t="n">
         <v>14</v>
-      </c>
-      <c r="C10" t="n">
-        <v>20</v>
-      </c>
-      <c r="D10" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>704</v>
-      </c>
-      <c r="F10" t="n">
-        <v>11</v>
-      </c>
-      <c r="G10" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -8057,13 +8300,13 @@
         <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>11.3</v>
+        <v>9.9</v>
       </c>
       <c r="E11" t="n">
-        <v>277</v>
+        <v>229</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
         <v>15</v>
@@ -8076,22 +8319,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>12.6</v>
+        <v>21.6</v>
       </c>
       <c r="E12" t="n">
-        <v>418</v>
+        <v>588</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/public/datos/plan_cuadrillas_risaralda.xlsx
+++ b/public/datos/plan_cuadrillas_risaralda.xlsx
@@ -2580,7 +2580,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>BASICO OTUN</t>
+          <t>LUIS CARLOS GONZALES MEJIA</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>166170000329</t>
+          <t>166170001490</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>BARRIO SAN JUDAS EL BALSO</t>
+          <t>BARRIO VILLA ALEXANDRA</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2619,13 +2619,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5.75</v>
+        <v>9.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.6</v>
+        <v>0.14</v>
       </c>
       <c r="R18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S18" t="n">
         <v>6.8</v>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 7 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 5 m de esa vía.</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Carrera 19</t>
+          <t>Calle 9</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="AC18" t="n">
-        <v>4.816666667</v>
+        <v>4.823055556</v>
       </c>
       <c r="AD18" t="n">
-        <v>-75.68333333</v>
+        <v>-75.6925</v>
       </c>
     </row>
     <row r="19">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>LUIS CARLOS GONZALES MEJIA</t>
+          <t>INSTITUTO EDUCATIVO EMPRESARIAL</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>166170001490</t>
+          <t>166170001911</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>BARRIO VILLA ALEXANDRA</t>
+          <t>LA BADEA -ANTIGUA  PLAZA DE FERIAS</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2743,20 +2743,20 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.6</v>
+        <v>0.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.6</v>
+        <v>7.44</v>
       </c>
       <c r="R19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S19" t="n">
         <v>6.8</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 5 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 21 m de esa vía.</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2793,7 +2793,7 @@
         <v>4.823055556</v>
       </c>
       <c r="AD19" t="n">
-        <v>-75.6925</v>
+        <v>-75.69194444</v>
       </c>
     </row>
     <row r="20">
@@ -3343,16 +3343,16 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>34.87</v>
+        <v>28.62</v>
       </c>
       <c r="Q24" t="n">
-        <v>7.8</v>
+        <v>0.96</v>
       </c>
       <c r="R24" t="n">
-        <v>76.90000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="S24" t="n">
-        <v>22.9</v>
+        <v>18.8</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>camino destapado</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3376,19 +3376,24 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 110 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 2 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Buena Vista</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC24" t="n">
-        <v>4.991425841</v>
+        <v>4.994828</v>
       </c>
       <c r="AD24" t="n">
-        <v>-75.75301358</v>
+        <v>-75.743863</v>
       </c>
     </row>
     <row r="25">
@@ -3462,16 +3467,16 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>7.8</v>
+        <v>0.96</v>
       </c>
       <c r="Q25" t="n">
         <v>34.19</v>
       </c>
       <c r="R25" t="n">
-        <v>76.90000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="S25" t="n">
-        <v>22.9</v>
+        <v>18.8</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -5263,7 +5268,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FABIO VASQUEZ BOTERO</t>
+          <t>SAN RAFAEL</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5273,7 +5278,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>166170001023</t>
+          <t>166170001937</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5288,7 +5293,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>LA PRADERA</t>
+          <t>KR 31 CL 13 SAN RAFAEL</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5302,25 +5307,25 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>7.14</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.88</v>
+        <v>3.41</v>
       </c>
       <c r="R40" t="n">
-        <v>18.5</v>
+        <v>22.3</v>
       </c>
       <c r="S40" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -5335,7 +5340,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 16 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5344,10 +5349,10 @@
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>4.830277778</v>
+        <v>4.817222222</v>
       </c>
       <c r="AD40" t="n">
-        <v>-75.6825</v>
+        <v>-75.6725</v>
       </c>
     </row>
     <row r="41">
@@ -5382,17 +5387,17 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>INSTITUTO EDUCATIVO EMPRESARIAL</t>
+          <t>LUIS CARLOS GALAN SARMIENTO</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
+          <t>INSTITUCION EDUCATIVA POPULAR DIOCESANO</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>166170001911</t>
+          <t>166170001481</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5407,7 +5412,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>LA BADEA -ANTIGUA  PLAZA DE FERIAS</t>
+          <t>BARRIO LAS VEGAS</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5421,20 +5426,20 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.88</v>
+        <v>3.41</v>
       </c>
       <c r="Q41" t="n">
-        <v>7.44</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="R41" t="n">
-        <v>18.5</v>
+        <v>22.3</v>
       </c>
       <c r="S41" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5444,7 +5449,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -5454,12 +5459,12 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 21 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 13 m de esa vía.</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>Calle 9</t>
+          <t>Carrera 24A</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -5468,10 +5473,10 @@
         </is>
       </c>
       <c r="AC41" t="n">
-        <v>4.823055556</v>
+        <v>4.816944444</v>
       </c>
       <c r="AD41" t="n">
-        <v>-75.69194444</v>
+        <v>-75.67805556</v>
       </c>
     </row>
     <row r="42">
@@ -5744,7 +5749,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SAN RAFAEL</t>
+          <t>FABIO VASQUEZ BOTERO</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5754,7 +5759,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>166170001937</t>
+          <t>166170001023</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5769,7 +5774,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>KR 31 CL 13 SAN RAFAEL</t>
+          <t>LA PRADERA</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5783,25 +5788,25 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>9.470000000000001</v>
+        <v>7.14</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.41</v>
+        <v>5.72</v>
       </c>
       <c r="R44" t="n">
-        <v>22.3</v>
+        <v>19.5</v>
       </c>
       <c r="S44" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -5816,7 +5821,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 16 m de esa vía.</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -5825,10 +5830,10 @@
         </is>
       </c>
       <c r="AC44" t="n">
-        <v>4.817222222</v>
+        <v>4.830277778</v>
       </c>
       <c r="AD44" t="n">
-        <v>-75.6725</v>
+        <v>-75.6825</v>
       </c>
     </row>
     <row r="45">
@@ -5863,17 +5868,17 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>LUIS CARLOS GALAN SARMIENTO</t>
+          <t>BASICO OTUN</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA POPULAR DIOCESANO</t>
+          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>166170001481</t>
+          <t>166170000329</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -5888,7 +5893,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>BARRIO LAS VEGAS</t>
+          <t>BARRIO SAN JUDAS EL BALSO</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5902,16 +5907,16 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.41</v>
+        <v>5.72</v>
       </c>
       <c r="Q45" t="n">
-        <v>9.460000000000001</v>
+        <v>6.63</v>
       </c>
       <c r="R45" t="n">
-        <v>22.3</v>
+        <v>19.5</v>
       </c>
       <c r="S45" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -5935,12 +5940,12 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 13 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 7 m de esa vía.</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Carrera 24A</t>
+          <t>Carrera 19</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -5949,10 +5954,10 @@
         </is>
       </c>
       <c r="AC45" t="n">
-        <v>4.816944444</v>
+        <v>4.816666667</v>
       </c>
       <c r="AD45" t="n">
-        <v>-75.67805556</v>
+        <v>-75.68333333</v>
       </c>
     </row>
     <row r="46">
@@ -8161,7 +8166,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -8300,10 +8305,10 @@
         <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>

--- a/public/datos/plan_cuadrillas_risaralda.xlsx
+++ b/public/datos/plan_cuadrillas_risaralda.xlsx
@@ -631,27 +631,27 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>JESUS DE LA BUENA ESPERANZA</t>
+          <t>SE ANTONIA SANTOS</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA JESUS DE LA BUENA ESPERANZA</t>
+          <t>IE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>166001000450</t>
+          <t>166045000198</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Apía</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>CR 3 NO 34 - 46</t>
+          <t>KR 7 7 49</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -671,29 +671,29 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Apia</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>4.66</v>
+        <v>93.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.64</v>
+        <v>0.17</v>
       </c>
       <c r="R2" t="n">
-        <v>10.3</v>
+        <v>93.5</v>
       </c>
       <c r="S2" t="n">
-        <v>3.8</v>
+        <v>64.3</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Carrera 2 Bis</t>
+          <t>Carrera 7</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>4.819868522229693</v>
+        <v>5.104722222</v>
       </c>
       <c r="AD2" t="n">
-        <v>-75.70621902228969</v>
+        <v>-75.9425</v>
       </c>
     </row>
     <row r="3">
@@ -755,64 +755,64 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PROVIDENCIA</t>
+          <t>SE CAJA DE ORO</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMPLEJO EDUCATIVO LA JULITA</t>
+          <t>IE INTERCULTURAL DOKABU</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>166001004978</t>
+          <t>266572001237</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>KR 20 23 15</t>
+          <t>VDA CAJA DE ORO</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Apia</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>5.49</v>
+        <v>167.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.56</v>
+        <v>120.41</v>
       </c>
       <c r="R3" t="n">
-        <v>10</v>
+        <v>288.4</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5</v>
+        <v>90.5</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -822,34 +822,29 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>camino destapado</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 3 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Carrera 20</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 240 m de esa vía.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>4.803937</v>
+        <v>5.331280525</v>
       </c>
       <c r="AD3" t="n">
-        <v>-75.699062</v>
+        <v>-75.9852455</v>
       </c>
     </row>
     <row r="4">
@@ -879,27 +874,27 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>LAS PALMAS</t>
+          <t>SE SAN PABLO - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA JESUS DE LA BUENA ESPERANZA</t>
+          <t>IE SAN PABLO</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>166001002754</t>
+          <t>166572000015</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -909,30 +904,30 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>AV DEL RIO NO 43 - 26</t>
+          <t>KR 5 4 51</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>6.25</v>
+        <v>1.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.210000000000001</v>
+        <v>1.42</v>
       </c>
       <c r="R4" t="n">
-        <v>15.5</v>
+        <v>3.2</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -956,24 +951,24 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Carrera 5</t>
+          <t>Calle 3 A</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>4.818122534</v>
+        <v>5.21916175028</v>
       </c>
       <c r="AD4" t="n">
-        <v>-75.71553498</v>
+        <v>-76.0331189595</v>
       </c>
     </row>
     <row r="5">
@@ -1003,69 +998,69 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA SAN FERNANDO</t>
+          <t>SE SAN PEDRO CLAVER</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA SAN FERNANDO</t>
+          <t>IE AGROAMBIENTAL PIO XII</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>166001000344</t>
+          <t>266572000141</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>IND CLL 70 NO 23-20 SAN FERNANDO CUBA</t>
+          <t>CGTO SANTA CECILIA</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>13.53</v>
+        <v>48.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.83</v>
+        <v>12.95</v>
       </c>
       <c r="R5" t="n">
-        <v>31.7</v>
+        <v>107.9</v>
       </c>
       <c r="S5" t="n">
-        <v>14.1</v>
+        <v>67</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Bajo</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1080,7 +1075,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 5 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 20 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Calle 3</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>4.805705</v>
+        <v>5.340317929</v>
       </c>
       <c r="AD5" t="n">
-        <v>-75.73962299999999</v>
+        <v>-76.14533188999999</v>
       </c>
     </row>
     <row r="6">
@@ -1122,89 +1122,84 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>INST EDUCATIVA JESUS MARIA ORMAZA</t>
+          <t>ESCUELA NUEVA AGÜITA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA JESUS MARIA ORMAZA</t>
+          <t>IE INTERCULTURAL DOKABU</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>166001000646</t>
+          <t>266572800032</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CL 70 22 00 BR CUBA</t>
+          <t>VDA AGUITA</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>12.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.37</v>
+        <v>46.77</v>
       </c>
       <c r="R6" t="n">
-        <v>31.7</v>
+        <v>107.9</v>
       </c>
       <c r="S6" t="n">
-        <v>14.1</v>
+        <v>67</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Bajo</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 35 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Calle 75</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 58 m de esa vía.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1213,10 +1208,10 @@
         </is>
       </c>
       <c r="AC6" t="n">
-        <v>4.803217136</v>
+        <v>5.366205</v>
       </c>
       <c r="AD6" t="n">
-        <v>-75.74425404</v>
+        <v>-76.10596200000001</v>
       </c>
     </row>
     <row r="7">
@@ -1251,55 +1246,55 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SE MARIA AUXILIADORA</t>
+          <t>SE BICHUBARA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IE LICEO DE OCCIDENTE</t>
+          <t>IE DACHI DADA KERA</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>166383000195</t>
+          <t>466572001121</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>La Celia</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>CL 5 2 69</t>
+          <t>VDA BICHUBARA</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>96.25</v>
+        <v>50.02</v>
       </c>
       <c r="Q7" t="n">
-        <v>51.88</v>
+        <v>4.82</v>
       </c>
       <c r="R7" t="n">
-        <v>148.1</v>
+        <v>109.2</v>
       </c>
       <c r="S7" t="n">
-        <v>81.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1313,7 +1308,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1323,24 +1318,19 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 18 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Calle 5</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «primary»). La sede queda a 3687 m de esa vía.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AC7" t="n">
-        <v>5.00296197</v>
+        <v>5.312197</v>
       </c>
       <c r="AD7" t="n">
-        <v>-76.00271345</v>
+        <v>-76.166676</v>
       </c>
     </row>
     <row r="8">
@@ -1359,14 +1349,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1375,69 +1365,69 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SE INSTITUTO SANTUARIO - SEDE PRINCIPAL</t>
+          <t>SE SIKUEDO</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>INSTITUCIÓN EDUCATIVA INSTITUTO SANTUARIO</t>
+          <t>IE DACHI DADA KERA</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>166687000256</t>
+          <t>266572000940</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>CL 6 7 17</t>
+          <t>VDA SIKUEDO</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.1</v>
+        <v>4.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.08</v>
+        <v>54.39</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2</v>
+        <v>109.2</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1447,12 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Carrera 7</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «primary»). La sede queda a 281 m de esa vía.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1461,10 +1446,10 @@
         </is>
       </c>
       <c r="AC8" t="n">
-        <v>5.072806629</v>
+        <v>5.355261</v>
       </c>
       <c r="AD8" t="n">
-        <v>-75.96351957</v>
+        <v>-76.177787</v>
       </c>
     </row>
     <row r="9">
@@ -1479,15 +1464,15 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -1499,22 +1484,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SE LA BAMBA</t>
+          <t>SE OSKORDO</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IE MARIA AUXILIADORA</t>
+          <t>IE INTERCULTURAL DOKABU</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>266687000030</t>
+          <t>266572001326</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1524,30 +1509,30 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>VDA LA BAMBA</t>
+          <t>VDA OSKORDO</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Pueblo Rico</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Apia</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>34.86</v>
+        <v>104.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.5</v>
+        <v>119.27</v>
       </c>
       <c r="R9" t="n">
-        <v>61.4</v>
+        <v>224</v>
       </c>
       <c r="S9" t="n">
-        <v>17.5</v>
+        <v>79.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1561,7 +1546,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>otra</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1571,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 121 m de esa vía.</t>
+          <t>La vía de entrada es otra según OpenStreetMap (clase «track_grade3»). La sede queda a 5445 m de esa vía.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1580,10 +1565,10 @@
         </is>
       </c>
       <c r="AC9" t="n">
-        <v>5.063056</v>
+        <v>5.275278</v>
       </c>
       <c r="AD9" t="n">
-        <v>-75.99972200000001</v>
+        <v>-76.162778</v>
       </c>
     </row>
     <row r="10">
@@ -1602,11 +1587,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -1618,22 +1603,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SE NUESTRA SEÑORA DEL ROSARIO - SEDE PRINCIPAL</t>
+          <t>SE LA FLORESTA - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CE NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>IE LA FLORESTA</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>266687000331</t>
+          <t>266045000061</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Apía</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1643,30 +1628,30 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>CGTO PERALONSO</t>
+          <t>VDA LA FLORESTA</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Apia</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apia</t>
+          <t>Belen De Umbria</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>49.62</v>
+        <v>21.47</v>
       </c>
       <c r="Q10" t="n">
-        <v>58.58</v>
+        <v>50.13</v>
       </c>
       <c r="R10" t="n">
-        <v>108.2</v>
+        <v>119.7</v>
       </c>
       <c r="S10" t="n">
-        <v>42.3</v>
+        <v>35.5</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1680,7 +1665,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1690,7 +1675,12 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 12 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 75 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Mateguadua-Apia</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1699,10 +1689,10 @@
         </is>
       </c>
       <c r="AC10" t="n">
-        <v>4.99014911697</v>
+        <v>5.11777777778</v>
       </c>
       <c r="AD10" t="n">
-        <v>-75.9242208477</v>
+        <v>-75.90472222219999</v>
       </c>
     </row>
     <row r="11">
@@ -1721,14 +1711,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1737,32 +1727,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SE ANTONIA SANTOS</t>
+          <t>SE EL ABEJERO</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>IE SAGRADA FAMILIA</t>
+          <t>IE SANTA EMILIA</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>166045000198</t>
+          <t>266088000315</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Apía</t>
+          <t>Belén de Umbría</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>KR 7 7 49</t>
+          <t>VDA EL ABEJERO</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1772,34 +1762,34 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apia</t>
+          <t>Belen De Umbria</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.21</v>
+        <v>50.13</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.17</v>
+        <v>48.09</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4</v>
+        <v>119.7</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1</v>
+        <v>35.5</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>otra</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1809,12 +1799,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Carrera 7</t>
+          <t>La vía de entrada es otra según OpenStreetMap (clase «track_grade3»). La sede queda a 293 m de esa vía.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1823,10 +1808,10 @@
         </is>
       </c>
       <c r="AC11" t="n">
-        <v>5.104722222</v>
+        <v>5.151535</v>
       </c>
       <c r="AD11" t="n">
-        <v>-75.9425</v>
+        <v>-75.904819</v>
       </c>
     </row>
     <row r="12">
@@ -1845,11 +1830,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -1861,22 +1846,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SE LA FLORESTA - SEDE PRINCIPAL</t>
+          <t>SE COLEGIO TECNICO AGROPECUARIO TAPARCAL - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>IE LA FLORESTA</t>
+          <t>IE COLEGIO TECNICO AGROPECUARIO TAPARCAL</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>266045000061</t>
+          <t>266088000528</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Apía</t>
+          <t>Belén de Umbría</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1886,44 +1871,44 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>VDA LA FLORESTA</t>
+          <t>CGTO TAPARCAL</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Apia</t>
+          <t>Belen De Umbria</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apia</t>
+          <t>Belen De Umbria</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>21.47</v>
+        <v>14.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>23.33</v>
+        <v>0.26</v>
       </c>
       <c r="R12" t="n">
-        <v>44.8</v>
+        <v>31.3</v>
       </c>
       <c r="S12" t="n">
-        <v>17.8</v>
+        <v>10.5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Colapso total</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1933,24 +1918,19 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 75 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Mateguadua-Apia</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 44 m de esa vía.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC12" t="n">
-        <v>5.11777777778</v>
+        <v>5.165871128</v>
       </c>
       <c r="AD12" t="n">
-        <v>-75.90472222219999</v>
+        <v>-75.86350014999999</v>
       </c>
     </row>
     <row r="13">
@@ -1969,14 +1949,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1985,22 +1965,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ESCUELA PATIO BONITO</t>
+          <t>SE TAPARCAL</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>IE PATIO BONITO</t>
+          <t>IE COLEGIO TECNICO AGROPECUARIO TAPARCAL</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>266383800005</t>
+          <t>266088000111</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>La Celia</t>
+          <t>Belén de Umbría</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2010,44 +1990,44 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>VDA PATIO BONITO</t>
+          <t>CGTO TAPARCAL</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Apia</t>
+          <t>Belen De Umbria</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Belen De Umbria</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>48.23</v>
+        <v>0.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.43</v>
+        <v>16.89</v>
       </c>
       <c r="R13" t="n">
-        <v>98.8</v>
+        <v>31.3</v>
       </c>
       <c r="S13" t="n">
-        <v>41.2</v>
+        <v>10.5</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2057,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 2 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2066,10 +2046,10 @@
         </is>
       </c>
       <c r="AC13" t="n">
-        <v>4.997163</v>
+        <v>5.165833</v>
       </c>
       <c r="AD13" t="n">
-        <v>-75.980045</v>
+        <v>-75.864133</v>
       </c>
     </row>
     <row r="14">
@@ -2088,14 +2068,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2104,22 +2084,22 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SE PATIO BONITO - SEDE PRINCIPAL</t>
+          <t>SE EL TIGRE</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>IE PATIO BONITO</t>
+          <t>IE SANTA EMILIA</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>266383000050</t>
+          <t>266088000366</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>La Celia</t>
+          <t>Belén de Umbría</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2129,54 +2109,54 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>VDA PATIO BONITO</t>
+          <t>VDA EL TIGRE</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Apia</t>
+          <t>Belen De Umbria</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Mistrato</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.43</v>
+        <v>26.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>50.17</v>
+        <v>60.32</v>
       </c>
       <c r="R14" t="n">
-        <v>98.8</v>
+        <v>96.2</v>
       </c>
       <c r="S14" t="n">
-        <v>41.2</v>
+        <v>42.4</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>camino destapado</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 92 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2185,10 +2165,10 @@
         </is>
       </c>
       <c r="AC14" t="n">
-        <v>4.996254019</v>
+        <v>5.174781</v>
       </c>
       <c r="AD14" t="n">
-        <v>-75.98177889999999</v>
+        <v>-75.89761</v>
       </c>
     </row>
     <row r="15">
@@ -2207,14 +2187,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2223,22 +2203,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>SE TAMBORES - SEDE PRINCIPAL</t>
+          <t>SE ALTO PUEBLO RICO</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>IE TAMBORES</t>
+          <t>IE INSTITUTO MISTRATO</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>266075000022</t>
+          <t>266456000100</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Balboa</t>
+          <t>Mistrató</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2248,30 +2228,30 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>VDA TAMBORES</t>
+          <t>VDA ALTO PUEBLO RICO</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Belen De Umbria</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Cartago</t>
+          <t>Mistrato</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>83.7</v>
+        <v>60.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>70.34999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="R15" t="n">
-        <v>154</v>
+        <v>96.2</v>
       </c>
       <c r="S15" t="n">
-        <v>78.09999999999999</v>
+        <v>42.4</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2285,17 +2265,17 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 1 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 11 m de esa vía.</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2304,10 +2284,10 @@
         </is>
       </c>
       <c r="AC15" t="n">
-        <v>4.885083</v>
+        <v>5.279785869</v>
       </c>
       <c r="AD15" t="n">
-        <v>-75.97331699999999</v>
+        <v>-75.89025909</v>
       </c>
     </row>
     <row r="16">
@@ -2322,42 +2302,42 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>EL PLACER</t>
+          <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA COMBIA</t>
+          <t>IE SANTA ANA</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>266001001698</t>
+          <t>266318800006</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Guática</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2367,39 +2347,39 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>CRUCERO DE COMBIA</t>
+          <t>CORREGIMIENTO SANTA ANA</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Cartago</t>
+          <t>Mistrato</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Quinchia</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>41.84</v>
+        <v>32.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>16.71</v>
+        <v>13.35</v>
       </c>
       <c r="R16" t="n">
-        <v>74.2</v>
+        <v>80</v>
       </c>
       <c r="S16" t="n">
-        <v>42.7</v>
+        <v>43.4</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -2414,7 +2394,12 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 147 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 4 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Carrera 4</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2423,10 +2408,10 @@
         </is>
       </c>
       <c r="AC16" t="n">
-        <v>4.819139218</v>
+        <v>5.30751835</v>
       </c>
       <c r="AD16" t="n">
-        <v>-75.76076208000001</v>
+        <v>-75.82041798</v>
       </c>
     </row>
     <row r="17">
@@ -2441,42 +2426,42 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA LUIS CARLOS GONZALEZ MEJIA</t>
+          <t>SE INSTITUTO GUATICA - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA LUIS CARLOS GONZALEZ MEJIA</t>
+          <t>IE INSTITUTO GUATICA</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>166001003505</t>
+          <t>166318000030</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Guática</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2486,44 +2471,44 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>KR 17 82 103</t>
+          <t>IND BR GAMONRRA</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Cartago</t>
+          <t>Mistrato</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Quinchia</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>16.71</v>
+        <v>13.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>15.61</v>
+        <v>34.54</v>
       </c>
       <c r="R17" t="n">
-        <v>74.2</v>
+        <v>80</v>
       </c>
       <c r="S17" t="n">
-        <v>42.7</v>
+        <v>43.4</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2533,7 +2518,12 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 9 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 13 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Calle 12</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2542,16 +2532,16 @@
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>4.806935893</v>
+        <v>5.318849336</v>
       </c>
       <c r="AD17" t="n">
-        <v>-75.74500842</v>
+        <v>-75.80047681000001</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2560,79 +2550,79 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>LUIS CARLOS GONZALES MEJIA</t>
+          <t>SE ENCENILLAL</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
+          <t>IE NUCLEO ESCOLAR RURAL</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>166170001490</t>
+          <t>266594000234</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Quinchía</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>BARRIO VILLA ALEXANDRA</t>
+          <t>VDA ENCENILLAL</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Quinchia</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Quinchia</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>9.4</v>
+        <v>10.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.14</v>
+        <v>23.64</v>
       </c>
       <c r="R18" t="n">
-        <v>17</v>
+        <v>47.5</v>
       </c>
       <c r="S18" t="n">
-        <v>6.8</v>
+        <v>19.2</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2642,22 +2632,17 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 5 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Calle 9</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 199 m de esa vía.</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2666,16 +2651,16 @@
         </is>
       </c>
       <c r="AC18" t="n">
-        <v>4.823055556</v>
+        <v>5.328055556</v>
       </c>
       <c r="AD18" t="n">
-        <v>-75.6925</v>
+        <v>-75.74833332999999</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2684,79 +2669,79 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>INSTITUTO EDUCATIVO EMPRESARIAL</t>
+          <t>SE NUESTRA SEÑORA DE LA CEIBA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
+          <t>IE NUCLEO ESCOLAR RURAL</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>166170001911</t>
+          <t>266594000340</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Quinchía</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>LA BADEA -ANTIGUA  PLAZA DE FERIAS</t>
+          <t>VDA LA CEIBA</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Quinchia</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Quinchia</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0.14</v>
+        <v>23.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.44</v>
+        <v>13.76</v>
       </c>
       <c r="R19" t="n">
-        <v>17</v>
+        <v>47.5</v>
       </c>
       <c r="S19" t="n">
-        <v>6.8</v>
+        <v>19.2</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2766,22 +2751,17 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 21 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Calle 9</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 36 m de esa vía.</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2790,16 +2770,16 @@
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>4.823055556</v>
+        <v>5.370566</v>
       </c>
       <c r="AD19" t="n">
-        <v>-75.69194444</v>
+        <v>-75.74896699999999</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2808,99 +2788,99 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>POPULAR DIOCESANO</t>
+          <t>SE EL TRIUNFO</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA POPULAR DIOCESANO</t>
+          <t>IE AGROPECUARIO NARANJAL</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>166170000256</t>
+          <t>266594000382</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Quinchía</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>LA BADEA</t>
+          <t>VDA GUERRERO</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Quinchia</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Quinchia</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>11.45</v>
+        <v>34.41</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>35.17</v>
       </c>
       <c r="R20" t="n">
-        <v>22.4</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>32.6</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 6 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -2909,16 +2889,16 @@
         </is>
       </c>
       <c r="AC20" t="n">
-        <v>4.824166667</v>
+        <v>5.283929</v>
       </c>
       <c r="AD20" t="n">
-        <v>-75.69972222</v>
+        <v>-75.69113299999999</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2927,57 +2907,57 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>13</v>
+      </c>
+      <c r="F21" t="n">
         <v>1</v>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>martes</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2</v>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>LA BADEA</t>
+          <t>SE AGUA SALADA</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
+          <t>IE SAUSAGUA</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>166170001741</t>
+          <t>266594000544</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Quinchía</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>BARRIO LA BADEA(ENSEGUIDA A LA IGLESIA)</t>
+          <t>VDA AGUA SALADA</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Quinchia</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2986,30 +2966,30 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>29.79</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.9</v>
+        <v>86.23</v>
       </c>
       <c r="R21" t="n">
-        <v>22.4</v>
+        <v>116</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>89.7</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3019,19 +2999,24 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 20 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 19 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Via Irra a Quinchia</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC21" t="n">
-        <v>4.82381384716</v>
+        <v>5.29672</v>
       </c>
       <c r="AD21" t="n">
-        <v>-75.699591841</v>
+        <v>-75.66537599999999</v>
       </c>
     </row>
     <row r="22">
@@ -3050,48 +3035,48 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SE LAS TAZAS</t>
+          <t>LUIS CARLOS GONZALES MEJIA</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>IE AGRICOLA MARSELLA</t>
+          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>266440000100</t>
+          <t>166170001490</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>VDA LAS TAZAS</t>
+          <t>BARRIO VILLA ALEXANDRA</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3101,44 +3086,49 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>51.42</v>
+        <v>9.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>11.61</v>
+        <v>0.14</v>
       </c>
       <c r="R22" t="n">
-        <v>97.90000000000001</v>
+        <v>17</v>
       </c>
       <c r="S22" t="n">
-        <v>35.5</v>
+        <v>6.8</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 35 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 5 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Calle 9</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3147,10 +3137,10 @@
         </is>
       </c>
       <c r="AC22" t="n">
-        <v>4.9022</v>
+        <v>4.823055556</v>
       </c>
       <c r="AD22" t="n">
-        <v>-75.773707</v>
+        <v>-75.6925</v>
       </c>
     </row>
     <row r="23">
@@ -3169,48 +3159,48 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SE LA BORDADITA</t>
+          <t>INSTITUTO EDUCATIVO EMPRESARIAL</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>IE AGRICOLA MARSELLA</t>
+          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>266440000525</t>
+          <t>166170001911</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>RESG INDIGENA ALTO MIRA</t>
+          <t>LA BADEA -ANTIGUA  PLAZA DE FERIAS</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3220,44 +3210,49 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>11.61</v>
+        <v>0.14</v>
       </c>
       <c r="Q23" t="n">
-        <v>34.84</v>
+        <v>7.44</v>
       </c>
       <c r="R23" t="n">
-        <v>97.90000000000001</v>
+        <v>17</v>
       </c>
       <c r="S23" t="n">
-        <v>35.5</v>
+        <v>6.8</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 40 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 21 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Calle 9</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3266,10 +3261,10 @@
         </is>
       </c>
       <c r="AC23" t="n">
-        <v>4.928985175</v>
+        <v>4.823055556</v>
       </c>
       <c r="AD23" t="n">
-        <v>-75.77832192</v>
+        <v>-75.69194444</v>
       </c>
     </row>
     <row r="24">
@@ -3288,75 +3283,75 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>SE ALTO CAUCA - SEDE PRINCIPAL</t>
+          <t>POPULAR DIOCESANO</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>IE INSTITUTO AGRICOLA ALTO CAUCA</t>
+          <t>INSTITUCION EDUCATIVA POPULAR DIOCESANO</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>266440000070</t>
+          <t>166170000256</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>CGTO ALTO CAUCA</t>
+          <t>LA BADEA</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>28.62</v>
+        <v>11.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>63.8</v>
+        <v>22.4</v>
       </c>
       <c r="S24" t="n">
-        <v>18.8</v>
+        <v>9</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3366,22 +3361,17 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 2 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Buena Vista</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3390,10 +3380,10 @@
         </is>
       </c>
       <c r="AC24" t="n">
-        <v>4.994828</v>
+        <v>4.824166667</v>
       </c>
       <c r="AD24" t="n">
-        <v>-75.743863</v>
+        <v>-75.69972222</v>
       </c>
     </row>
     <row r="25">
@@ -3412,71 +3402,71 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
         <v>2</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>ANTONIO JOSE DE SUCRE</t>
+          <t>LA BADEA</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>IE INSTITUTO AGRICOLA ALTO CAUCA</t>
+          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>266440800017</t>
+          <t>166170001741</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>CORREGIMIENTO DE ALTO CAUCA</t>
+          <t>BARRIO LA BADEA(ENSEGUIDA A LA IGLESIA)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>34.19</v>
+        <v>9.9</v>
       </c>
       <c r="R25" t="n">
-        <v>63.8</v>
+        <v>22.4</v>
       </c>
       <c r="S25" t="n">
-        <v>18.8</v>
+        <v>9</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -3490,34 +3480,29 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 7 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Buena Vista</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 20 m de esa vía.</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AC25" t="n">
-        <v>4.992762</v>
+        <v>4.82381384716</v>
       </c>
       <c r="AD25" t="n">
-        <v>-75.74432</v>
+        <v>-75.699591841</v>
       </c>
     </row>
     <row r="26">
@@ -3536,11 +3521,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -3552,17 +3537,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>SE EL RAYO</t>
+          <t>SE LAS TAZAS</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>IE INSTITUTO ESTRADA</t>
+          <t>IE AGRICOLA MARSELLA</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>266440000274</t>
+          <t>266440000100</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3577,30 +3562,30 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>VDA EL RAYO</t>
+          <t>VDA LAS TAZAS</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
           <t>Marsella</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Marsella</t>
-        </is>
-      </c>
       <c r="P26" t="n">
-        <v>15.5</v>
+        <v>51.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.460000000000001</v>
+        <v>11.61</v>
       </c>
       <c r="R26" t="n">
-        <v>50.1</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>19.3</v>
+        <v>35.5</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -3624,19 +3609,19 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 22 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 35 m de esa vía.</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC26" t="n">
-        <v>4.909338798</v>
+        <v>4.9022</v>
       </c>
       <c r="AD26" t="n">
-        <v>-75.72299636</v>
+        <v>-75.773707</v>
       </c>
     </row>
     <row r="27">
@@ -3655,11 +3640,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
         <v>2</v>
@@ -3671,17 +3656,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SE SAN ANDRES</t>
+          <t>SE LA BORDADITA</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>IE INSTITUTO ESTRADA</t>
+          <t>IE AGRICOLA MARSELLA</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>266440000045</t>
+          <t>266440000525</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3696,39 +3681,39 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>VDA SAN ANDRES</t>
+          <t>RESG INDIGENA ALTO MIRA</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
           <t>Marsella</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Marsella</t>
-        </is>
-      </c>
       <c r="P27" t="n">
-        <v>9.460000000000001</v>
+        <v>11.61</v>
       </c>
       <c r="Q27" t="n">
-        <v>25.13</v>
+        <v>34.84</v>
       </c>
       <c r="R27" t="n">
-        <v>50.1</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>19.3</v>
+        <v>35.5</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -3743,24 +3728,19 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 318 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>Vía la Bodega</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 40 m de esa vía.</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC27" t="n">
-        <v>4.896608682</v>
+        <v>4.928985175</v>
       </c>
       <c r="AD27" t="n">
-        <v>-75.71433512</v>
+        <v>-75.77832192</v>
       </c>
     </row>
     <row r="28">
@@ -3779,11 +3759,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
@@ -3795,22 +3775,22 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>SE EL ESPAÑOL</t>
+          <t>SE ALTO CAUCA - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>IE INSTITUTO AGRICOLA LA FLORIDA</t>
+          <t>IE INSTITUTO AGRICOLA ALTO CAUCA</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>266682001771</t>
+          <t>266440000070</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Santa Rosa de Cabal</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3820,7 +3800,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>CGTO EL ESPAÑOL</t>
+          <t>CGTO ALTO CAUCA</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3830,49 +3810,49 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Santa Rosa De Cabal</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>42.71</v>
+        <v>28.62</v>
       </c>
       <c r="Q28" t="n">
-        <v>51.83</v>
+        <v>0.96</v>
       </c>
       <c r="R28" t="n">
-        <v>105</v>
+        <v>63.8</v>
       </c>
       <c r="S28" t="n">
-        <v>43.1</v>
+        <v>18.8</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 20 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Al Español</t>
+          <t>Buena Vista</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -3881,10 +3861,10 @@
         </is>
       </c>
       <c r="AC28" t="n">
-        <v>4.932181</v>
+        <v>4.994828</v>
       </c>
       <c r="AD28" t="n">
-        <v>-75.698198</v>
+        <v>-75.743863</v>
       </c>
     </row>
     <row r="29">
@@ -3903,11 +3883,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F29" t="n">
         <v>2</v>
@@ -3919,22 +3899,22 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SE SANTO DOMINGO</t>
+          <t>ANTONIO JOSE DE SUCRE</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>IE INSTITUTO AGROPECUARIO VERACRUZ</t>
+          <t>IE INSTITUTO AGRICOLA ALTO CAUCA</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>266682001372</t>
+          <t>266440800017</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Santa Rosa de Cabal</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3944,7 +3924,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>VDA SANTO DOMINGO</t>
+          <t>CORREGIMIENTO DE ALTO CAUCA</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3954,29 +3934,29 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Santa Rosa De Cabal</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>51.83</v>
+        <v>0.96</v>
       </c>
       <c r="Q29" t="n">
-        <v>10.45</v>
+        <v>34.19</v>
       </c>
       <c r="R29" t="n">
-        <v>105</v>
+        <v>63.8</v>
       </c>
       <c r="S29" t="n">
-        <v>43.1</v>
+        <v>18.8</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -3991,7 +3971,12 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 30 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 7 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Buena Vista</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4000,10 +3985,10 @@
         </is>
       </c>
       <c r="AC29" t="n">
-        <v>4.884255</v>
+        <v>4.992762</v>
       </c>
       <c r="AD29" t="n">
-        <v>-75.634398</v>
+        <v>-75.74432</v>
       </c>
     </row>
     <row r="30">
@@ -4018,15 +4003,15 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
@@ -4038,22 +4023,22 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>SE PEDRO URIBE MEJIA - SEDE PRINCIPAL</t>
+          <t>SE EL RAYO</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>IE INSTITUTO AGRICOLA PEDRO URIBE MEJIA</t>
+          <t>IE INSTITUTO ESTRADA</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>266682000465</t>
+          <t>266440000274</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Santa Rosa de Cabal</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -4063,30 +4048,30 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>VDA EL JAZMIN</t>
+          <t>VDA EL RAYO</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Santa Rosa De Cabal</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Santa Rosa De Cabal</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>22.68</v>
+        <v>15.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>33.82</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="R30" t="n">
-        <v>86.09999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="S30" t="n">
-        <v>37.4</v>
+        <v>26.6</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -4110,24 +4095,19 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 135 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>A Campoalegre</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 22 m de esa vía.</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AC30" t="n">
-        <v>4.914981371</v>
+        <v>4.909338798</v>
       </c>
       <c r="AD30" t="n">
-        <v>-75.61788369</v>
+        <v>-75.72299636</v>
       </c>
     </row>
     <row r="31">
@@ -4142,15 +4122,15 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F31" t="n">
         <v>2</v>
@@ -4162,22 +4142,22 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SE CHARCO HONDO</t>
+          <t>SE SAN ANDRES</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>IE INSTITUTO AGRICOLA PEDRO URIBE MEJIA</t>
+          <t>IE INSTITUTO ESTRADA</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>266682000996</t>
+          <t>266440000045</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Santa Rosa de Cabal</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -4187,30 +4167,30 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>VDA CHARCO HONDO</t>
+          <t>VDA SAN ANDRES</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Santa Rosa De Cabal</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Santa Rosa De Cabal</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>33.82</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="Q31" t="n">
-        <v>29.58</v>
+        <v>51.85</v>
       </c>
       <c r="R31" t="n">
-        <v>86.09999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="S31" t="n">
-        <v>37.4</v>
+        <v>26.6</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -4234,19 +4214,24 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 55 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 318 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Vía la Bodega</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AC31" t="n">
-        <v>4.966084</v>
+        <v>4.896608682</v>
       </c>
       <c r="AD31" t="n">
-        <v>-75.63563000000001</v>
+        <v>-75.71433512</v>
       </c>
     </row>
     <row r="32">
@@ -4261,42 +4246,42 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SE COL DE JESUS</t>
+          <t>RUFINO JOSE CUERVO</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>IE INSTITUTO TECNOLOGICO SANTA ROSA DE CABAL</t>
+          <t>INSTITUCION EDUCATIVA PABLO SEXTO</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>166682001025</t>
+          <t>166170000744</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Santa Rosa de Cabal</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -4306,12 +4291,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>KR 15 12 71</t>
+          <t>KR 18 43 08</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Santa Rosa De Cabal</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -4320,30 +4305,30 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.84</v>
+        <v>2.78</v>
       </c>
       <c r="Q32" t="n">
-        <v>16.02</v>
+        <v>1.17</v>
       </c>
       <c r="R32" t="n">
-        <v>21.2</v>
+        <v>4</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4353,12 +4338,12 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 14 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 18 m de esa vía.</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Carrera 15</t>
+          <t>Carrera 18</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4367,10 +4352,10 @@
         </is>
       </c>
       <c r="AC32" t="n">
-        <v>4.865108</v>
+        <v>4.835834367</v>
       </c>
       <c r="AD32" t="n">
-        <v>-75.62179101</v>
+        <v>-75.66730004</v>
       </c>
     </row>
     <row r="33">
@@ -4389,14 +4374,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4435,7 +4420,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Santa Rosa De Cabal</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -4444,16 +4429,16 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>16.02</v>
+        <v>2.67</v>
       </c>
       <c r="Q33" t="n">
         <v>3.34</v>
       </c>
       <c r="R33" t="n">
-        <v>21.2</v>
+        <v>6</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>2.4</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -4462,7 +4447,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -4513,11 +4498,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
@@ -4529,7 +4514,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA PABLO VI</t>
+          <t>ELADIA MEJIA GONZALEZ</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4539,7 +4524,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>166170000078</t>
+          <t>166170000175</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4554,7 +4539,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>CALLE 44 NO. 23 - 24</t>
+          <t>KR 21 41 80</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4568,16 +4553,16 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.64</v>
+        <v>3.07</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="R34" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="S34" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -4586,12 +4571,12 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -4601,12 +4586,12 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 4 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Carrera 23</t>
+          <t>Carrera 21</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -4615,10 +4600,10 @@
         </is>
       </c>
       <c r="AC34" t="n">
-        <v>4.834166667</v>
+        <v>4.833675657</v>
       </c>
       <c r="AD34" t="n">
-        <v>-75.66527778</v>
+        <v>-75.66815895000001</v>
       </c>
     </row>
     <row r="35">
@@ -4637,11 +4622,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F35" t="n">
         <v>2</v>
@@ -4653,7 +4638,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>RUFINO JOSE CUERVO</t>
+          <t>INSTITUCION EDUCATIVA PABLO VI</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4663,7 +4648,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>166170000744</t>
+          <t>166170000078</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4678,7 +4663,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>KR 18 43 08</t>
+          <t>CALLE 44 NO. 23 - 24</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4692,16 +4677,16 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.17</v>
+        <v>1.8</v>
       </c>
       <c r="R35" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="S35" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -4710,7 +4695,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -4725,12 +4710,12 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 18 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 4 m de esa vía.</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Carrera 18</t>
+          <t>Carrera 23</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -4739,10 +4724,10 @@
         </is>
       </c>
       <c r="AC35" t="n">
-        <v>4.835834367</v>
+        <v>4.834166667</v>
       </c>
       <c r="AD35" t="n">
-        <v>-75.66730004</v>
+        <v>-75.66527778</v>
       </c>
     </row>
     <row r="36">
@@ -4761,11 +4746,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
@@ -4834,7 +4819,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -4885,11 +4870,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F37" t="n">
         <v>2</v>
@@ -4958,7 +4943,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -5009,11 +4994,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
@@ -5025,17 +5010,17 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ELADIA MEJIA GONZALEZ</t>
+          <t>LUIS CARLOS GALAN SARMIENTO</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA PABLO SEXTO</t>
+          <t>INSTITUCION EDUCATIVA POPULAR DIOCESANO</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>166170000175</t>
+          <t>166170001481</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5050,7 +5035,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>KR 21 41 80</t>
+          <t>BARRIO LAS VEGAS</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5064,30 +5049,30 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.07</v>
+        <v>10.53</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.1</v>
+        <v>3.18</v>
       </c>
       <c r="R38" t="n">
-        <v>12.8</v>
+        <v>22.3</v>
       </c>
       <c r="S38" t="n">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -5097,12 +5082,12 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 12 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 13 m de esa vía.</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Carrera 21</t>
+          <t>Carrera 24A</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5111,10 +5096,10 @@
         </is>
       </c>
       <c r="AC38" t="n">
-        <v>4.833675657</v>
+        <v>4.816944444</v>
       </c>
       <c r="AD38" t="n">
-        <v>-75.66815895000001</v>
+        <v>-75.67805556</v>
       </c>
     </row>
     <row r="39">
@@ -5133,11 +5118,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F39" t="n">
         <v>2</v>
@@ -5149,7 +5134,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CENTRO EDUCATIVO LAS VIOLETAS</t>
+          <t>SAN RAFAEL</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5159,7 +5144,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>166170001562</t>
+          <t>166170001937</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5169,12 +5154,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>CL 26A KR 27A -28</t>
+          <t>KR 31 CL 13 SAN RAFAEL</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5188,25 +5173,25 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>4.1</v>
+        <v>3.18</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.66</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="R39" t="n">
-        <v>12.8</v>
+        <v>22.3</v>
       </c>
       <c r="S39" t="n">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -5221,7 +5206,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 36 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5230,10 +5215,10 @@
         </is>
       </c>
       <c r="AC39" t="n">
-        <v>4.825547182</v>
+        <v>4.817222222</v>
       </c>
       <c r="AD39" t="n">
-        <v>-75.66634138000001</v>
+        <v>-75.6725</v>
       </c>
     </row>
     <row r="40">
@@ -5252,11 +5237,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
@@ -5268,7 +5253,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SAN RAFAEL</t>
+          <t>CENTRO EDUCATIVO NARANJALES</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5278,7 +5263,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>166170001937</t>
+          <t>266170000897</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5288,12 +5273,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>KR 31 CL 13 SAN RAFAEL</t>
+          <t>NARANJALES</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5303,29 +5288,29 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>9.470000000000001</v>
+        <v>10.56</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.41</v>
+        <v>5.31</v>
       </c>
       <c r="R40" t="n">
-        <v>22.3</v>
+        <v>21.5</v>
       </c>
       <c r="S40" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -5340,7 +5325,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 56 m de esa vía.</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5349,10 +5334,10 @@
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>4.817222222</v>
+        <v>4.818297979</v>
       </c>
       <c r="AD40" t="n">
-        <v>-75.6725</v>
+        <v>-75.66450766</v>
       </c>
     </row>
     <row r="41">
@@ -5371,11 +5356,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F41" t="n">
         <v>2</v>
@@ -5387,17 +5372,17 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>LUIS CARLOS GALAN SARMIENTO</t>
+          <t>CENTRO EDUCATIVO LAS VIOLETAS</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA POPULAR DIOCESANO</t>
+          <t>INSTITUCION EDUCATIVA FABIO VASQUEZ BOTERO</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>166170001481</t>
+          <t>166170001562</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5407,12 +5392,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>BARRIO LAS VEGAS</t>
+          <t>CL 26A KR 27A -28</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5422,29 +5407,29 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.41</v>
+        <v>5.31</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.460000000000001</v>
+        <v>5.66</v>
       </c>
       <c r="R41" t="n">
-        <v>22.3</v>
+        <v>21.5</v>
       </c>
       <c r="S41" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -5459,12 +5444,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 13 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>Carrera 24A</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 36 m de esa vía.</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -5473,10 +5453,10 @@
         </is>
       </c>
       <c r="AC41" t="n">
-        <v>4.816944444</v>
+        <v>4.825547182</v>
       </c>
       <c r="AD41" t="n">
-        <v>-75.67805556</v>
+        <v>-75.66634138000001</v>
       </c>
     </row>
     <row r="42">
@@ -5491,99 +5471,99 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SE LAS MANGAS</t>
+          <t>FABIO VASQUEZ BOTERO</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>IE INSTITUTO AGROPECUARIO VERACRUZ</t>
+          <t>INSTITUCION EDUCATIVA FABIO VASQUEZ BOTERO</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>266682001101</t>
+          <t>166170001023</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Santa Rosa de Cabal</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>VDA LAS MANGAS</t>
+          <t>LA PRADERA</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>20.9</v>
+        <v>7.14</v>
       </c>
       <c r="Q42" t="n">
-        <v>21.38</v>
+        <v>5.72</v>
       </c>
       <c r="R42" t="n">
-        <v>51.9</v>
+        <v>19.5</v>
       </c>
       <c r="S42" t="n">
-        <v>20.4</v>
+        <v>7.4</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 81 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 16 m de esa vía.</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -5592,10 +5572,10 @@
         </is>
       </c>
       <c r="AC42" t="n">
-        <v>4.783364</v>
+        <v>4.830277778</v>
       </c>
       <c r="AD42" t="n">
-        <v>-75.641834</v>
+        <v>-75.6825</v>
       </c>
     </row>
     <row r="43">
@@ -5610,15 +5590,15 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F43" t="n">
         <v>2</v>
@@ -5630,17 +5610,17 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CENTRO EDUCATIVO NARANJALES</t>
+          <t>BASICO OTUN</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA FABIO VASQUEZ BOTERO</t>
+          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>266170000897</t>
+          <t>166170000329</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -5650,44 +5630,44 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>NARANJALES</t>
+          <t>BARRIO SAN JUDAS EL BALSO</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>21.38</v>
+        <v>5.72</v>
       </c>
       <c r="Q43" t="n">
-        <v>9.65</v>
+        <v>6.63</v>
       </c>
       <c r="R43" t="n">
-        <v>51.9</v>
+        <v>19.5</v>
       </c>
       <c r="S43" t="n">
-        <v>20.4</v>
+        <v>7.4</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -5702,7 +5682,12 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 56 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 7 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Carrera 19</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -5711,16 +5696,16 @@
         </is>
       </c>
       <c r="AC43" t="n">
-        <v>4.818297979</v>
+        <v>4.816666667</v>
       </c>
       <c r="AD43" t="n">
-        <v>-75.66450766</v>
+        <v>-75.68333333</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5729,42 +5714,42 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>FABIO VASQUEZ BOTERO</t>
+          <t>LAS PALMAS</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA FABIO VASQUEZ BOTERO</t>
+          <t>INSTITUCION EDUCATIVA JESUS DE LA BUENA ESPERANZA</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>166170001023</t>
+          <t>166001002754</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -5774,12 +5759,12 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>LA PRADERA</t>
+          <t>AV DEL RIO NO 43 - 26</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -5788,16 +5773,16 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>7.14</v>
+        <v>6.25</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.72</v>
+        <v>3.32</v>
       </c>
       <c r="R44" t="n">
-        <v>19.5</v>
+        <v>15.2</v>
       </c>
       <c r="S44" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -5821,7 +5806,12 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 16 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Carrera 5</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -5830,16 +5820,16 @@
         </is>
       </c>
       <c r="AC44" t="n">
-        <v>4.830277778</v>
+        <v>4.818122534</v>
       </c>
       <c r="AD44" t="n">
-        <v>-75.6825</v>
+        <v>-75.71553498</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5848,42 +5838,42 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
         <v>2</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>BASICO OTUN</t>
+          <t>JESUS DE LA BUENA ESPERANZA</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
+          <t>INSTITUCION EDUCATIVA JESUS DE LA BUENA ESPERANZA</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>166170000329</t>
+          <t>166001000450</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5893,12 +5883,12 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>BARRIO SAN JUDAS EL BALSO</t>
+          <t>CR 3 NO 34 - 46</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -5907,25 +5897,25 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>5.72</v>
+        <v>3.32</v>
       </c>
       <c r="Q45" t="n">
-        <v>6.63</v>
+        <v>5.64</v>
       </c>
       <c r="R45" t="n">
-        <v>19.5</v>
+        <v>15.2</v>
       </c>
       <c r="S45" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -5940,12 +5930,12 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 7 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Carrera 19</t>
+          <t>Carrera 2 Bis</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -5954,10 +5944,10 @@
         </is>
       </c>
       <c r="AC45" t="n">
-        <v>4.816666667</v>
+        <v>4.819868522229693</v>
       </c>
       <c r="AD45" t="n">
-        <v>-75.68333333</v>
+        <v>-75.70621902228969</v>
       </c>
     </row>
     <row r="46">
@@ -5976,48 +5966,48 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SE AGUA SALADA</t>
+          <t>INSTITUCION EDUCATIVA SAN FERNANDO</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>IE SAUSAGUA</t>
+          <t>INSTITUCION EDUCATIVA SAN FERNANDO</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>266594000544</t>
+          <t>166001000344</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Quinchía</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>VDA AGUA SALADA</t>
+          <t>IND CLL 70 NO 23-20 SAN FERNANDO CUBA</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6027,34 +6017,34 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Quinchia</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>88.73999999999999</v>
+        <v>13.53</v>
       </c>
       <c r="Q46" t="n">
-        <v>29.34</v>
+        <v>1.83</v>
       </c>
       <c r="R46" t="n">
-        <v>118.1</v>
+        <v>31.7</v>
       </c>
       <c r="S46" t="n">
-        <v>92.59999999999999</v>
+        <v>14.1</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -6064,12 +6054,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 19 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>Via Irra a Quinchia</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 5 m de esa vía.</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -6078,10 +6063,10 @@
         </is>
       </c>
       <c r="AC46" t="n">
-        <v>5.29672</v>
+        <v>4.805705</v>
       </c>
       <c r="AD46" t="n">
-        <v>-75.66537599999999</v>
+        <v>-75.73962299999999</v>
       </c>
     </row>
     <row r="47">
@@ -6107,88 +6092,93 @@
         <v>2</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SE ENCENILLAL</t>
+          <t>INST EDUCATIVA JESUS MARIA ORMAZA</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>IE NUCLEO ESCOLAR RURAL</t>
+          <t>INSTITUCION EDUCATIVA JESUS MARIA ORMAZA</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>266594000234</t>
+          <t>166001000646</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Quinchía</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>VDA ENCENILLAL</t>
+          <t>CL 70 22 00 BR CUBA</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Quinchia</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Quinchia</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>10.14</v>
+        <v>1.83</v>
       </c>
       <c r="Q47" t="n">
-        <v>10.98</v>
+        <v>16.37</v>
       </c>
       <c r="R47" t="n">
-        <v>21.1</v>
+        <v>31.7</v>
       </c>
       <c r="S47" t="n">
-        <v>6.5</v>
+        <v>14.1</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 199 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 35 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Calle 75</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6197,10 +6187,10 @@
         </is>
       </c>
       <c r="AC47" t="n">
-        <v>5.328055556</v>
+        <v>4.803217136</v>
       </c>
       <c r="AD47" t="n">
-        <v>-75.74833332999999</v>
+        <v>-75.74425404</v>
       </c>
     </row>
     <row r="48">
@@ -6235,22 +6225,22 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SE NUESTRA SEÑORA DE LA CEIBA</t>
+          <t>SE NUESTRA SEÑORA DEL ROSARIO - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>IE NUCLEO ESCOLAR RURAL</t>
+          <t>CE NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>266594000340</t>
+          <t>266687000331</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Quinchía</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -6260,30 +6250,30 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>VDA LA CEIBA</t>
+          <t>CGTO PERALONSO</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Quinchia</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Quinchia</t>
+          <t>Apia</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>12.46</v>
+        <v>90.97</v>
       </c>
       <c r="Q48" t="n">
-        <v>13.76</v>
+        <v>58.58</v>
       </c>
       <c r="R48" t="n">
-        <v>26.2</v>
+        <v>149.6</v>
       </c>
       <c r="S48" t="n">
-        <v>13.1</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -6297,29 +6287,29 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 36 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="AC48" t="n">
-        <v>5.370566</v>
+        <v>4.99014911697</v>
       </c>
       <c r="AD48" t="n">
-        <v>-75.74896699999999</v>
+        <v>-75.9242208477</v>
       </c>
     </row>
     <row r="49">
@@ -6354,22 +6344,22 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SE EL TRIUNFO</t>
+          <t>ESCUELA PATIO BONITO</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>IE AGROPECUARIO NARANJAL</t>
+          <t>IE PATIO BONITO</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>266594000382</t>
+          <t>266383800005</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Quinchía</t>
+          <t>La Celia</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -6379,54 +6369,54 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>VDA GUERRERO</t>
+          <t>VDA PATIO BONITO</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Quinchia</t>
+          <t>Apia</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Quinchia</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>34.41</v>
+        <v>48.3</v>
       </c>
       <c r="Q49" t="n">
-        <v>35.17</v>
+        <v>1.21</v>
       </c>
       <c r="R49" t="n">
-        <v>69.59999999999999</v>
+        <v>101.4</v>
       </c>
       <c r="S49" t="n">
-        <v>32.6</v>
+        <v>42.5</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 8 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 13 m de esa vía.</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -6435,10 +6425,10 @@
         </is>
       </c>
       <c r="AC49" t="n">
-        <v>5.283929</v>
+        <v>4.996865</v>
       </c>
       <c r="AD49" t="n">
-        <v>-75.69113299999999</v>
+        <v>-75.980124</v>
       </c>
     </row>
     <row r="50">
@@ -6457,14 +6447,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -6473,69 +6463,69 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SE INSTITUTO GUATICA - SEDE PRINCIPAL</t>
+          <t>SE PATIO BONITO - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>IE INSTITUTO GUATICA</t>
+          <t>IE PATIO BONITO</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>166318000030</t>
+          <t>266383000050</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Guática</t>
+          <t>La Celia</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>IND BR GAMONRRA</t>
+          <t>VDA PATIO BONITO</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Quinchia</t>
+          <t>Apia</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Mistrato</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>30.5</v>
+        <v>1.21</v>
       </c>
       <c r="Q50" t="n">
-        <v>13.31</v>
+        <v>51.87</v>
       </c>
       <c r="R50" t="n">
-        <v>80.59999999999999</v>
+        <v>101.4</v>
       </c>
       <c r="S50" t="n">
-        <v>43.3</v>
+        <v>42.5</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -6545,12 +6535,12 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 13 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 28 m de esa vía.</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>Calle 12</t>
+          <t>La Celia-Balboa</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -6559,10 +6549,10 @@
         </is>
       </c>
       <c r="AC50" t="n">
-        <v>5.318849336</v>
+        <v>4.993201</v>
       </c>
       <c r="AD50" t="n">
-        <v>-75.80047681000001</v>
+        <v>-75.981357</v>
       </c>
     </row>
     <row r="51">
@@ -6588,7 +6578,7 @@
         <v>5</v>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -6597,22 +6587,22 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL CARMEN</t>
+          <t>SE LA BAMBA</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>IE SANTA ANA</t>
+          <t>IE MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>266318800006</t>
+          <t>266687000030</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Guática</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -6622,39 +6612,39 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>CORREGIMIENTO SANTA ANA</t>
+          <t>VDA LA BAMBA</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Quinchia</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Mistrato</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>13.31</v>
+        <v>34.86</v>
       </c>
       <c r="Q51" t="n">
-        <v>36.83</v>
+        <v>26.5</v>
       </c>
       <c r="R51" t="n">
-        <v>80.59999999999999</v>
+        <v>61.4</v>
       </c>
       <c r="S51" t="n">
-        <v>43.3</v>
+        <v>17.5</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
@@ -6669,12 +6659,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 4 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>Carrera 4</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 121 m de esa vía.</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -6683,10 +6668,10 @@
         </is>
       </c>
       <c r="AC51" t="n">
-        <v>5.30751835</v>
+        <v>5.063056</v>
       </c>
       <c r="AD51" t="n">
-        <v>-75.82041798</v>
+        <v>-75.99972200000001</v>
       </c>
     </row>
     <row r="52">
@@ -6721,55 +6706,55 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SE ALTO PUEBLO RICO</t>
+          <t>SE INSTITUTO SANTUARIO - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>IE INSTITUTO MISTRATO</t>
+          <t>INSTITUCIÓN EDUCATIVA INSTITUTO SANTUARIO</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>266456000100</t>
+          <t>166687000256</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Mistrató</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>VDA ALTO PUEBLO RICO</t>
+          <t>CL 6 7 17</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Mistrato</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Mistrato</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>6.84</v>
+        <v>0.1</v>
       </c>
       <c r="Q52" t="n">
-        <v>9.26</v>
+        <v>49.67</v>
       </c>
       <c r="R52" t="n">
-        <v>16.1</v>
+        <v>101.6</v>
       </c>
       <c r="S52" t="n">
-        <v>7.6</v>
+        <v>44</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -6783,7 +6768,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -6793,7 +6778,12 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 11 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Carrera 7</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -6802,10 +6792,10 @@
         </is>
       </c>
       <c r="AC52" t="n">
-        <v>5.279785869</v>
+        <v>5.072806629</v>
       </c>
       <c r="AD52" t="n">
-        <v>-75.89025909</v>
+        <v>-75.96351957</v>
       </c>
     </row>
     <row r="53">
@@ -6820,19 +6810,19 @@
         </is>
       </c>
       <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6</v>
+      </c>
+      <c r="F53" t="n">
         <v>2</v>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>lunes</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>7</v>
-      </c>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>Risaralda</t>
@@ -6840,55 +6830,55 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SE EL TIGRE</t>
+          <t>SE MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>IE SANTA EMILIA</t>
+          <t>IE LICEO DE OCCIDENTE</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>266088000366</t>
+          <t>166383000195</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Belén de Umbría</t>
+          <t>La Celia</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>VDA EL TIGRE</t>
+          <t>CL 5 2 69</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Mistrato</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Belen De Umbria</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>53.11</v>
+        <v>49.67</v>
       </c>
       <c r="Q53" t="n">
-        <v>32.26</v>
+        <v>51.88</v>
       </c>
       <c r="R53" t="n">
-        <v>85.40000000000001</v>
+        <v>101.6</v>
       </c>
       <c r="S53" t="n">
-        <v>35.1</v>
+        <v>44</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -6902,17 +6892,22 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>camino destapado</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 8 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 18 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>Calle 5</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
@@ -6921,10 +6916,10 @@
         </is>
       </c>
       <c r="AC53" t="n">
-        <v>5.174781</v>
+        <v>5.00296197</v>
       </c>
       <c r="AD53" t="n">
-        <v>-75.89761</v>
+        <v>-76.00271345</v>
       </c>
     </row>
     <row r="54">
@@ -6943,11 +6938,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F54" t="n">
         <v>1</v>
@@ -6959,22 +6954,22 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SE COLEGIO TECNICO AGROPECUARIO TAPARCAL - SEDE PRINCIPAL</t>
+          <t>SE TAMBORES - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>IE COLEGIO TECNICO AGROPECUARIO TAPARCAL</t>
+          <t>IE TAMBORES</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>266088000528</t>
+          <t>266075000022</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Belén de Umbría</t>
+          <t>Balboa</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -6984,54 +6979,54 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>CGTO TAPARCAL</t>
+          <t>VDA TAMBORES</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Belen De Umbria</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Belen De Umbria</t>
+          <t>Cartago</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>14.18</v>
+        <v>83.7</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.26</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="R54" t="n">
-        <v>31.3</v>
+        <v>154</v>
       </c>
       <c r="S54" t="n">
-        <v>10.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>Colapso total</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 44 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 1 m de esa vía.</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
@@ -7040,10 +7035,10 @@
         </is>
       </c>
       <c r="AC54" t="n">
-        <v>5.165871128</v>
+        <v>4.885083</v>
       </c>
       <c r="AD54" t="n">
-        <v>-75.86350014999999</v>
+        <v>-75.97331699999999</v>
       </c>
     </row>
     <row r="55">
@@ -7069,73 +7064,73 @@
         <v>8</v>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SE TAPARCAL</t>
+          <t>INSTITUCION EDUCATIVA LUIS CARLOS GONZALEZ MEJIA</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>IE COLEGIO TECNICO AGROPECUARIO TAPARCAL</t>
+          <t>INSTITUCION EDUCATIVA LUIS CARLOS GONZALEZ MEJIA</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>266088000111</t>
+          <t>166001003505</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Belén de Umbría</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>CGTO TAPARCAL</t>
+          <t>KR 17 82 103</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Belen De Umbria</t>
+          <t>Cartago</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Belen De Umbria</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0.26</v>
+        <v>32.55</v>
       </c>
       <c r="Q55" t="n">
-        <v>16.89</v>
+        <v>17.05</v>
       </c>
       <c r="R55" t="n">
-        <v>31.3</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S55" t="n">
-        <v>10.5</v>
+        <v>55.7</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
@@ -7150,7 +7145,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 9 m de esa vía.</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -7159,10 +7154,10 @@
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>5.165833</v>
+        <v>4.806935893</v>
       </c>
       <c r="AD55" t="n">
-        <v>-75.864133</v>
+        <v>-75.74500842</v>
       </c>
     </row>
     <row r="56">
@@ -7181,38 +7176,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SE EL ABEJERO</t>
+          <t>EL PLACER</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>IE SANTA EMILIA</t>
+          <t>INSTITUCION EDUCATIVA COMBIA</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>266088000315</t>
+          <t>266001001698</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Belén de Umbría</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -7222,34 +7217,34 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>VDA EL ABEJERO</t>
+          <t>CRUCERO DE COMBIA</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Belen De Umbria</t>
+          <t>Cartago</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Apia</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>40.29</v>
+        <v>17.05</v>
       </c>
       <c r="Q56" t="n">
-        <v>76.54000000000001</v>
+        <v>48.99</v>
       </c>
       <c r="R56" t="n">
-        <v>116.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S56" t="n">
-        <v>35.5</v>
+        <v>55.7</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -7259,7 +7254,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -7269,7 +7264,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>La vía de entrada es otra según OpenStreetMap (clase «track_grade3»). La sede queda a 293 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 147 m de esa vía.</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -7278,10 +7273,10 @@
         </is>
       </c>
       <c r="AC56" t="n">
-        <v>5.151535</v>
+        <v>4.819139218</v>
       </c>
       <c r="AD56" t="n">
-        <v>-75.904819</v>
+        <v>-75.76076208000001</v>
       </c>
     </row>
     <row r="57">
@@ -7300,11 +7295,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -7316,22 +7311,22 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>SE CAJA DE ORO</t>
+          <t>SE EL ESPAÑOL</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>IE INTERCULTURAL DOKABU</t>
+          <t>IE INSTITUTO AGRICOLA LA FLORIDA</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>266572001237</t>
+          <t>266682001771</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Santa Rosa de Cabal</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -7341,66 +7336,71 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>VDA CAJA DE ORO</t>
+          <t>CGTO EL ESPAÑOL</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Apia</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Santa Rosa De Cabal</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>167.98</v>
+        <v>42.71</v>
       </c>
       <c r="Q57" t="n">
-        <v>120.41</v>
+        <v>51.83</v>
       </c>
       <c r="R57" t="n">
-        <v>288.4</v>
+        <v>105</v>
       </c>
       <c r="S57" t="n">
-        <v>90.5</v>
+        <v>43.1</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>camino destapado</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 240 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 20 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>Al Español</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC57" t="n">
-        <v>5.331280525</v>
+        <v>4.932181</v>
       </c>
       <c r="AD57" t="n">
-        <v>-75.9852455</v>
+        <v>-75.698198</v>
       </c>
     </row>
     <row r="58">
@@ -7419,14 +7419,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -7435,96 +7435,91 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SE SAN PABLO - SEDE PRINCIPAL</t>
+          <t>SE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>IE SAN PABLO</t>
+          <t>IE INSTITUTO AGROPECUARIO VERACRUZ</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>166572000015</t>
+          <t>266682001372</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Santa Rosa de Cabal</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>KR 5 4 51</t>
+          <t>VDA SANTO DOMINGO</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Santa Rosa De Cabal</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.82</v>
+        <v>51.83</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.42</v>
+        <v>10.45</v>
       </c>
       <c r="R58" t="n">
-        <v>3.2</v>
+        <v>105</v>
       </c>
       <c r="S58" t="n">
-        <v>0.8</v>
+        <v>43.1</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>Calle 3 A</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 30 m de esa vía.</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC58" t="n">
-        <v>5.21916175028</v>
+        <v>4.884255</v>
       </c>
       <c r="AD58" t="n">
-        <v>-76.0331189595</v>
+        <v>-75.634398</v>
       </c>
     </row>
     <row r="59">
@@ -7543,11 +7538,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F59" t="n">
         <v>1</v>
@@ -7559,55 +7554,55 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>SE SAN PEDRO CLAVER</t>
+          <t>SE COL DE JESUS</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>IE AGROAMBIENTAL PIO XII</t>
+          <t>IE INSTITUTO TECNOLOGICO SANTA ROSA DE CABAL</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>266572000141</t>
+          <t>166682001025</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Santa Rosa de Cabal</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>CGTO SANTA CECILIA</t>
+          <t>KR 15 12 71</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Santa Rosa De Cabal</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Santa Rosa De Cabal</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>48.16</v>
+        <v>1.84</v>
       </c>
       <c r="Q59" t="n">
-        <v>12.95</v>
+        <v>1.35</v>
       </c>
       <c r="R59" t="n">
-        <v>107.9</v>
+        <v>3.2</v>
       </c>
       <c r="S59" t="n">
-        <v>67</v>
+        <v>0.8</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -7621,7 +7616,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -7631,12 +7626,12 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 20 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 14 m de esa vía.</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>Calle 3</t>
+          <t>Carrera 15</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
@@ -7645,10 +7640,10 @@
         </is>
       </c>
       <c r="AC59" t="n">
-        <v>5.340317929</v>
+        <v>4.865108</v>
       </c>
       <c r="AD59" t="n">
-        <v>-76.14533188999999</v>
+        <v>-75.62179101</v>
       </c>
     </row>
     <row r="60">
@@ -7667,14 +7662,14 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7683,22 +7678,22 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>ESCUELA NUEVA AGÜITA</t>
+          <t>SE PEDRO URIBE MEJIA - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>IE INTERCULTURAL DOKABU</t>
+          <t>IE INSTITUTO AGRICOLA PEDRO URIBE MEJIA</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>266572800032</t>
+          <t>266682000465</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Santa Rosa de Cabal</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -7708,39 +7703,39 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>VDA AGUITA</t>
+          <t>VDA EL JAZMIN</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Santa Rosa De Cabal</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>12.95</v>
+        <v>22.68</v>
       </c>
       <c r="Q60" t="n">
-        <v>46.77</v>
+        <v>33.82</v>
       </c>
       <c r="R60" t="n">
-        <v>107.9</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="S60" t="n">
-        <v>67</v>
+        <v>44.4</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -7755,7 +7750,12 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 58 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 135 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>A Campoalegre</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
@@ -7764,10 +7764,10 @@
         </is>
       </c>
       <c r="AC60" t="n">
-        <v>5.366205</v>
+        <v>4.914981371</v>
       </c>
       <c r="AD60" t="n">
-        <v>-76.10596200000001</v>
+        <v>-75.61788369</v>
       </c>
     </row>
     <row r="61">
@@ -7782,18 +7782,18 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -7802,22 +7802,22 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SE BICHUBARA</t>
+          <t>SE CHARCO HONDO</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>IE DACHI DADA KERA</t>
+          <t>IE INSTITUTO AGRICOLA PEDRO URIBE MEJIA</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>466572001121</t>
+          <t>266682000996</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Santa Rosa de Cabal</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -7827,66 +7827,66 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>VDA BICHUBARA</t>
+          <t>VDA CHARCO HONDO</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Santa Rosa De Cabal</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>50.02</v>
+        <v>33.82</v>
       </c>
       <c r="Q61" t="n">
-        <v>4.82</v>
+        <v>36.9</v>
       </c>
       <c r="R61" t="n">
-        <v>109.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="S61" t="n">
-        <v>74.09999999999999</v>
+        <v>44.4</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «primary»). La sede queda a 3687 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 55 m de esa vía.</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC61" t="n">
-        <v>5.312197</v>
+        <v>4.966084</v>
       </c>
       <c r="AD61" t="n">
-        <v>-76.166676</v>
+        <v>-75.63563000000001</v>
       </c>
     </row>
     <row r="62">
@@ -7901,18 +7901,18 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7921,22 +7921,22 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>SE SIKUEDO</t>
+          <t>SE LAS MANGAS</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>IE DACHI DADA KERA</t>
+          <t>IE INSTITUTO AGROPECUARIO VERACRUZ</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>266572000940</t>
+          <t>266682001101</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Santa Rosa de Cabal</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -7946,54 +7946,54 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>VDA SIKUEDO</t>
+          <t>VDA LAS MANGAS</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>4.82</v>
+        <v>28.88</v>
       </c>
       <c r="Q62" t="n">
-        <v>54.39</v>
+        <v>23.97</v>
       </c>
       <c r="R62" t="n">
-        <v>109.2</v>
+        <v>57.4</v>
       </c>
       <c r="S62" t="n">
-        <v>74.09999999999999</v>
+        <v>22.4</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «primary»). La sede queda a 281 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 81 m de esa vía.</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="AC62" t="n">
-        <v>5.355261</v>
+        <v>4.783364</v>
       </c>
       <c r="AD62" t="n">
-        <v>-76.177787</v>
+        <v>-75.641834</v>
       </c>
     </row>
     <row r="63">
@@ -8020,89 +8020,89 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>SE OSKORDO</t>
+          <t>PROVIDENCIA</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>IE INTERCULTURAL DOKABU</t>
+          <t>COMPLEJO EDUCATIVO LA JULITA</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>266572001326</t>
+          <t>166001004978</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>VDA OSKORDO</t>
+          <t>KR 20 23 15</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Pueblo Rico</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Apia</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>104.73</v>
+        <v>23.97</v>
       </c>
       <c r="Q63" t="n">
-        <v>119.27</v>
+        <v>4.56</v>
       </c>
       <c r="R63" t="n">
-        <v>224</v>
+        <v>57.4</v>
       </c>
       <c r="S63" t="n">
-        <v>79.3</v>
+        <v>22.4</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Sin afectación</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -8112,7 +8112,12 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>La vía de entrada es otra según OpenStreetMap (clase «track_grade3»). La sede queda a 5445 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 3 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>Carrera 20</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
@@ -8121,10 +8126,10 @@
         </is>
       </c>
       <c r="AC63" t="n">
-        <v>5.275278</v>
+        <v>4.803937</v>
       </c>
       <c r="AD63" t="n">
-        <v>-76.162778</v>
+        <v>-75.699062</v>
       </c>
     </row>
   </sheetData>
@@ -8277,16 +8282,16 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>12.6</v>
+        <v>23.1</v>
       </c>
       <c r="E10" t="n">
-        <v>349</v>
+        <v>649</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G10" t="n">
         <v>14</v>
@@ -8299,22 +8304,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>9.699999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="E11" t="n">
-        <v>225</v>
+        <v>129</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -8324,22 +8329,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>21.6</v>
+        <v>16.2</v>
       </c>
       <c r="E12" t="n">
-        <v>588</v>
+        <v>447</v>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/public/datos/plan_cuadrillas_risaralda.xlsx
+++ b/public/datos/plan_cuadrillas_risaralda.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plan'!$A$1:$AD$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plan'!$A$1:$AI$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD63"/>
+  <dimension ref="A1:AI63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,55 +550,80 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Concepto (tablero del Valle)</t>
+          <t>Especialidad de la visita</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>Concepto técnico (tablero del Valle)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>Dictamen</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Estado (MEN)</t>
-        </is>
-      </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>Restringido en la ficha</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Reporte rector al MEN</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>Nivel de afectación (MEN)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Reporte rector a la Secretaría del Valle</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Reporte FFIE 2026</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Marca en el mapa</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Tipo de vía</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Acceso</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Por qué</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Vía de acceso</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Coordenada en revisión</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Latitud</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Longitud</t>
         </is>
@@ -686,45 +711,45 @@
       <c r="S2" t="n">
         <v>64.3</v>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Carrera 7</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC2" t="n">
+      <c r="AH2" t="n">
         <v>5.104722222</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AI2" t="n">
         <v>-75.9425</v>
       </c>
     </row>
@@ -810,40 +835,40 @@
       <c r="S3" t="n">
         <v>90.5</v>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>camino destapado</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 240 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="AC3" t="n">
+      <c r="AH3" t="n">
         <v>5.331280525</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AI3" t="n">
         <v>-75.9852455</v>
       </c>
     </row>
@@ -929,45 +954,45 @@
       <c r="S4" t="n">
         <v>0.8</v>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>Calle 3 A</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="AC4" t="n">
+      <c r="AH4" t="n">
         <v>5.21916175028</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AI4" t="n">
         <v>-76.0331189595</v>
       </c>
     </row>
@@ -1053,45 +1078,45 @@
       <c r="S5" t="n">
         <v>67</v>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>rojo</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 20 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>Calle 3</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC5" t="n">
+      <c r="AH5" t="n">
         <v>5.340317929</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AI5" t="n">
         <v>-76.14533188999999</v>
       </c>
     </row>
@@ -1177,40 +1202,40 @@
       <c r="S6" t="n">
         <v>67</v>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 58 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC6" t="n">
+      <c r="AH6" t="n">
         <v>5.366205</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AI6" t="n">
         <v>-76.10596200000001</v>
       </c>
     </row>
@@ -1296,40 +1321,40 @@
       <c r="S7" t="n">
         <v>74.09999999999999</v>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «primary»). La sede queda a 3687 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="AC7" t="n">
+      <c r="AH7" t="n">
         <v>5.312197</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AI7" t="n">
         <v>-76.166676</v>
       </c>
     </row>
@@ -1415,40 +1440,40 @@
       <c r="S8" t="n">
         <v>74.09999999999999</v>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «primary»). La sede queda a 281 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC8" t="n">
+      <c r="AH8" t="n">
         <v>5.355261</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AI8" t="n">
         <v>-76.177787</v>
       </c>
     </row>
@@ -1534,40 +1559,40 @@
       <c r="S9" t="n">
         <v>79.3</v>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X9" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>otra</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>La vía de entrada es otra según OpenStreetMap (clase «track_grade3»). La sede queda a 5445 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC9" t="n">
+      <c r="AH9" t="n">
         <v>5.275278</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AI9" t="n">
         <v>-76.162778</v>
       </c>
     </row>
@@ -1653,45 +1678,45 @@
       <c r="S10" t="n">
         <v>35.5</v>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X10" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 75 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>Mateguadua-Apia</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="AC10" t="n">
+      <c r="AH10" t="n">
         <v>5.11777777778</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AI10" t="n">
         <v>-75.90472222219999</v>
       </c>
     </row>
@@ -1777,40 +1802,40 @@
       <c r="S11" t="n">
         <v>35.5</v>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>otra</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>La vía de entrada es otra según OpenStreetMap (clase «track_grade3»). La sede queda a 293 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AG11" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC11" t="n">
+      <c r="AH11" t="n">
         <v>5.151535</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AI11" t="n">
         <v>-75.904819</v>
       </c>
     </row>
@@ -1896,40 +1921,45 @@
       <c r="S12" t="n">
         <v>10.5</v>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>Colapso total</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>rojo</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 44 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC12" t="n">
+      <c r="AH12" t="n">
         <v>5.165871128</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AI12" t="n">
         <v>-75.86350014999999</v>
       </c>
     </row>
@@ -2015,40 +2045,40 @@
       <c r="S13" t="n">
         <v>10.5</v>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AG13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC13" t="n">
+      <c r="AH13" t="n">
         <v>5.165833</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AI13" t="n">
         <v>-75.864133</v>
       </c>
     </row>
@@ -2134,40 +2164,40 @@
       <c r="S14" t="n">
         <v>42.4</v>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>camino destapado</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AG14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC14" t="n">
+      <c r="AH14" t="n">
         <v>5.174781</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AI14" t="n">
         <v>-75.89761</v>
       </c>
     </row>
@@ -2253,40 +2283,40 @@
       <c r="S15" t="n">
         <v>42.4</v>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X15" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 11 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC15" t="n">
+      <c r="AH15" t="n">
         <v>5.279785869</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AI15" t="n">
         <v>-75.89025909</v>
       </c>
     </row>
@@ -2372,45 +2402,45 @@
       <c r="S16" t="n">
         <v>43.4</v>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 4 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AF16" t="inlineStr">
         <is>
           <t>Carrera 4</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC16" t="n">
+      <c r="AH16" t="n">
         <v>5.30751835</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AI16" t="n">
         <v>-75.82041798</v>
       </c>
     </row>
@@ -2496,45 +2526,50 @@
       <c r="S17" t="n">
         <v>43.4</v>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>rojo</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 13 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AF17" t="inlineStr">
         <is>
           <t>Calle 12</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC17" t="n">
+      <c r="AH17" t="n">
         <v>5.318849336</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AI17" t="n">
         <v>-75.80047681000001</v>
       </c>
     </row>
@@ -2620,40 +2655,40 @@
       <c r="S18" t="n">
         <v>19.2</v>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X18" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 199 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC18" t="n">
+      <c r="AH18" t="n">
         <v>5.328055556</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AI18" t="n">
         <v>-75.74833332999999</v>
       </c>
     </row>
@@ -2739,40 +2774,40 @@
       <c r="S19" t="n">
         <v>19.2</v>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X19" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 36 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC19" t="n">
+      <c r="AH19" t="n">
         <v>5.370566</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AI19" t="n">
         <v>-75.74896699999999</v>
       </c>
     </row>
@@ -2858,40 +2893,40 @@
       <c r="S20" t="n">
         <v>32.6</v>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AG20" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC20" t="n">
+      <c r="AH20" t="n">
         <v>5.283929</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AI20" t="n">
         <v>-75.69113299999999</v>
       </c>
     </row>
@@ -2977,45 +3012,45 @@
       <c r="S21" t="n">
         <v>89.7</v>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 19 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AF21" t="inlineStr">
         <is>
           <t>Via Irra a Quinchia</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AG21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC21" t="n">
+      <c r="AH21" t="n">
         <v>5.29672</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AI21" t="n">
         <v>-75.66537599999999</v>
       </c>
     </row>
@@ -3101,45 +3136,45 @@
       <c r="S22" t="n">
         <v>6.8</v>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 5 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AF22" t="inlineStr">
         <is>
           <t>Calle 9</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC22" t="n">
+      <c r="AH22" t="n">
         <v>4.823055556</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AI22" t="n">
         <v>-75.6925</v>
       </c>
     </row>
@@ -3225,45 +3260,45 @@
       <c r="S23" t="n">
         <v>6.8</v>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 21 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AF23" t="inlineStr">
         <is>
           <t>Calle 9</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AG23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC23" t="n">
+      <c r="AH23" t="n">
         <v>4.823055556</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AI23" t="n">
         <v>-75.69194444</v>
       </c>
     </row>
@@ -3349,40 +3384,45 @@
       <c r="S24" t="n">
         <v>9</v>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>rojo</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AG24" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC24" t="n">
+      <c r="AH24" t="n">
         <v>4.824166667</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AI24" t="n">
         <v>-75.69972222</v>
       </c>
     </row>
@@ -3468,40 +3508,40 @@
       <c r="S25" t="n">
         <v>9</v>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 20 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AG25" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="AC25" t="n">
+      <c r="AH25" t="n">
         <v>4.82381384716</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AI25" t="n">
         <v>-75.699591841</v>
       </c>
     </row>
@@ -3587,40 +3627,40 @@
       <c r="S26" t="n">
         <v>35.5</v>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X26" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 35 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC26" t="n">
+      <c r="AH26" t="n">
         <v>4.9022</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AI26" t="n">
         <v>-75.773707</v>
       </c>
     </row>
@@ -3706,40 +3746,40 @@
       <c r="S27" t="n">
         <v>35.5</v>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 40 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC27" t="n">
+      <c r="AH27" t="n">
         <v>4.928985175</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AI27" t="n">
         <v>-75.77832192</v>
       </c>
     </row>
@@ -3825,45 +3865,50 @@
       <c r="S28" t="n">
         <v>18.8</v>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>rojo</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AF28" t="inlineStr">
         <is>
           <t>Buena Vista</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC28" t="n">
+      <c r="AH28" t="n">
         <v>4.994828</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AI28" t="n">
         <v>-75.743863</v>
       </c>
     </row>
@@ -3949,45 +3994,45 @@
       <c r="S29" t="n">
         <v>18.8</v>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 7 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AF29" t="inlineStr">
         <is>
           <t>Buena Vista</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AG29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC29" t="n">
+      <c r="AH29" t="n">
         <v>4.992762</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AI29" t="n">
         <v>-75.74432</v>
       </c>
     </row>
@@ -4073,40 +4118,40 @@
       <c r="S30" t="n">
         <v>26.6</v>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X30" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 22 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AG30" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="AC30" t="n">
+      <c r="AH30" t="n">
         <v>4.909338798</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AI30" t="n">
         <v>-75.72299636</v>
       </c>
     </row>
@@ -4192,45 +4237,45 @@
       <c r="S31" t="n">
         <v>26.6</v>
       </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X31" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 318 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AF31" t="inlineStr">
         <is>
           <t>Vía la Bodega</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AG31" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="AC31" t="n">
+      <c r="AH31" t="n">
         <v>4.896608682</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AI31" t="n">
         <v>-75.71433512</v>
       </c>
     </row>
@@ -4316,45 +4361,45 @@
       <c r="S32" t="n">
         <v>1.4</v>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 18 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AF32" t="inlineStr">
         <is>
           <t>Carrera 18</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AG32" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC32" t="n">
+      <c r="AH32" t="n">
         <v>4.835834367</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AI32" t="n">
         <v>-75.66730004</v>
       </c>
     </row>
@@ -4440,45 +4485,45 @@
       <c r="S33" t="n">
         <v>2.4</v>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AE33" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 23 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AF33" t="inlineStr">
         <is>
           <t>Calle 61</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
+      <c r="AG33" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC33" t="n">
+      <c r="AH33" t="n">
         <v>4.843896232</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AI33" t="n">
         <v>-75.66503904</v>
       </c>
     </row>
@@ -4564,45 +4609,45 @@
       <c r="S34" t="n">
         <v>2.1</v>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AE34" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AF34" t="inlineStr">
         <is>
           <t>Carrera 21</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AG34" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC34" t="n">
+      <c r="AH34" t="n">
         <v>4.833675657</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AI34" t="n">
         <v>-75.66815895000001</v>
       </c>
     </row>
@@ -4688,45 +4733,45 @@
       <c r="S35" t="n">
         <v>2.1</v>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AE35" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 4 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AF35" t="inlineStr">
         <is>
           <t>Carrera 23</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AG35" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC35" t="n">
+      <c r="AH35" t="n">
         <v>4.834166667</v>
       </c>
-      <c r="AD35" t="n">
+      <c r="AI35" t="n">
         <v>-75.66527778</v>
       </c>
     </row>
@@ -4812,45 +4857,45 @@
       <c r="S36" t="n">
         <v>3</v>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AE36" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 17 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AF36" t="inlineStr">
         <is>
           <t>Calle 64</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AG36" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC36" t="n">
+      <c r="AH36" t="n">
         <v>4.843075404</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AI36" t="n">
         <v>-75.66069447</v>
       </c>
     </row>
@@ -4936,45 +4981,45 @@
       <c r="S37" t="n">
         <v>3</v>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="AE37" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 11 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AF37" t="inlineStr">
         <is>
           <t>Calle 67</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AG37" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC37" t="n">
+      <c r="AH37" t="n">
         <v>4.844819</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AI37" t="n">
         <v>-75.660687</v>
       </c>
     </row>
@@ -5060,45 +5105,45 @@
       <c r="S38" t="n">
         <v>8</v>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="AE38" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 13 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AF38" t="inlineStr">
         <is>
           <t>Carrera 24A</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
+      <c r="AG38" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC38" t="n">
+      <c r="AH38" t="n">
         <v>4.816944444</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AI38" t="n">
         <v>-75.67805556</v>
       </c>
     </row>
@@ -5184,40 +5229,40 @@
       <c r="S39" t="n">
         <v>8</v>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AE39" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
+      <c r="AG39" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC39" t="n">
+      <c r="AH39" t="n">
         <v>4.817222222</v>
       </c>
-      <c r="AD39" t="n">
+      <c r="AI39" t="n">
         <v>-75.6725</v>
       </c>
     </row>
@@ -5303,40 +5348,40 @@
       <c r="S40" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AE40" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 56 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
+      <c r="AG40" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC40" t="n">
+      <c r="AH40" t="n">
         <v>4.818297979</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AI40" t="n">
         <v>-75.66450766</v>
       </c>
     </row>
@@ -5422,40 +5467,40 @@
       <c r="S41" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AE41" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 36 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
+      <c r="AG41" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC41" t="n">
+      <c r="AH41" t="n">
         <v>4.825547182</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AI41" t="n">
         <v>-75.66634138000001</v>
       </c>
     </row>
@@ -5541,40 +5586,40 @@
       <c r="S42" t="n">
         <v>7.4</v>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="AC42" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="AD42" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AE42" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 16 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AG42" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC42" t="n">
+      <c r="AH42" t="n">
         <v>4.830277778</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AI42" t="n">
         <v>-75.6825</v>
       </c>
     </row>
@@ -5660,45 +5705,45 @@
       <c r="S43" t="n">
         <v>7.4</v>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="AC43" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="AD43" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AE43" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 7 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AF43" t="inlineStr">
         <is>
           <t>Carrera 19</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
+      <c r="AG43" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC43" t="n">
+      <c r="AH43" t="n">
         <v>4.816666667</v>
       </c>
-      <c r="AD43" t="n">
+      <c r="AI43" t="n">
         <v>-75.68333333</v>
       </c>
     </row>
@@ -5784,45 +5829,45 @@
       <c r="S44" t="n">
         <v>5.7</v>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="AD44" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AE44" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AF44" t="inlineStr">
         <is>
           <t>Carrera 5</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AG44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC44" t="n">
+      <c r="AH44" t="n">
         <v>4.818122534</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AI44" t="n">
         <v>-75.71553498</v>
       </c>
     </row>
@@ -5908,45 +5953,45 @@
       <c r="S45" t="n">
         <v>5.7</v>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="AC45" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="AD45" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AE45" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AF45" t="inlineStr">
         <is>
           <t>Carrera 2 Bis</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AG45" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC45" t="n">
+      <c r="AH45" t="n">
         <v>4.819868522229693</v>
       </c>
-      <c r="AD45" t="n">
+      <c r="AI45" t="n">
         <v>-75.70621902228969</v>
       </c>
     </row>
@@ -6032,40 +6077,40 @@
       <c r="S46" t="n">
         <v>14.1</v>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AE46" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 5 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AG46" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC46" t="n">
+      <c r="AH46" t="n">
         <v>4.805705</v>
       </c>
-      <c r="AD46" t="n">
+      <c r="AI46" t="n">
         <v>-75.73962299999999</v>
       </c>
     </row>
@@ -6151,45 +6196,45 @@
       <c r="S47" t="n">
         <v>14.1</v>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="AD47" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AE47" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 35 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AF47" t="inlineStr">
         <is>
           <t>Calle 75</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
+      <c r="AG47" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC47" t="n">
+      <c r="AH47" t="n">
         <v>4.803217136</v>
       </c>
-      <c r="AD47" t="n">
+      <c r="AI47" t="n">
         <v>-75.74425404</v>
       </c>
     </row>
@@ -6275,40 +6320,40 @@
       <c r="S48" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X48" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="AD48" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AE48" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AG48" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="AC48" t="n">
+      <c r="AH48" t="n">
         <v>4.99014911697</v>
       </c>
-      <c r="AD48" t="n">
+      <c r="AI48" t="n">
         <v>-75.9242208477</v>
       </c>
     </row>
@@ -6394,40 +6439,40 @@
       <c r="S49" t="n">
         <v>42.5</v>
       </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X49" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="AD49" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AE49" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 13 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AG49" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC49" t="n">
+      <c r="AH49" t="n">
         <v>4.996865</v>
       </c>
-      <c r="AD49" t="n">
+      <c r="AI49" t="n">
         <v>-75.980124</v>
       </c>
     </row>
@@ -6513,45 +6558,45 @@
       <c r="S50" t="n">
         <v>42.5</v>
       </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X50" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>rojo, verde</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="AD50" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AE50" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 28 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AF50" t="inlineStr">
         <is>
           <t>La Celia-Balboa</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AG50" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC50" t="n">
+      <c r="AH50" t="n">
         <v>4.993201</v>
       </c>
-      <c r="AD50" t="n">
+      <c r="AI50" t="n">
         <v>-75.981357</v>
       </c>
     </row>
@@ -6637,40 +6682,40 @@
       <c r="S51" t="n">
         <v>17.5</v>
       </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X51" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="AD51" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AE51" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 121 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
+      <c r="AG51" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC51" t="n">
+      <c r="AH51" t="n">
         <v>5.063056</v>
       </c>
-      <c r="AD51" t="n">
+      <c r="AI51" t="n">
         <v>-75.99972200000001</v>
       </c>
     </row>
@@ -6756,45 +6801,45 @@
       <c r="S52" t="n">
         <v>44</v>
       </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X52" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="AD52" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="AE52" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AF52" t="inlineStr">
         <is>
           <t>Carrera 7</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
+      <c r="AG52" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC52" t="n">
+      <c r="AH52" t="n">
         <v>5.072806629</v>
       </c>
-      <c r="AD52" t="n">
+      <c r="AI52" t="n">
         <v>-75.96351957</v>
       </c>
     </row>
@@ -6880,45 +6925,45 @@
       <c r="S53" t="n">
         <v>44</v>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="AC53" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="AD53" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AE53" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 18 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AF53" t="inlineStr">
         <is>
           <t>Calle 5</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
+      <c r="AG53" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC53" t="n">
+      <c r="AH53" t="n">
         <v>5.00296197</v>
       </c>
-      <c r="AD53" t="n">
+      <c r="AI53" t="n">
         <v>-76.00271345</v>
       </c>
     </row>
@@ -7004,40 +7049,40 @@
       <c r="S54" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X54" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>rojo</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="AD54" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AE54" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 1 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
+      <c r="AG54" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC54" t="n">
+      <c r="AH54" t="n">
         <v>4.885083</v>
       </c>
-      <c r="AD54" t="n">
+      <c r="AI54" t="n">
         <v>-75.97331699999999</v>
       </c>
     </row>
@@ -7123,40 +7168,40 @@
       <c r="S55" t="n">
         <v>55.7</v>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="AC55" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="AD55" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AE55" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 9 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
+      <c r="AG55" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC55" t="n">
+      <c r="AH55" t="n">
         <v>4.806935893</v>
       </c>
-      <c r="AD55" t="n">
+      <c r="AI55" t="n">
         <v>-75.74500842</v>
       </c>
     </row>
@@ -7242,40 +7287,40 @@
       <c r="S56" t="n">
         <v>55.7</v>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="AC56" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="AD56" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AE56" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 147 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
+      <c r="AG56" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC56" t="n">
+      <c r="AH56" t="n">
         <v>4.819139218</v>
       </c>
-      <c r="AD56" t="n">
+      <c r="AI56" t="n">
         <v>-75.76076208000001</v>
       </c>
     </row>
@@ -7361,45 +7406,45 @@
       <c r="S57" t="n">
         <v>43.1</v>
       </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X57" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="AD57" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AE57" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 20 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AF57" t="inlineStr">
         <is>
           <t>Al Español</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
+      <c r="AG57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC57" t="n">
+      <c r="AH57" t="n">
         <v>4.932181</v>
       </c>
-      <c r="AD57" t="n">
+      <c r="AI57" t="n">
         <v>-75.698198</v>
       </c>
     </row>
@@ -7485,40 +7530,40 @@
       <c r="S58" t="n">
         <v>43.1</v>
       </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X58" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="AD58" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AE58" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 30 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
+      <c r="AG58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC58" t="n">
+      <c r="AH58" t="n">
         <v>4.884255</v>
       </c>
-      <c r="AD58" t="n">
+      <c r="AI58" t="n">
         <v>-75.634398</v>
       </c>
     </row>
@@ -7604,45 +7649,45 @@
       <c r="S59" t="n">
         <v>0.8</v>
       </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X59" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="AD59" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AE59" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 14 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AF59" t="inlineStr">
         <is>
           <t>Carrera 15</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
+      <c r="AG59" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC59" t="n">
+      <c r="AH59" t="n">
         <v>4.865108</v>
       </c>
-      <c r="AD59" t="n">
+      <c r="AI59" t="n">
         <v>-75.62179101</v>
       </c>
     </row>
@@ -7728,45 +7773,45 @@
       <c r="S60" t="n">
         <v>44.4</v>
       </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X60" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="AD60" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AE60" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 135 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AF60" t="inlineStr">
         <is>
           <t>A Campoalegre</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
+      <c r="AG60" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC60" t="n">
+      <c r="AH60" t="n">
         <v>4.914981371</v>
       </c>
-      <c r="AD60" t="n">
+      <c r="AI60" t="n">
         <v>-75.61788369</v>
       </c>
     </row>
@@ -7852,40 +7897,40 @@
       <c r="S61" t="n">
         <v>44.4</v>
       </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X61" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="AD61" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AE61" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 55 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
+      <c r="AG61" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC61" t="n">
+      <c r="AH61" t="n">
         <v>4.966084</v>
       </c>
-      <c r="AD61" t="n">
+      <c r="AI61" t="n">
         <v>-75.63563000000001</v>
       </c>
     </row>
@@ -7971,40 +8016,40 @@
       <c r="S62" t="n">
         <v>22.4</v>
       </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
       <c r="X62" t="inlineStr">
         <is>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="AD62" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AE62" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 81 m de esa vía.</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
+      <c r="AG62" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC62" t="n">
+      <c r="AH62" t="n">
         <v>4.783364</v>
       </c>
-      <c r="AD62" t="n">
+      <c r="AI62" t="n">
         <v>-75.641834</v>
       </c>
     </row>
@@ -8090,50 +8135,50 @@
       <c r="S63" t="n">
         <v>22.4</v>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="AC63" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="AD63" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AE63" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 3 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AF63" t="inlineStr">
         <is>
           <t>Carrera 20</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
+      <c r="AG63" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AC63" t="n">
+      <c r="AH63" t="n">
         <v>4.803937</v>
       </c>
-      <c r="AD63" t="n">
+      <c r="AI63" t="n">
         <v>-75.699062</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD63"/>
+  <autoFilter ref="A1:AI63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8144,7 +8189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8171,7 +8216,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -8235,115 +8280,127 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Cuadrilla</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Días</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Sedes</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Horas de carretera</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Km</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Noches fuera</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Noches de hotel</t>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cada columna dice de dónde viene el dato. «No reportó al MEN» no quiere decir que la sede no tenga daño: quiere decir que no hay reporte. Todas las sedes del plan se visitan, tengan o no reporte o concepto técnico.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>13</v>
-      </c>
-      <c r="C10" t="n">
-        <v>20</v>
-      </c>
-      <c r="D10" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>649</v>
-      </c>
-      <c r="F10" t="n">
-        <v>12</v>
-      </c>
-      <c r="G10" t="n">
-        <v>14</v>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Cuadrilla</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Días</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Sedes</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Horas de carretera</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Km</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Noches fuera</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Noches de hotel</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>649</v>
+      </c>
+      <c r="F11" t="n">
         <v>12</v>
       </c>
-      <c r="C11" t="n">
-        <v>22</v>
-      </c>
-      <c r="D11" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>129</v>
-      </c>
-      <c r="F11" t="n">
-        <v>9</v>
-      </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D12" t="n">
-        <v>16.2</v>
+        <v>6.1</v>
       </c>
       <c r="E12" t="n">
-        <v>447</v>
+        <v>129</v>
       </c>
       <c r="F12" t="n">
         <v>9</v>
       </c>
       <c r="G12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>447</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" t="n">
         <v>12</v>
       </c>
     </row>

--- a/public/datos/plan_cuadrillas_risaralda.xlsx
+++ b/public/datos/plan_cuadrillas_risaralda.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plan'!$A$1:$AI$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plan'!$A$1:$AI$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI63"/>
+  <dimension ref="A1:AI64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -700,16 +700,16 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>93.36</v>
+        <v>92.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.17</v>
+        <v>0.37</v>
       </c>
       <c r="R2" t="n">
-        <v>93.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>64.3</v>
+        <v>63.9</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 1 m de esa vía.</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>5.104722222</v>
+        <v>5.105562</v>
       </c>
       <c r="AI2" t="n">
-        <v>-75.9425</v>
+        <v>-75.943062</v>
       </c>
     </row>
     <row r="3">
@@ -943,16 +943,16 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.42</v>
+        <v>0.74</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -976,24 +976,24 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 31 m de esa vía.</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>Calle 3 A</t>
+          <t>Carrera 5 B</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>5.21916175028</v>
+        <v>5.220642</v>
       </c>
       <c r="AI4" t="n">
-        <v>-76.0331189595</v>
+        <v>-76.03213599999999</v>
       </c>
     </row>
     <row r="5">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>21.47</v>
+        <v>21.17</v>
       </c>
       <c r="Q10" t="n">
-        <v>50.13</v>
+        <v>50.38</v>
       </c>
       <c r="R10" t="n">
-        <v>119.7</v>
+        <v>119.6</v>
       </c>
       <c r="S10" t="n">
         <v>35.5</v>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 75 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 55 m de esa vía.</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1710,14 +1710,14 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>5.11777777778</v>
+        <v>5.119188</v>
       </c>
       <c r="AI10" t="n">
-        <v>-75.90472222219999</v>
+        <v>-75.905563</v>
       </c>
     </row>
     <row r="11">
@@ -1791,13 +1791,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>50.13</v>
+        <v>50.38</v>
       </c>
       <c r="Q11" t="n">
         <v>48.09</v>
       </c>
       <c r="R11" t="n">
-        <v>119.7</v>
+        <v>119.6</v>
       </c>
       <c r="S11" t="n">
         <v>35.5</v>
@@ -2156,13 +2156,13 @@
         <v>26.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>60.32</v>
+        <v>59.67</v>
       </c>
       <c r="R14" t="n">
-        <v>96.2</v>
+        <v>95</v>
       </c>
       <c r="S14" t="n">
-        <v>42.4</v>
+        <v>42</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>60.32</v>
+        <v>59.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.26</v>
+        <v>8.65</v>
       </c>
       <c r="R15" t="n">
-        <v>96.2</v>
+        <v>95</v>
       </c>
       <c r="S15" t="n">
-        <v>42.4</v>
+        <v>42</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 11 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 34 m de esa vía.</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>5.279785869</v>
+        <v>5.280181</v>
       </c>
       <c r="AI15" t="n">
-        <v>-75.89025909</v>
+        <v>-75.888633</v>
       </c>
     </row>
     <row r="16">
@@ -2686,10 +2686,10 @@
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>5.328055556</v>
+        <v>5.328056</v>
       </c>
       <c r="AI18" t="n">
-        <v>-75.74833332999999</v>
+        <v>-75.748333</v>
       </c>
     </row>
     <row r="19">
@@ -3081,27 +3081,27 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>LUIS CARLOS GONZALES MEJIA</t>
+          <t>INSTITUCION EDUCATIVA SAN FERNANDO</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
+          <t>INSTITUCION EDUCATIVA SAN FERNANDO</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>166170001490</t>
+          <t>166001000344</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>BARRIO VILLA ALEXANDRA</t>
+          <t>IND CLL 70 NO 23-20 SAN FERNANDO CUBA</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3125,30 +3125,30 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>9.4</v>
+        <v>13.53</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.14</v>
+        <v>1.83</v>
       </c>
       <c r="R22" t="n">
-        <v>17</v>
+        <v>31.7</v>
       </c>
       <c r="S22" t="n">
-        <v>6.8</v>
+        <v>14.1</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -3158,12 +3158,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 5 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>Calle 9</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 5 m de esa vía.</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -3172,10 +3167,10 @@
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>4.823055556</v>
+        <v>4.805705</v>
       </c>
       <c r="AI22" t="n">
-        <v>-75.6925</v>
+        <v>-75.73962299999999</v>
       </c>
     </row>
     <row r="23">
@@ -3205,27 +3200,27 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>INSTITUTO EDUCATIVO EMPRESARIAL</t>
+          <t>INST EDUCATIVA JESUS MARIA ORMAZA</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
+          <t>INSTITUCION EDUCATIVA JESUS MARIA ORMAZA</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>166170001911</t>
+          <t>166001000646</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3235,7 +3230,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>LA BADEA -ANTIGUA  PLAZA DE FERIAS</t>
+          <t>CL 70 22 00 BR CUBA</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3249,16 +3244,16 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.14</v>
+        <v>1.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.44</v>
+        <v>16.37</v>
       </c>
       <c r="R23" t="n">
-        <v>17</v>
+        <v>31.7</v>
       </c>
       <c r="S23" t="n">
-        <v>6.8</v>
+        <v>14.1</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3272,7 +3267,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -3282,12 +3277,12 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 21 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 35 m de esa vía.</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>Calle 9</t>
+          <t>Calle 75</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -3296,10 +3291,10 @@
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>4.823055556</v>
+        <v>4.803217136</v>
       </c>
       <c r="AI23" t="n">
-        <v>-75.69194444</v>
+        <v>-75.74425404</v>
       </c>
     </row>
     <row r="24">
@@ -3329,60 +3324,60 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>POPULAR DIOCESANO</t>
+          <t>LAS PALMAS</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA POPULAR DIOCESANO</t>
+          <t>INSTITUCION EDUCATIVA JESUS DE LA BUENA ESPERANZA</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>166170000256</t>
+          <t>166001002754</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>AV DEL RIO NO 43 - 26</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
           <t>Dos Quebradas</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>LA BADEA</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Pereira</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Pereira</t>
-        </is>
-      </c>
       <c r="P24" t="n">
-        <v>11.45</v>
+        <v>6.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>3.32</v>
       </c>
       <c r="R24" t="n">
-        <v>22.4</v>
+        <v>25.9</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3394,11 +3389,6 @@
           <t>Critico</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
@@ -3411,7 +3401,12 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 6 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Carrera 5</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3420,10 +3415,10 @@
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>4.824166667</v>
+        <v>4.818122534</v>
       </c>
       <c r="AI24" t="n">
-        <v>-75.69972222</v>
+        <v>-75.71553498</v>
       </c>
     </row>
     <row r="25">
@@ -3453,69 +3448,69 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>LA BADEA</t>
+          <t>JESUS DE LA BUENA ESPERANZA</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
+          <t>INSTITUCION EDUCATIVA JESUS DE LA BUENA ESPERANZA</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>166170001741</t>
+          <t>166001000450</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>CR 3 NO 34 - 46</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
           <t>Dos Quebradas</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>BARRIO LA BADEA(ENSEGUIDA A LA IGLESIA)</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Pereira</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Pereira</t>
-        </is>
-      </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>3.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>9.9</v>
+        <v>16.29</v>
       </c>
       <c r="R25" t="n">
-        <v>22.4</v>
+        <v>25.9</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3530,19 +3525,24 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 20 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Carrera 2 Bis</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>4.82381384716</v>
+        <v>4.819868522229693</v>
       </c>
       <c r="AI25" t="n">
-        <v>-75.699591841</v>
+        <v>-75.70621902228969</v>
       </c>
     </row>
     <row r="26">
@@ -3572,84 +3572,84 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>SE LAS TAZAS</t>
+          <t>EL PLACER</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>IE AGRICOLA MARSELLA</t>
+          <t>INSTITUCION EDUCATIVA COMBIA</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>266440000100</t>
+          <t>266001001698</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>CRUCERO DE COMBIA</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Dos Quebradas</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
           <t>Marsella</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>VDA LAS TAZAS</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Pereira</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Marsella</t>
-        </is>
-      </c>
       <c r="P26" t="n">
-        <v>51.42</v>
+        <v>29.57</v>
       </c>
       <c r="Q26" t="n">
-        <v>11.61</v>
+        <v>22.55</v>
       </c>
       <c r="R26" t="n">
-        <v>97.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>35.5</v>
+        <v>40.7</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>No reportó al MEN</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>Sin concepto técnico ni reporte del rector</t>
+          <t>Riesgo inminente de colapso</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Critico</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 35 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 147 m de esa vía.</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>4.9022</v>
+        <v>4.819139218</v>
       </c>
       <c r="AI26" t="n">
-        <v>-75.773707</v>
+        <v>-75.76076208000001</v>
       </c>
     </row>
     <row r="27">
@@ -3696,17 +3696,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SE LA BORDADITA</t>
+          <t>KURMADO</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>IE AGRICOLA MARSELLA</t>
+          <t>IE WAARRARA DEE</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>266440000525</t>
+          <t>266440800018</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>RESG INDIGENA ALTO MIRA</t>
+          <t>VDA EL GUAYABO</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3735,25 +3735,25 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>11.61</v>
+        <v>22.55</v>
       </c>
       <c r="Q27" t="n">
-        <v>34.84</v>
+        <v>31.47</v>
       </c>
       <c r="R27" t="n">
-        <v>97.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>35.5</v>
+        <v>40.7</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>Moderado</t>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3768,7 +3768,12 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 40 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 167 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Ruta de Sembrando Lecturas</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -3777,10 +3782,10 @@
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>4.928985175</v>
+        <v>4.877583</v>
       </c>
       <c r="AI27" t="n">
-        <v>-75.77832192</v>
+        <v>-75.7701</v>
       </c>
     </row>
     <row r="28">
@@ -4068,17 +4073,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>SE EL RAYO</t>
+          <t>SE LAS TAZAS</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>IE INSTITUTO ESTRADA</t>
+          <t>IE AGRICOLA MARSELLA</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>266440000274</t>
+          <t>266440000100</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4093,7 +4098,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>VDA EL RAYO</t>
+          <t>VDA LAS TAZAS</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4103,20 +4108,20 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>15.5</v>
+        <v>29.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.460000000000001</v>
+        <v>14.74</v>
       </c>
       <c r="R30" t="n">
-        <v>76.8</v>
+        <v>76.7</v>
       </c>
       <c r="S30" t="n">
-        <v>26.6</v>
+        <v>29.3</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -4140,19 +4145,19 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 22 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 35 m de esa vía.</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>4.909338798</v>
+        <v>4.9022</v>
       </c>
       <c r="AI30" t="n">
-        <v>-75.72299636</v>
+        <v>-75.773707</v>
       </c>
     </row>
     <row r="31">
@@ -4187,17 +4192,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SE SAN ANDRES</t>
+          <t>SE LA BORDADITA</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>IE INSTITUTO ESTRADA</t>
+          <t>IE AGRICOLA MARSELLA</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>266440000045</t>
+          <t>266440000525</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4212,7 +4217,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>VDA SAN ANDRES</t>
+          <t>RESG INDIGENA ALTO MIRA</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4222,29 +4227,29 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>9.460000000000001</v>
+        <v>14.74</v>
       </c>
       <c r="Q31" t="n">
-        <v>51.85</v>
+        <v>32.29</v>
       </c>
       <c r="R31" t="n">
-        <v>76.8</v>
+        <v>76.7</v>
       </c>
       <c r="S31" t="n">
-        <v>26.6</v>
+        <v>29.3</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>No reportó al MEN</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>Sin concepto técnico ni reporte del rector</t>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4259,24 +4264,19 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 318 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>Vía la Bodega</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 61 m de esa vía.</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>4.896608682</v>
+        <v>4.933312</v>
       </c>
       <c r="AI31" t="n">
-        <v>-75.71433512</v>
+        <v>-75.780563</v>
       </c>
     </row>
     <row r="32">
@@ -4306,89 +4306,84 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>RUFINO JOSE CUERVO</t>
+          <t>SE EL RAYO</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA PABLO SEXTO</t>
+          <t>IE INSTITUTO ESTRADA</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>166170000744</t>
+          <t>266440000274</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>KR 18 43 08</t>
+          <t>VDA EL RAYO</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.78</v>
+        <v>15.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.17</v>
+        <v>16.62</v>
       </c>
       <c r="R32" t="n">
-        <v>4</v>
+        <v>83.2</v>
       </c>
       <c r="S32" t="n">
-        <v>1.4</v>
+        <v>29.9</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>Bajo</t>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 18 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>Carrera 18</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 22 m de esa vía.</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
@@ -4397,10 +4392,10 @@
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>4.835834367</v>
+        <v>4.909339</v>
       </c>
       <c r="AI32" t="n">
-        <v>-75.66730004</v>
+        <v>-75.72299599999999</v>
       </c>
     </row>
     <row r="33">
@@ -4415,104 +4410,99 @@
         </is>
       </c>
       <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" t="n">
         <v>2</v>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>lunes</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>7</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ANTONIO JOSE DE SUCRE</t>
+          <t>SE SAN ANDRES</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA PABLO SEXTO</t>
+          <t>IE INSTITUTO ESTRADA</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>166170000043</t>
+          <t>266440000045</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>CL 16 14 A 19</t>
+          <t>VDA SAN ANDRES</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Marsella</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.67</v>
+        <v>16.62</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.34</v>
+        <v>51.09</v>
       </c>
       <c r="R33" t="n">
-        <v>6</v>
+        <v>83.2</v>
       </c>
       <c r="S33" t="n">
-        <v>2.4</v>
+        <v>29.9</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Bajo</t>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino destapado</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 23 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>Calle 61</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 26 m de esa vía.</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
@@ -4521,10 +4511,10 @@
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>4.843896232</v>
+        <v>4.900063</v>
       </c>
       <c r="AI33" t="n">
-        <v>-75.66503904</v>
+        <v>-75.701937</v>
       </c>
     </row>
     <row r="34">
@@ -4543,85 +4533,85 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ELADIA MEJIA GONZALEZ</t>
+          <t>SE NUESTRA SEÑORA DEL ROSARIO - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA PABLO SEXTO</t>
+          <t>CE NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>166170000175</t>
+          <t>266687000331</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>KR 21 41 80</t>
+          <t>CGTO PERALONSO</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Apia</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3.07</v>
+        <v>90.42</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.26</v>
+        <v>57.95</v>
       </c>
       <c r="R34" t="n">
-        <v>6.1</v>
+        <v>148.4</v>
       </c>
       <c r="S34" t="n">
-        <v>2.1</v>
+        <v>78.5</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Bajo</t>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
@@ -4631,12 +4621,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 12 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>Carrera 21</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 20 m de esa vía.</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
@@ -4645,10 +4630,10 @@
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>4.833675657</v>
+        <v>4.993499</v>
       </c>
       <c r="AI34" t="n">
-        <v>-75.66815895000001</v>
+        <v>-75.925836</v>
       </c>
     </row>
     <row r="35">
@@ -4674,31 +4659,31 @@
         <v>8</v>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA PABLO VI</t>
+          <t>SE MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA PABLO SEXTO</t>
+          <t>IE LICEO DE OCCIDENTE</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>166170000078</t>
+          <t>166383000195</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>La Celia</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4708,39 +4693,39 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>CALLE 44 NO. 23 - 24</t>
+          <t>CL 5 2 69</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Apia</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.26</v>
+        <v>54.33</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.8</v>
+        <v>41.67</v>
       </c>
       <c r="R35" t="n">
-        <v>6.1</v>
+        <v>117.7</v>
       </c>
       <c r="S35" t="n">
-        <v>2.1</v>
+        <v>44.5</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>Bajo</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4755,12 +4740,12 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 4 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 18 m de esa vía.</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>Carrera 23</t>
+          <t>Calle 5</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
@@ -4769,10 +4754,10 @@
         </is>
       </c>
       <c r="AH35" t="n">
-        <v>4.834166667</v>
+        <v>5.00296197</v>
       </c>
       <c r="AI35" t="n">
-        <v>-75.66527778</v>
+        <v>-76.00271345</v>
       </c>
     </row>
     <row r="36">
@@ -4791,80 +4776,80 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>MANUELA BELTRAN</t>
+          <t>SE LA BAMBA</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA CRISTO REY</t>
+          <t>IE MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>166170000272</t>
+          <t>266687000030</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>KR 19 64 08</t>
+          <t>VDA LA BAMBA</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Apia</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.78</v>
+        <v>41.67</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.86</v>
+        <v>21.69</v>
       </c>
       <c r="R36" t="n">
-        <v>7.4</v>
+        <v>117.7</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>44.5</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Moderado</t>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4879,12 +4864,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 17 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>Calle 64</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
@@ -4893,10 +4873,10 @@
         </is>
       </c>
       <c r="AH36" t="n">
-        <v>4.843075404</v>
+        <v>5.063438</v>
       </c>
       <c r="AI36" t="n">
-        <v>-75.66069447</v>
+        <v>-76.001812</v>
       </c>
     </row>
     <row r="37">
@@ -4922,31 +4902,31 @@
         <v>9</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA CRISTO REY</t>
+          <t>SE INSTITUTO SANTUARIO - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA CRISTO REY</t>
+          <t>INSTITUCIÓN EDUCATIVA INSTITUTO SANTUARIO</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>166170000159</t>
+          <t>166687000256</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4956,39 +4936,39 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>CLLE 67 # 18-01 BARRIO LA CAPILLA</t>
+          <t>CL 6 7 17</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.86</v>
+        <v>0.1</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.73</v>
+        <v>0.08</v>
       </c>
       <c r="R37" t="n">
-        <v>7.4</v>
+        <v>0.2</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>Bajo</t>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5003,12 +4983,12 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 11 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>Calle 67</t>
+          <t>Carrera 7</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
@@ -5017,10 +4997,10 @@
         </is>
       </c>
       <c r="AH37" t="n">
-        <v>4.844819</v>
+        <v>5.072806629</v>
       </c>
       <c r="AI37" t="n">
-        <v>-75.660687</v>
+        <v>-75.96351957</v>
       </c>
     </row>
     <row r="38">
@@ -5050,74 +5030,74 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>LUIS CARLOS GALAN SARMIENTO</t>
+          <t>ESCUELA PATIO BONITO</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA POPULAR DIOCESANO</t>
+          <t>IE PATIO BONITO</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>166170001481</t>
+          <t>266383800005</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>La Celia</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>BARRIO LAS VEGAS</t>
+          <t>VDA PATIO BONITO</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>10.53</v>
+        <v>51.97</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.18</v>
+        <v>1.21</v>
       </c>
       <c r="R38" t="n">
-        <v>22.3</v>
+        <v>105</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>36.9</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>Moderado</t>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
@@ -5127,12 +5107,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 13 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>Carrera 24A</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 13 m de esa vía.</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
@@ -5141,10 +5116,10 @@
         </is>
       </c>
       <c r="AH38" t="n">
-        <v>4.816944444</v>
+        <v>4.996865</v>
       </c>
       <c r="AI38" t="n">
-        <v>-75.67805556</v>
+        <v>-75.980124</v>
       </c>
     </row>
     <row r="39">
@@ -5174,74 +5149,74 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SAN RAFAEL</t>
+          <t>SE PATIO BONITO - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA FABIO VASQUEZ BOTERO</t>
+          <t>IE PATIO BONITO</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>166170001937</t>
+          <t>266383000050</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>La Celia</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>KR 31 CL 13 SAN RAFAEL</t>
+          <t>VDA PATIO BONITO</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3.18</v>
+        <v>1.21</v>
       </c>
       <c r="Q39" t="n">
-        <v>8.619999999999999</v>
+        <v>51.87</v>
       </c>
       <c r="R39" t="n">
-        <v>22.3</v>
+        <v>105</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>36.9</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>Moderado</t>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>rojo, verde</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
@@ -5251,7 +5226,12 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 28 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>La Celia-Balboa</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
@@ -5260,10 +5240,10 @@
         </is>
       </c>
       <c r="AH39" t="n">
-        <v>4.817222222</v>
+        <v>4.993201</v>
       </c>
       <c r="AI39" t="n">
-        <v>-75.6725</v>
+        <v>-75.981357</v>
       </c>
     </row>
     <row r="40">
@@ -5293,27 +5273,27 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>CENTRO EDUCATIVO NARANJALES</t>
+          <t>SE TAMBORES - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA FABIO VASQUEZ BOTERO</t>
+          <t>IE TAMBORES</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>266170000897</t>
+          <t>266075000022</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Balboa</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -5323,54 +5303,54 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>NARANJALES</t>
+          <t>VDA TAMBORES</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Santuario</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Cartago</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>10.56</v>
+        <v>83.7</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.31</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="R40" t="n">
-        <v>21.5</v>
+        <v>154</v>
       </c>
       <c r="S40" t="n">
-        <v>8.300000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>Bajo</t>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>rojo</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 56 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 1 m de esa vía.</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
@@ -5379,10 +5359,10 @@
         </is>
       </c>
       <c r="AH40" t="n">
-        <v>4.818297979</v>
+        <v>4.885083</v>
       </c>
       <c r="AI40" t="n">
-        <v>-75.66450766</v>
+        <v>-75.97331699999999</v>
       </c>
     </row>
     <row r="41">
@@ -5401,80 +5381,80 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>CENTRO EDUCATIVO LAS VIOLETAS</t>
+          <t>INSTITUCION EDUCATIVA LUIS CARLOS GONZALEZ MEJIA</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA FABIO VASQUEZ BOTERO</t>
+          <t>INSTITUCION EDUCATIVA LUIS CARLOS GONZALEZ MEJIA</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>166170001562</t>
+          <t>166001003505</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>CL 26A KR 27A -28</t>
+          <t>KR 17 82 103</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Cartago</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>5.31</v>
+        <v>32.55</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.66</v>
+        <v>10.94</v>
       </c>
       <c r="R41" t="n">
-        <v>21.5</v>
+        <v>48</v>
       </c>
       <c r="S41" t="n">
-        <v>8.300000000000001</v>
+        <v>30.5</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>Bajo</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5489,7 +5469,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 36 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 9 m de esa vía.</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
@@ -5498,10 +5478,10 @@
         </is>
       </c>
       <c r="AH41" t="n">
-        <v>4.825547182</v>
+        <v>4.806935893</v>
       </c>
       <c r="AI41" t="n">
-        <v>-75.66634138000001</v>
+        <v>-75.74500842</v>
       </c>
     </row>
     <row r="42">
@@ -5527,31 +5507,31 @@
         <v>12</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>FABIO VASQUEZ BOTERO</t>
+          <t>PROVIDENCIA</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA FABIO VASQUEZ BOTERO</t>
+          <t>COMPLEJO EDUCATIVO LA JULITA</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>166170001023</t>
+          <t>166001004978</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -5561,12 +5541,12 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>LA PRADERA</t>
+          <t>KR 20 23 15</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Cartago</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -5575,20 +5555,20 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>7.14</v>
+        <v>10.94</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.72</v>
+        <v>4.56</v>
       </c>
       <c r="R42" t="n">
-        <v>19.5</v>
+        <v>48</v>
       </c>
       <c r="S42" t="n">
-        <v>7.4</v>
+        <v>30.5</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -5598,7 +5578,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
@@ -5608,7 +5588,12 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 16 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 3 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>Carrera 20</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
@@ -5617,16 +5602,16 @@
         </is>
       </c>
       <c r="AH42" t="n">
-        <v>4.830277778</v>
+        <v>4.803937</v>
       </c>
       <c r="AI42" t="n">
-        <v>-75.6825</v>
+        <v>-75.699062</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5635,18 +5620,18 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5655,17 +5640,17 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>BASICO OTUN</t>
+          <t>LUIS CARLOS GALAN SARMIENTO</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
+          <t>INSTITUCION EDUCATIVA POPULAR DIOCESANO</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>166170000329</t>
+          <t>166170001481</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -5680,12 +5665,12 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>BARRIO SAN JUDAS EL BALSO</t>
+          <t>BARRIO LAS VEGAS</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -5694,16 +5679,16 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>5.72</v>
+        <v>8.9</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.63</v>
+        <v>3.71</v>
       </c>
       <c r="R43" t="n">
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
       <c r="S43" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5727,12 +5712,12 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 7 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 3 m de esa vía.</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>Carrera 19</t>
+          <t>Carrera 10 Oeste</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
@@ -5741,10 +5726,10 @@
         </is>
       </c>
       <c r="AH43" t="n">
-        <v>4.816666667</v>
+        <v>4.825563</v>
       </c>
       <c r="AI43" t="n">
-        <v>-75.68333333</v>
+        <v>-75.71006300000001</v>
       </c>
     </row>
     <row r="44">
@@ -5770,31 +5755,31 @@
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>LAS PALMAS</t>
+          <t>POPULAR DIOCESANO</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA JESUS DE LA BUENA ESPERANZA</t>
+          <t>INSTITUCION EDUCATIVA POPULAR DIOCESANO</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>166001002754</t>
+          <t>166170000256</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -5804,7 +5789,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>AV DEL RIO NO 43 - 26</t>
+          <t>LA BADEA</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5818,16 +5803,16 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>6.25</v>
+        <v>3.71</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.32</v>
+        <v>9.85</v>
       </c>
       <c r="R44" t="n">
-        <v>15.2</v>
+        <v>22.5</v>
       </c>
       <c r="S44" t="n">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5839,6 +5824,11 @@
           <t>Critico</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>rojo</t>
+        </is>
+      </c>
       <c r="AC44" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
@@ -5851,12 +5841,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>Carrera 5</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
@@ -5865,10 +5850,10 @@
         </is>
       </c>
       <c r="AH44" t="n">
-        <v>4.818122534</v>
+        <v>4.824166667</v>
       </c>
       <c r="AI44" t="n">
-        <v>-75.71553498</v>
+        <v>-75.69972222</v>
       </c>
     </row>
     <row r="45">
@@ -5887,38 +5872,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="F45" t="n">
-        <v>2</v>
-      </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>JESUS DE LA BUENA ESPERANZA</t>
+          <t>LUIS CARLOS GONZALES MEJIA</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA JESUS DE LA BUENA ESPERANZA</t>
+          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>166001000450</t>
+          <t>166170001490</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5928,7 +5913,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>CR 3 NO 34 - 46</t>
+          <t>BARRIO VILLA ALEXANDRA</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5942,25 +5927,25 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.32</v>
+        <v>11.7</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.64</v>
+        <v>1.64</v>
       </c>
       <c r="R45" t="n">
-        <v>15.2</v>
+        <v>21.9</v>
       </c>
       <c r="S45" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5975,12 +5960,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>Carrera 2 Bis</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 5 m de esa vía.</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
@@ -5989,10 +5969,10 @@
         </is>
       </c>
       <c r="AH45" t="n">
-        <v>4.819868522229693</v>
+        <v>4.826688</v>
       </c>
       <c r="AI45" t="n">
-        <v>-75.70621902228969</v>
+        <v>-75.698437</v>
       </c>
     </row>
     <row r="46">
@@ -6018,31 +5998,31 @@
         <v>2</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA SAN FERNANDO</t>
+          <t>LA BADEA</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA SAN FERNANDO</t>
+          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>166001000344</t>
+          <t>166170001741</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -6052,7 +6032,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>IND CLL 70 NO 23-20 SAN FERNANDO CUBA</t>
+          <t>BARRIO LA BADEA(ENSEGUIDA A LA IGLESIA)</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6066,25 +6046,25 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>13.53</v>
+        <v>1.64</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.83</v>
+        <v>8.58</v>
       </c>
       <c r="R46" t="n">
-        <v>31.7</v>
+        <v>21.9</v>
       </c>
       <c r="S46" t="n">
-        <v>14.1</v>
+        <v>8.6</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>Bajo</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6099,7 +6079,12 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 5 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 12 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>Transversal 5</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
@@ -6108,10 +6093,10 @@
         </is>
       </c>
       <c r="AH46" t="n">
-        <v>4.805705</v>
+        <v>4.824188</v>
       </c>
       <c r="AI46" t="n">
-        <v>-75.73962299999999</v>
+        <v>-75.69556300000001</v>
       </c>
     </row>
     <row r="47">
@@ -6130,48 +6115,48 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>INST EDUCATIVA JESUS MARIA ORMAZA</t>
+          <t>SE LAS MANGAS</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA JESUS MARIA ORMAZA</t>
+          <t>IE INSTITUTO AGROPECUARIO VERACRUZ</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>166001000646</t>
+          <t>266682001101</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Santa Rosa de Cabal</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>CL 70 22 00 BR CUBA</t>
+          <t>VDA LAS MANGAS</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6185,45 +6170,40 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.83</v>
+        <v>20.9</v>
       </c>
       <c r="Q47" t="n">
-        <v>16.37</v>
+        <v>19.07</v>
       </c>
       <c r="R47" t="n">
-        <v>31.7</v>
+        <v>46.6</v>
       </c>
       <c r="S47" t="n">
-        <v>14.1</v>
+        <v>18.4</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Afectación menor</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>Bajo</t>
+          <t>No reportó al MEN</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Sin concepto técnico ni reporte del rector</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 35 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>Calle 75</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 81 m de esa vía.</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
@@ -6232,10 +6212,10 @@
         </is>
       </c>
       <c r="AH47" t="n">
-        <v>4.803217136</v>
+        <v>4.783364</v>
       </c>
       <c r="AI47" t="n">
-        <v>-75.74425404</v>
+        <v>-75.641834</v>
       </c>
     </row>
     <row r="48">
@@ -6261,41 +6241,41 @@
         <v>3</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SE NUESTRA SEÑORA DEL ROSARIO - SEDE PRINCIPAL</t>
+          <t>BASICO OTUN</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CE NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>266687000331</t>
+          <t>166170000329</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>CGTO PERALONSO</t>
+          <t>BARRIO SAN JUDAS EL BALSO</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6305,29 +6285,29 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Apia</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>90.97</v>
+        <v>19.07</v>
       </c>
       <c r="Q48" t="n">
-        <v>58.58</v>
+        <v>6.63</v>
       </c>
       <c r="R48" t="n">
-        <v>149.6</v>
+        <v>46.6</v>
       </c>
       <c r="S48" t="n">
-        <v>78.90000000000001</v>
+        <v>18.4</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>No reportó al MEN</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>Sin concepto técnico ni reporte del rector</t>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6342,19 +6322,24 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 12 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 7 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>Carrera 19</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AH48" t="n">
-        <v>4.99014911697</v>
+        <v>4.816666667</v>
       </c>
       <c r="AI48" t="n">
-        <v>-75.9242208477</v>
+        <v>-75.68333333</v>
       </c>
     </row>
     <row r="49">
@@ -6384,74 +6369,74 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>ESCUELA PATIO BONITO</t>
+          <t>SAN RAFAEL</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>IE PATIO BONITO</t>
+          <t>INSTITUCION EDUCATIVA FABIO VASQUEZ BOTERO</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>266383800005</t>
+          <t>166170001937</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>La Celia</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>VDA PATIO BONITO</t>
+          <t>KR 31 CL 13 SAN RAFAEL</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Apia</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>48.3</v>
+        <v>11.2</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.21</v>
+        <v>3.83</v>
       </c>
       <c r="R49" t="n">
-        <v>101.4</v>
+        <v>24.7</v>
       </c>
       <c r="S49" t="n">
-        <v>42.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>No reportó al MEN</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>Sin concepto técnico ni reporte del rector</t>
+          <t>Afectación parcial</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
@@ -6461,7 +6446,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 13 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
@@ -6470,10 +6455,10 @@
         </is>
       </c>
       <c r="AH49" t="n">
-        <v>4.996865</v>
+        <v>4.817222</v>
       </c>
       <c r="AI49" t="n">
-        <v>-75.980124</v>
+        <v>-75.6725</v>
       </c>
     </row>
     <row r="50">
@@ -6503,27 +6488,27 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SE PATIO BONITO - SEDE PRINCIPAL</t>
+          <t>CENTRO EDUCATIVO NARANJALES</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>IE PATIO BONITO</t>
+          <t>INSTITUCION EDUCATIVA FABIO VASQUEZ BOTERO</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>266383000050</t>
+          <t>266170000897</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>La Celia</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -6533,44 +6518,44 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>VDA PATIO BONITO</t>
+          <t>NARANJALES</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Apia</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.21</v>
+        <v>3.83</v>
       </c>
       <c r="Q50" t="n">
-        <v>51.87</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="R50" t="n">
-        <v>101.4</v>
+        <v>24.7</v>
       </c>
       <c r="S50" t="n">
-        <v>42.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>No reportó al MEN</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>rojo, verde</t>
+          <t>Afectación menor</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
@@ -6580,12 +6565,12 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 28 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>La Celia-Balboa</t>
+          <t>Calle 21</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
@@ -6594,10 +6579,10 @@
         </is>
       </c>
       <c r="AH50" t="n">
-        <v>4.993201</v>
+        <v>4.81695</v>
       </c>
       <c r="AI50" t="n">
-        <v>-75.981357</v>
+        <v>-75.66296699999999</v>
       </c>
     </row>
     <row r="51">
@@ -6627,69 +6612,69 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SE LA BAMBA</t>
+          <t>INSTITUCION EDUCATIVA PABLO VI</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>IE MARIA AUXILIADORA</t>
+          <t>INSTITUCION EDUCATIVA PABLO SEXTO</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>266687000030</t>
+          <t>166170000078</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>VDA LA BAMBA</t>
+          <t>CALLE 44 NO. 23 - 24</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>34.86</v>
+        <v>2.13</v>
       </c>
       <c r="Q51" t="n">
-        <v>26.5</v>
+        <v>1.22</v>
       </c>
       <c r="R51" t="n">
-        <v>61.4</v>
+        <v>4.5</v>
       </c>
       <c r="S51" t="n">
-        <v>17.5</v>
+        <v>1.6</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>No reportó al MEN</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>Sin concepto técnico ni reporte del rector</t>
+          <t>Afectación menor</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6704,7 +6689,12 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 121 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 38 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>Calle 45</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
@@ -6713,10 +6703,10 @@
         </is>
       </c>
       <c r="AH51" t="n">
-        <v>5.063056</v>
+        <v>4.8345</v>
       </c>
       <c r="AI51" t="n">
-        <v>-75.99972200000001</v>
+        <v>-75.66475</v>
       </c>
     </row>
     <row r="52">
@@ -6735,38 +6725,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SE INSTITUTO SANTUARIO - SEDE PRINCIPAL</t>
+          <t>RUFINO JOSE CUERVO</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>INSTITUCIÓN EDUCATIVA INSTITUTO SANTUARIO</t>
+          <t>INSTITUCION EDUCATIVA PABLO SEXTO</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>166687000256</t>
+          <t>166170000744</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -6776,39 +6766,39 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>CL 6 7 17</t>
+          <t>KR 18 43 08</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0.1</v>
+        <v>1.22</v>
       </c>
       <c r="Q52" t="n">
-        <v>49.67</v>
+        <v>1.17</v>
       </c>
       <c r="R52" t="n">
-        <v>101.6</v>
+        <v>4.5</v>
       </c>
       <c r="S52" t="n">
-        <v>44</v>
+        <v>1.6</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>No reportó al MEN</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>Sin concepto técnico ni reporte del rector</t>
+          <t>Afectación menor</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6823,12 +6813,12 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 18 m de esa vía.</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>Carrera 7</t>
+          <t>Carrera 18</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
@@ -6837,10 +6827,10 @@
         </is>
       </c>
       <c r="AH52" t="n">
-        <v>5.072806629</v>
+        <v>4.835834</v>
       </c>
       <c r="AI52" t="n">
-        <v>-75.96351957</v>
+        <v>-75.6673</v>
       </c>
     </row>
     <row r="53">
@@ -6866,31 +6856,31 @@
         <v>6</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SE MARIA AUXILIADORA</t>
+          <t>MANUELA BELTRAN</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>IE LICEO DE OCCIDENTE</t>
+          <t>INSTITUCION EDUCATIVA CRISTO REY</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>166383000195</t>
+          <t>166170000272</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>La Celia</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -6900,30 +6890,30 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>CL 5 2 69</t>
+          <t>KR 19 64 08</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>49.67</v>
+        <v>2.78</v>
       </c>
       <c r="Q53" t="n">
-        <v>51.88</v>
+        <v>0.86</v>
       </c>
       <c r="R53" t="n">
-        <v>101.6</v>
+        <v>7.4</v>
       </c>
       <c r="S53" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -6937,22 +6927,22 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 18 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 17 m de esa vía.</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>Calle 5</t>
+          <t>Calle 64</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">
@@ -6961,10 +6951,10 @@
         </is>
       </c>
       <c r="AH53" t="n">
-        <v>5.00296197</v>
+        <v>4.843075404</v>
       </c>
       <c r="AI53" t="n">
-        <v>-76.00271345</v>
+        <v>-75.66069447</v>
       </c>
     </row>
     <row r="54">
@@ -6979,99 +6969,104 @@
         </is>
       </c>
       <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6</v>
+      </c>
+      <c r="F54" t="n">
         <v>2</v>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>lunes</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>7</v>
-      </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SE TAMBORES - SEDE PRINCIPAL</t>
+          <t>INSTITUCION EDUCATIVA CRISTO REY</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>IE TAMBORES</t>
+          <t>INSTITUCION EDUCATIVA CRISTO REY</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>266075000022</t>
+          <t>166170000159</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Balboa</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>VDA TAMBORES</t>
+          <t>CLLE 67 # 18-01 BARRIO LA CAPILLA</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Santuario</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Cartago</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>83.7</v>
+        <v>0.86</v>
       </c>
       <c r="Q54" t="n">
-        <v>70.34999999999999</v>
+        <v>3.73</v>
       </c>
       <c r="R54" t="n">
-        <v>154</v>
+        <v>7.4</v>
       </c>
       <c r="S54" t="n">
-        <v>78.09999999999999</v>
+        <v>3</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>No reportó al MEN</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>rojo</t>
+          <t>Afectación menor</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 1 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 11 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>Calle 67</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr">
@@ -7080,10 +7075,10 @@
         </is>
       </c>
       <c r="AH54" t="n">
-        <v>4.885083</v>
+        <v>4.844819</v>
       </c>
       <c r="AI54" t="n">
-        <v>-75.97331699999999</v>
+        <v>-75.660687</v>
       </c>
     </row>
     <row r="55">
@@ -7102,38 +7097,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA LUIS CARLOS GONZALEZ MEJIA</t>
+          <t>ELADIA MEJIA GONZALEZ</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA LUIS CARLOS GONZALEZ MEJIA</t>
+          <t>INSTITUCION EDUCATIVA PABLO SEXTO</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>166001003505</t>
+          <t>166170000175</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -7143,39 +7138,39 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>KR 17 82 103</t>
+          <t>KR 21 41 80</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Cartago</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>32.55</v>
+        <v>2.69</v>
       </c>
       <c r="Q55" t="n">
-        <v>17.05</v>
+        <v>4.67</v>
       </c>
       <c r="R55" t="n">
-        <v>98.59999999999999</v>
+        <v>13</v>
       </c>
       <c r="S55" t="n">
-        <v>55.7</v>
+        <v>4.5</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -7190,7 +7185,12 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 9 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 1 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>Diagonal 46</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="AH55" t="n">
-        <v>4.806935893</v>
+        <v>4.833937</v>
       </c>
       <c r="AI55" t="n">
-        <v>-75.74500842</v>
+        <v>-75.667063</v>
       </c>
     </row>
     <row r="56">
@@ -7221,38 +7221,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>2</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>EL PLACER</t>
+          <t>CENTRO EDUCATIVO LAS VIOLETAS</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA COMBIA</t>
+          <t>INSTITUCION EDUCATIVA FABIO VASQUEZ BOTERO</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>266001001698</t>
+          <t>166170001562</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -7262,39 +7262,39 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>CRUCERO DE COMBIA</t>
+          <t>CL 26A KR 27A -28</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Cartago</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>17.05</v>
+        <v>4.67</v>
       </c>
       <c r="Q56" t="n">
-        <v>48.99</v>
+        <v>5.66</v>
       </c>
       <c r="R56" t="n">
-        <v>98.59999999999999</v>
+        <v>13</v>
       </c>
       <c r="S56" t="n">
-        <v>55.7</v>
+        <v>4.5</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Afectación menor</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 147 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 36 m de esa vía.</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">
@@ -7318,10 +7318,10 @@
         </is>
       </c>
       <c r="AH56" t="n">
-        <v>4.819139218</v>
+        <v>4.825547</v>
       </c>
       <c r="AI56" t="n">
-        <v>-75.76076208000001</v>
+        <v>-75.666341</v>
       </c>
     </row>
     <row r="57">
@@ -7340,11 +7340,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -7356,17 +7356,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>SE EL ESPAÑOL</t>
+          <t>SE CHARCO HONDO</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>IE INSTITUTO AGRICOLA LA FLORIDA</t>
+          <t>IE INSTITUTO AGRICOLA PEDRO URIBE MEJIA</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>266682001771</t>
+          <t>266682000996</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>CGTO EL ESPAÑOL</t>
+          <t>VDA CHARCO HONDO</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -7395,16 +7395,16 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>42.71</v>
+        <v>39.23</v>
       </c>
       <c r="Q57" t="n">
-        <v>51.83</v>
+        <v>19.96</v>
       </c>
       <c r="R57" t="n">
-        <v>105</v>
+        <v>72.3</v>
       </c>
       <c r="S57" t="n">
-        <v>43.1</v>
+        <v>41.3</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -7418,22 +7418,17 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 20 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>Al Español</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 55 m de esa vía.</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">
@@ -7442,10 +7437,10 @@
         </is>
       </c>
       <c r="AH57" t="n">
-        <v>4.932181</v>
+        <v>4.966084</v>
       </c>
       <c r="AI57" t="n">
-        <v>-75.698198</v>
+        <v>-75.63563000000001</v>
       </c>
     </row>
     <row r="58">
@@ -7464,11 +7459,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F58" t="n">
         <v>2</v>
@@ -7480,17 +7475,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SE SANTO DOMINGO</t>
+          <t>SE PEDRO URIBE MEJIA - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>IE INSTITUTO AGROPECUARIO VERACRUZ</t>
+          <t>IE INSTITUTO AGRICOLA PEDRO URIBE MEJIA</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>266682001372</t>
+          <t>266682000465</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -7505,12 +7500,12 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>VDA SANTO DOMINGO</t>
+          <t>VDA EL JAZMIN</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -7519,16 +7514,16 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>51.83</v>
+        <v>19.96</v>
       </c>
       <c r="Q58" t="n">
-        <v>10.45</v>
+        <v>13.15</v>
       </c>
       <c r="R58" t="n">
-        <v>105</v>
+        <v>72.3</v>
       </c>
       <c r="S58" t="n">
-        <v>43.1</v>
+        <v>41.3</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -7552,7 +7547,12 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 30 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 70 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>Vereda El Jazmín</t>
         </is>
       </c>
       <c r="AG58" t="inlineStr">
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="AH58" t="n">
-        <v>4.884255</v>
+        <v>4.909313</v>
       </c>
       <c r="AI58" t="n">
-        <v>-75.634398</v>
+        <v>-75.622938</v>
       </c>
     </row>
     <row r="59">
@@ -7583,11 +7583,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F59" t="n">
         <v>1</v>
@@ -7707,11 +7707,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F60" t="n">
         <v>1</v>
@@ -7723,17 +7723,17 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>SE PEDRO URIBE MEJIA - SEDE PRINCIPAL</t>
+          <t>SE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>IE INSTITUTO AGRICOLA PEDRO URIBE MEJIA</t>
+          <t>IE INSTITUTO AGROPECUARIO VERACRUZ</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>266682000465</t>
+          <t>266682001372</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>VDA EL JAZMIN</t>
+          <t>VDA SANTO DOMINGO</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -7758,20 +7758,20 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Dos Quebradas</t>
+          <t>Santa Rosa De Cabal</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>22.68</v>
+        <v>9.66</v>
       </c>
       <c r="Q60" t="n">
-        <v>33.82</v>
+        <v>10.45</v>
       </c>
       <c r="R60" t="n">
-        <v>93.40000000000001</v>
+        <v>20.1</v>
       </c>
       <c r="S60" t="n">
-        <v>44.4</v>
+        <v>7.4</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -7795,12 +7795,7 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 135 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>A Campoalegre</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 30 m de esa vía.</t>
         </is>
       </c>
       <c r="AG60" t="inlineStr">
@@ -7809,10 +7804,10 @@
         </is>
       </c>
       <c r="AH60" t="n">
-        <v>4.914981371</v>
+        <v>4.884255</v>
       </c>
       <c r="AI60" t="n">
-        <v>-75.61788369</v>
+        <v>-75.634398</v>
       </c>
     </row>
     <row r="61">
@@ -7838,7 +7833,7 @@
         <v>11</v>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -7847,17 +7842,17 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SE CHARCO HONDO</t>
+          <t>SE EL ESPAÑOL</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>IE INSTITUTO AGRICOLA PEDRO URIBE MEJIA</t>
+          <t>IE INSTITUTO AGRICOLA LA FLORIDA</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>266682000996</t>
+          <t>266682001771</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -7872,7 +7867,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>VDA CHARCO HONDO</t>
+          <t>CGTO EL ESPAÑOL</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -7886,16 +7881,16 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>33.82</v>
+        <v>55.88</v>
       </c>
       <c r="Q61" t="n">
-        <v>36.9</v>
+        <v>53.29</v>
       </c>
       <c r="R61" t="n">
-        <v>93.40000000000001</v>
+        <v>112.5</v>
       </c>
       <c r="S61" t="n">
-        <v>44.4</v>
+        <v>42.1</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -7909,17 +7904,22 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 55 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 20 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>Al Español</t>
         </is>
       </c>
       <c r="AG61" t="inlineStr">
@@ -7928,10 +7928,10 @@
         </is>
       </c>
       <c r="AH61" t="n">
-        <v>4.966084</v>
+        <v>4.932181</v>
       </c>
       <c r="AI61" t="n">
-        <v>-75.63563000000001</v>
+        <v>-75.698198</v>
       </c>
     </row>
     <row r="62">
@@ -7950,95 +7950,100 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>sábado</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Dosquebradas</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>SE LAS MANGAS</t>
+          <t>ANTONIO JOSE DE SUCRE</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>IE INSTITUTO AGROPECUARIO VERACRUZ</t>
+          <t>INSTITUCION EDUCATIVA PABLO SEXTO</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>266682001101</t>
+          <t>166170000043</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Santa Rosa de Cabal</t>
+          <t>Dos Quebradas</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>VDA LAS MANGAS</t>
+          <t>CL 16 14 A 19</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
+          <t>Santa Rosa De Cabal</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
           <t>Dos Quebradas</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>Pereira</t>
-        </is>
-      </c>
       <c r="P62" t="n">
-        <v>28.88</v>
+        <v>53.29</v>
       </c>
       <c r="Q62" t="n">
-        <v>23.97</v>
+        <v>3.34</v>
       </c>
       <c r="R62" t="n">
-        <v>57.4</v>
+        <v>112.5</v>
       </c>
       <c r="S62" t="n">
-        <v>22.4</v>
+        <v>42.1</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>No reportó al MEN</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>Sin concepto técnico ni reporte del rector</t>
+          <t>Afectación menor</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>Bajo</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 81 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 23 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>Calle 61</t>
         </is>
       </c>
       <c r="AG62" t="inlineStr">
@@ -8047,10 +8052,10 @@
         </is>
       </c>
       <c r="AH62" t="n">
-        <v>4.783364</v>
+        <v>4.843896232</v>
       </c>
       <c r="AI62" t="n">
-        <v>-75.641834</v>
+        <v>-75.66503904</v>
       </c>
     </row>
     <row r="63">
@@ -8076,109 +8081,228 @@
         <v>12</v>
       </c>
       <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Dosquebradas</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>FABIO VASQUEZ BOTERO</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA FABIO VASQUEZ BOTERO</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>166170001023</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Dos Quebradas</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>LA PRADERA</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Dos Quebradas</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R63" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="S63" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Colapso parcial</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>Critico</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>calle de casco urbano</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>fácil</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 16 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AH63" t="n">
+        <v>4.830277778</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>-75.6825</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
         <v>2</v>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Pereira</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>PROVIDENCIA</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>COMPLEJO EDUCATIVO LA JULITA</t>
-        </is>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>166001004978</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Pereira</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>12</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Dosquebradas</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>INSTITUTO EDUCATIVO EMPRESARIAL</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>INSTITUCION EDUCATIVA EMPRESARIAL</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>166170001911</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Dos Quebradas</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t>Urbana</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>KR 20 23 15</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>LA BADEA -ANTIGUA  PLAZA DE FERIAS</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t>Dos Quebradas</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>Pereira</t>
-        </is>
-      </c>
-      <c r="P63" t="n">
-        <v>23.97</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="R63" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="S63" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>Riesgo inminente de colapso</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>Critico</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>via terciaria</t>
-        </is>
-      </c>
-      <c r="AD63" t="inlineStr">
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="R64" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="S64" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Afectación menor</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>via principal pavimentada</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 3 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>Carrera 20</t>
-        </is>
-      </c>
-      <c r="AG63" t="inlineStr">
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 21 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>Calle 9</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AH63" t="n">
-        <v>4.803937</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>-75.699062</v>
+      <c r="AH64" t="n">
+        <v>4.823055556</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>-75.69194444</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AI63"/>
+  <autoFilter ref="A1:AI64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8204,7 +8328,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>63 SE Risaralda. Las 62 sedes ruteables de las 63 del listado V5. Falta KURMADO (Marsella), que no tiene coordenada en ninguna fuente. Dos de las tres que faltaban se ubicaron con fotos georreferenciadas el 24-sep-2026. Tres cuadrillas con base en Pereira: con dos no cabe. Sin volver a la base los domingos.</t>
+          <t>63 SE Risaralda. Las 63 sedes del listado V5. Dos de las que faltaban se ubicaron con fotos georreferenciadas el 24-sep-2026 y KURMADO (Marsella) con la coordenada que envió el MEN el 30-sep-2026, por confirmar en campo. Tres cuadrillas con base en Pereira: con dos no cabe. Sin volver a la base los domingos.</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8340,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -8342,10 +8466,10 @@
         <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="E11" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F11" t="n">
         <v>12</v>
@@ -8364,13 +8488,13 @@
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>6.1</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="n">
-        <v>129</v>
+        <v>412</v>
       </c>
       <c r="F12" t="n">
         <v>9</v>
@@ -8389,16 +8513,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>16.2</v>
+        <v>6.1</v>
       </c>
       <c r="E13" t="n">
-        <v>447</v>
+        <v>154</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
